--- a/xlsx/dre/DRE_05_2026.xlsx
+++ b/xlsx/dre/DRE_05_2026.xlsx
@@ -474,6 +474,33 @@
     <t>R$ 1.846,76</t>
   </si>
   <si>
+    <t>IRRF/2</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>R$  178,31</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>1/4</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  476,46</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>INSS/0</t>
   </si>
   <si>
@@ -481,33 +508,6 @@
   </si>
   <si>
     <t>R$  1.191,99</t>
-  </si>
-  <si>
-    <t>ADM</t>
-  </si>
-  <si>
-    <t>1/4</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  476,46</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
-  </si>
-  <si>
-    <t>IRRF/2</t>
-  </si>
-  <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>R$  178,31</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -1585,21 +1585,57 @@
     <t>05/08/26</t>
   </si>
   <si>
+    <t>75901/1</t>
+  </si>
+  <si>
+    <t>R$  119,03</t>
+  </si>
+  <si>
+    <t>75901VitorOR</t>
+  </si>
+  <si>
+    <t>73201/1</t>
+  </si>
+  <si>
+    <t>R$  277,04</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  226,76</t>
+  </si>
+  <si>
+    <t>R$  378,22</t>
+  </si>
+  <si>
     <t>01/07/26</t>
   </si>
   <si>
     <t>R$  738,38</t>
   </si>
   <si>
-    <t>R$  378,22</t>
-  </si>
-  <si>
     <t>David Alves</t>
   </si>
   <si>
     <t>R$  210,00</t>
   </si>
   <si>
+    <t>40901/1</t>
+  </si>
+  <si>
+    <t>R$  612,81</t>
+  </si>
+  <si>
+    <t>40901DOUGLASJOS</t>
+  </si>
+  <si>
+    <t>R$  1.007,63</t>
+  </si>
+  <si>
+    <t>73501SilvioOP</t>
+  </si>
+  <si>
     <t>adm/0</t>
   </si>
   <si>
@@ -1609,51 +1645,15 @@
     <t>R$  680,27</t>
   </si>
   <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  226,76</t>
-  </si>
-  <si>
-    <t>40901/1</t>
-  </si>
-  <si>
-    <t>R$  612,81</t>
-  </si>
-  <si>
-    <t>40901DOUGLASJOS</t>
-  </si>
-  <si>
-    <t>R$  1.007,63</t>
-  </si>
-  <si>
-    <t>73501SilvioOP</t>
-  </si>
-  <si>
-    <t>75901/1</t>
-  </si>
-  <si>
-    <t>R$  119,03</t>
-  </si>
-  <si>
-    <t>75901VitorOR</t>
-  </si>
-  <si>
-    <t>73201/1</t>
-  </si>
-  <si>
-    <t>R$  277,04</t>
-  </si>
-  <si>
     <t>DECORA INTERIORES LTDA</t>
   </si>
   <si>
+    <t>R$  437,64</t>
+  </si>
+  <si>
     <t>R$  75,71</t>
   </si>
   <si>
-    <t>R$  437,64</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1726,10 +1726,10 @@
     <t>DSR maio26/1</t>
   </si>
   <si>
+    <t>R$  1.008,15</t>
+  </si>
+  <si>
     <t>R$  480,34</t>
-  </si>
-  <si>
-    <t>R$  1.008,15</t>
   </si>
   <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
@@ -1956,21 +1956,21 @@
     <t>4.03.03.08.01 Brindes para clientes (CV)</t>
   </si>
   <si>
+    <t>BRINDE CLIENTES 3/0</t>
+  </si>
+  <si>
+    <t>Licoretto Bebidas</t>
+  </si>
+  <si>
+    <t>R$  159,96</t>
+  </si>
+  <si>
+    <t>BRINDE CLIENTES 2/0</t>
+  </si>
+  <si>
     <t>BRINDE CLIENTES/0</t>
   </si>
   <si>
-    <t>Licoretto Bebidas</t>
-  </si>
-  <si>
-    <t>R$  159,96</t>
-  </si>
-  <si>
-    <t>BRINDE CLIENTES 2/0</t>
-  </si>
-  <si>
-    <t>BRINDE CLIENTES 3/0</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -2004,6 +2004,18 @@
     <t>Google 2026</t>
   </si>
   <si>
+    <t>1/3</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>R$  3.750,00</t>
+  </si>
+  <si>
+    <t>Facebook 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -2016,18 +2028,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>1/3</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>R$  3.750,00</t>
-  </si>
-  <si>
-    <t>Facebook 2026</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -2070,40 +2070,85 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>19/05/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.645,57</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  1.285,29</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>660/1</t>
+  </si>
+  <si>
+    <t>adiantamento</t>
+  </si>
+  <si>
     <t>Fixo/1</t>
   </si>
   <si>
     <t>R$  54,24</t>
   </si>
   <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  1.285,29</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.687,39</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
   </si>
   <si>
     <t>GUTEMBERG DIAS GOMES</t>
@@ -2115,51 +2160,6 @@
     <t>Gutemberg Dias - Pagamento</t>
   </si>
   <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>19/05/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.645,57</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>660/1</t>
-  </si>
-  <si>
-    <t>adiantamento</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.687,39</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -2400,16 +2400,16 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
-    <t>672/1</t>
-  </si>
-  <si>
-    <t>Lojas Mel</t>
-  </si>
-  <si>
-    <t>R$  19,99</t>
-  </si>
-  <si>
-    <t>Material limpeza</t>
+    <t>668/1</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>R$  177,42</t>
+  </si>
+  <si>
+    <t>Papel interfolhado, esfregão</t>
   </si>
   <si>
     <t>651/1</t>
@@ -2425,16 +2425,16 @@
 </t>
   </si>
   <si>
-    <t>668/1</t>
-  </si>
-  <si>
-    <t>Shopee</t>
-  </si>
-  <si>
-    <t>R$  177,42</t>
-  </si>
-  <si>
-    <t>Papel interfolhado, esfregão</t>
+    <t>672/1</t>
+  </si>
+  <si>
+    <t>Lojas Mel</t>
+  </si>
+  <si>
+    <t>R$  19,99</t>
+  </si>
+  <si>
+    <t>Material limpeza</t>
   </si>
   <si>
     <t>634/1</t>
@@ -2533,19 +2533,64 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>R$  599,00</t>
   </si>
   <si>
     <t>Promob 2026</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
+    <t>64/12</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>22/06/26</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
+    <t>63/12</t>
+  </si>
+  <si>
+    <t>R$  376,44</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>62/12</t>
+  </si>
+  <si>
+    <t>R$  293,21</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
+    <t>3/4</t>
+  </si>
+  <si>
+    <t>R$  1.248,82</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
   </si>
   <si>
     <t>61/1</t>
@@ -2555,51 +2600,6 @@
   </si>
   <si>
     <t>R$  95,73</t>
-  </si>
-  <si>
-    <t>64/12</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>22/06/26</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>63/12</t>
-  </si>
-  <si>
-    <t>R$  376,44</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>62/12</t>
-  </si>
-  <si>
-    <t>R$  293,21</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>3/4</t>
-  </si>
-  <si>
-    <t>R$  1.248,82</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -15235,7 +15235,7 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>230</v>
+        <v>519</v>
       </c>
       <c r="F228" t="s">
         <v>203</v>
@@ -15247,13 +15247,13 @@
         <v>516</v>
       </c>
       <c r="I228" t="s">
-        <v>461</v>
+        <v>520</v>
       </c>
       <c r="J228" t="s">
-        <v>519</v>
+        <v>134</v>
       </c>
       <c r="K228" t="s">
-        <v>51</v>
+        <v>247</v>
       </c>
       <c r="L228" t="s">
         <v>34</v>
@@ -15265,10 +15265,10 @@
         <v>47</v>
       </c>
       <c r="O228" t="s">
-        <v>143</v>
+        <v>521</v>
       </c>
       <c r="P228" t="s">
-        <v>461</v>
+        <v>520</v>
       </c>
       <c r="Q228" t="s">
         <v>47</v>
@@ -15291,7 +15291,7 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>202</v>
+        <v>522</v>
       </c>
       <c r="F229" t="s">
         <v>203</v>
@@ -15303,13 +15303,13 @@
         <v>516</v>
       </c>
       <c r="I229" t="s">
-        <v>457</v>
+        <v>523</v>
       </c>
       <c r="J229" t="s">
-        <v>519</v>
+        <v>134</v>
       </c>
       <c r="K229" t="s">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="L229" t="s">
         <v>34</v>
@@ -15321,10 +15321,10 @@
         <v>47</v>
       </c>
       <c r="O229" t="s">
-        <v>206</v>
+        <v>358</v>
       </c>
       <c r="P229" t="s">
-        <v>457</v>
+        <v>523</v>
       </c>
       <c r="Q229" t="s">
         <v>47</v>
@@ -15347,7 +15347,7 @@
         <v>34</v>
       </c>
       <c r="E230" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="F230" t="s">
         <v>203</v>
@@ -15356,16 +15356,16 @@
         <v>41</v>
       </c>
       <c r="H230" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="I230" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="J230" t="s">
-        <v>519</v>
+        <v>134</v>
       </c>
       <c r="K230" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L230" t="s">
         <v>34</v>
@@ -15377,10 +15377,10 @@
         <v>47</v>
       </c>
       <c r="O230" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="P230" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="Q230" t="s">
         <v>47</v>
@@ -15415,10 +15415,10 @@
         <v>516</v>
       </c>
       <c r="I231" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J231" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K231" t="s">
         <v>70</v>
@@ -15436,7 +15436,7 @@
         <v>106</v>
       </c>
       <c r="P231" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="Q231" t="s">
         <v>47</v>
@@ -15459,7 +15459,7 @@
         <v>34</v>
       </c>
       <c r="E232" t="s">
-        <v>439</v>
+        <v>228</v>
       </c>
       <c r="F232" t="s">
         <v>203</v>
@@ -15468,13 +15468,13 @@
         <v>41</v>
       </c>
       <c r="H232" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="I232" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="J232" t="s">
-        <v>134</v>
+        <v>527</v>
       </c>
       <c r="K232" t="s">
         <v>66</v>
@@ -15489,10 +15489,10 @@
         <v>47</v>
       </c>
       <c r="O232" t="s">
-        <v>138</v>
+        <v>353</v>
       </c>
       <c r="P232" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="Q232" t="s">
         <v>47</v>
@@ -15515,25 +15515,25 @@
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>524</v>
+        <v>439</v>
       </c>
       <c r="F233" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
       </c>
       <c r="H233" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="I233" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="J233" t="s">
         <v>134</v>
       </c>
       <c r="K233" t="s">
-        <v>247</v>
+        <v>66</v>
       </c>
       <c r="L233" t="s">
         <v>34</v>
@@ -15545,10 +15545,10 @@
         <v>47</v>
       </c>
       <c r="O233" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="P233" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="Q233" t="s">
         <v>47</v>
@@ -15571,7 +15571,7 @@
         <v>34</v>
       </c>
       <c r="E234" t="s">
-        <v>215</v>
+        <v>531</v>
       </c>
       <c r="F234" t="s">
         <v>203</v>
@@ -15580,16 +15580,16 @@
         <v>41</v>
       </c>
       <c r="H234" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I234" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="J234" t="s">
         <v>134</v>
       </c>
       <c r="K234" t="s">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15601,10 +15601,10 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>361</v>
+        <v>533</v>
       </c>
       <c r="P234" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Q234" t="s">
         <v>47</v>
@@ -15627,7 +15627,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>529</v>
+        <v>230</v>
       </c>
       <c r="F235" t="s">
         <v>203</v>
@@ -15636,16 +15636,16 @@
         <v>41</v>
       </c>
       <c r="H235" t="s">
+        <v>516</v>
+      </c>
+      <c r="I235" t="s">
+        <v>461</v>
+      </c>
+      <c r="J235" t="s">
         <v>527</v>
       </c>
-      <c r="I235" t="s">
-        <v>530</v>
-      </c>
-      <c r="J235" t="s">
-        <v>134</v>
-      </c>
       <c r="K235" t="s">
-        <v>247</v>
+        <v>51</v>
       </c>
       <c r="L235" t="s">
         <v>34</v>
@@ -15657,10 +15657,10 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>531</v>
+        <v>143</v>
       </c>
       <c r="P235" t="s">
-        <v>530</v>
+        <v>461</v>
       </c>
       <c r="Q235" t="s">
         <v>47</v>
@@ -15695,7 +15695,7 @@
         <v>516</v>
       </c>
       <c r="I236" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J236" t="s">
         <v>134</v>
@@ -15716,7 +15716,7 @@
         <v>103</v>
       </c>
       <c r="P236" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Q236" t="s">
         <v>47</v>
@@ -15769,7 +15769,7 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P237" t="s">
         <v>425</v>
@@ -15795,19 +15795,19 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F238" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G238" t="s">
         <v>41</v>
       </c>
       <c r="H238" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="I238" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J238" t="s">
         <v>134</v>
@@ -15825,10 +15825,10 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>536</v>
+        <v>156</v>
       </c>
       <c r="P238" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="Q238" t="s">
         <v>47</v>
@@ -15851,7 +15851,7 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>537</v>
+        <v>202</v>
       </c>
       <c r="F239" t="s">
         <v>203</v>
@@ -15863,13 +15863,13 @@
         <v>516</v>
       </c>
       <c r="I239" t="s">
-        <v>538</v>
+        <v>457</v>
       </c>
       <c r="J239" t="s">
-        <v>134</v>
+        <v>527</v>
       </c>
       <c r="K239" t="s">
-        <v>247</v>
+        <v>120</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15881,10 +15881,10 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>358</v>
+        <v>206</v>
       </c>
       <c r="P239" t="s">
-        <v>538</v>
+        <v>457</v>
       </c>
       <c r="Q239" t="s">
         <v>47</v>
@@ -15907,7 +15907,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F240" t="s">
         <v>500</v>
@@ -15922,10 +15922,10 @@
         <v>540</v>
       </c>
       <c r="J240" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="K240" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15963,7 +15963,7 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="F241" t="s">
         <v>500</v>
@@ -15978,10 +15978,10 @@
         <v>541</v>
       </c>
       <c r="J241" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="K241" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -16868,7 +16868,7 @@
         <v>41</v>
       </c>
       <c r="H257" t="s">
-        <v>493</v>
+        <v>417</v>
       </c>
       <c r="I257" t="s">
         <v>566</v>
@@ -16924,7 +16924,7 @@
         <v>41</v>
       </c>
       <c r="H258" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="I258" t="s">
         <v>567</v>
@@ -18259,10 +18259,10 @@
         <v>33</v>
       </c>
       <c r="E282" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="F282" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
@@ -18289,7 +18289,7 @@
         <v>47</v>
       </c>
       <c r="O282" t="s">
-        <v>389</v>
+        <v>622</v>
       </c>
       <c r="P282" t="s">
         <v>621</v>
@@ -18371,7 +18371,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F284" t="s">
         <v>173</v>
@@ -18386,10 +18386,10 @@
         <v>621</v>
       </c>
       <c r="J284" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K284" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="L284" t="s">
         <v>34</v>
@@ -18401,7 +18401,7 @@
         <v>47</v>
       </c>
       <c r="O284" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="P284" t="s">
         <v>621</v>
@@ -18427,7 +18427,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="F285" t="s">
         <v>173</v>
@@ -18442,10 +18442,10 @@
         <v>621</v>
       </c>
       <c r="J285" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K285" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18457,7 +18457,7 @@
         <v>47</v>
       </c>
       <c r="O285" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="P285" t="s">
         <v>621</v>
@@ -18483,10 +18483,10 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="F286" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
@@ -18498,10 +18498,10 @@
         <v>621</v>
       </c>
       <c r="J286" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="K286" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -18513,7 +18513,7 @@
         <v>47</v>
       </c>
       <c r="O286" t="s">
-        <v>103</v>
+        <v>353</v>
       </c>
       <c r="P286" t="s">
         <v>621</v>
@@ -18539,7 +18539,7 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="F287" t="s">
         <v>173</v>
@@ -18569,7 +18569,7 @@
         <v>47</v>
       </c>
       <c r="O287" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="P287" t="s">
         <v>621</v>
@@ -18595,10 +18595,10 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F288" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G288" t="s">
         <v>41</v>
@@ -18610,10 +18610,10 @@
         <v>621</v>
       </c>
       <c r="J288" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K288" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18625,7 +18625,7 @@
         <v>47</v>
       </c>
       <c r="O288" t="s">
-        <v>622</v>
+        <v>106</v>
       </c>
       <c r="P288" t="s">
         <v>621</v>
@@ -18651,7 +18651,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F289" t="s">
         <v>173</v>
@@ -18666,10 +18666,10 @@
         <v>621</v>
       </c>
       <c r="J289" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="K289" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="L289" t="s">
         <v>34</v>
@@ -18681,7 +18681,7 @@
         <v>47</v>
       </c>
       <c r="O289" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="P289" t="s">
         <v>621</v>
@@ -18707,10 +18707,10 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="F290" t="s">
-        <v>284</v>
+        <v>199</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
@@ -18722,10 +18722,10 @@
         <v>621</v>
       </c>
       <c r="J290" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="K290" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L290" t="s">
         <v>34</v>
@@ -18737,13 +18737,13 @@
         <v>47</v>
       </c>
       <c r="O290" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="P290" t="s">
-        <v>34</v>
+        <v>621</v>
       </c>
       <c r="Q290" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R290" t="s">
         <v>34</v>
@@ -18763,10 +18763,10 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="F291" t="s">
-        <v>173</v>
+        <v>284</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
@@ -18778,10 +18778,10 @@
         <v>621</v>
       </c>
       <c r="J291" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="K291" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="L291" t="s">
         <v>34</v>
@@ -18793,13 +18793,13 @@
         <v>47</v>
       </c>
       <c r="O291" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="P291" t="s">
-        <v>621</v>
+        <v>34</v>
       </c>
       <c r="Q291" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R291" t="s">
         <v>34</v>
@@ -18819,10 +18819,10 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>213</v>
+        <v>499</v>
       </c>
       <c r="F292" t="s">
-        <v>173</v>
+        <v>284</v>
       </c>
       <c r="G292" t="s">
         <v>41</v>
@@ -18834,10 +18834,10 @@
         <v>621</v>
       </c>
       <c r="J292" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="K292" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="L292" t="s">
         <v>34</v>
@@ -18849,13 +18849,13 @@
         <v>47</v>
       </c>
       <c r="O292" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="P292" t="s">
-        <v>621</v>
+        <v>34</v>
       </c>
       <c r="Q292" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R292" t="s">
         <v>34</v>
@@ -18931,10 +18931,10 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>499</v>
+        <v>213</v>
       </c>
       <c r="F294" t="s">
-        <v>284</v>
+        <v>173</v>
       </c>
       <c r="G294" t="s">
         <v>41</v>
@@ -18946,10 +18946,10 @@
         <v>621</v>
       </c>
       <c r="J294" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="K294" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="L294" t="s">
         <v>34</v>
@@ -18961,13 +18961,13 @@
         <v>47</v>
       </c>
       <c r="O294" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="P294" t="s">
-        <v>34</v>
+        <v>621</v>
       </c>
       <c r="Q294" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R294" t="s">
         <v>34</v>
@@ -19603,7 +19603,7 @@
         <v>34</v>
       </c>
       <c r="E306" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F306" t="s">
         <v>173</v>
@@ -19612,16 +19612,16 @@
         <v>41</v>
       </c>
       <c r="H306" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I306" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J306" t="s">
-        <v>660</v>
+        <v>182</v>
       </c>
       <c r="K306" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="L306" t="s">
         <v>661</v>
@@ -19636,7 +19636,7 @@
         <v>156</v>
       </c>
       <c r="P306" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Q306" t="s">
         <v>47</v>
@@ -19659,7 +19659,7 @@
         <v>34</v>
       </c>
       <c r="E307" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="F307" t="s">
         <v>173</v>
@@ -19668,16 +19668,16 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
+        <v>662</v>
+      </c>
+      <c r="I307" t="s">
         <v>663</v>
       </c>
-      <c r="I307" t="s">
+      <c r="J307" t="s">
         <v>664</v>
       </c>
-      <c r="J307" t="s">
-        <v>182</v>
-      </c>
       <c r="K307" t="s">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="L307" t="s">
         <v>665</v>
@@ -19692,7 +19692,7 @@
         <v>156</v>
       </c>
       <c r="P307" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="Q307" t="s">
         <v>47</v>
@@ -19898,7 +19898,7 @@
         <v>673</v>
       </c>
       <c r="J311" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K311" t="s">
         <v>86</v>
@@ -20051,28 +20051,28 @@
         <v>33</v>
       </c>
       <c r="E314" t="s">
+        <v>157</v>
+      </c>
+      <c r="F314" t="s">
+        <v>173</v>
+      </c>
+      <c r="G314" t="s">
+        <v>41</v>
+      </c>
+      <c r="H314" t="s">
+        <v>497</v>
+      </c>
+      <c r="I314" t="s">
         <v>680</v>
       </c>
-      <c r="F314" t="s">
-        <v>199</v>
-      </c>
-      <c r="G314" t="s">
-        <v>41</v>
-      </c>
-      <c r="H314" t="s">
-        <v>493</v>
-      </c>
-      <c r="I314" t="s">
+      <c r="J314" t="s">
         <v>681</v>
       </c>
-      <c r="J314" t="s">
-        <v>247</v>
-      </c>
       <c r="K314" t="s">
-        <v>247</v>
+        <v>682</v>
       </c>
       <c r="L314" t="s">
-        <v>34</v>
+        <v>683</v>
       </c>
       <c r="M314" t="s">
         <v>679</v>
@@ -20084,7 +20084,7 @@
         <v>156</v>
       </c>
       <c r="P314" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="Q314" t="s">
         <v>47</v>
@@ -20122,13 +20122,13 @@
         <v>673</v>
       </c>
       <c r="J315" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K315" t="s">
         <v>247</v>
       </c>
       <c r="L315" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="M315" t="s">
         <v>679</v>
@@ -20172,19 +20172,19 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I316" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="J316" t="s">
-        <v>294</v>
+        <v>664</v>
       </c>
       <c r="K316" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L316" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="M316" t="s">
         <v>679</v>
@@ -20196,7 +20196,7 @@
         <v>156</v>
       </c>
       <c r="P316" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -20219,7 +20219,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="F317" t="s">
         <v>173</v>
@@ -20228,19 +20228,19 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
-        <v>417</v>
+        <v>689</v>
       </c>
       <c r="I317" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="J317" t="s">
-        <v>687</v>
+        <v>294</v>
       </c>
       <c r="K317" t="s">
-        <v>86</v>
+        <v>247</v>
       </c>
       <c r="L317" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M317" t="s">
         <v>679</v>
@@ -20252,7 +20252,7 @@
         <v>156</v>
       </c>
       <c r="P317" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -20275,7 +20275,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F318" t="s">
         <v>173</v>
@@ -20284,19 +20284,19 @@
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>689</v>
+        <v>417</v>
       </c>
       <c r="I318" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="J318" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="K318" t="s">
         <v>86</v>
       </c>
       <c r="L318" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="M318" t="s">
         <v>679</v>
@@ -20308,7 +20308,7 @@
         <v>156</v>
       </c>
       <c r="P318" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Q318" t="s">
         <v>47</v>
@@ -20340,19 +20340,19 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="I319" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="J319" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K319" t="s">
         <v>86</v>
       </c>
       <c r="L319" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="M319" t="s">
         <v>679</v>
@@ -20364,7 +20364,7 @@
         <v>156</v>
       </c>
       <c r="P319" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Q319" t="s">
         <v>47</v>
@@ -20396,19 +20396,19 @@
         <v>41</v>
       </c>
       <c r="H320" t="s">
-        <v>636</v>
+        <v>436</v>
       </c>
       <c r="I320" t="s">
-        <v>673</v>
+        <v>695</v>
       </c>
       <c r="J320" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K320" t="s">
         <v>86</v>
       </c>
       <c r="L320" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M320" t="s">
         <v>679</v>
@@ -20420,7 +20420,7 @@
         <v>156</v>
       </c>
       <c r="P320" t="s">
-        <v>673</v>
+        <v>695</v>
       </c>
       <c r="Q320" t="s">
         <v>47</v>
@@ -20443,28 +20443,28 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>654</v>
+        <v>698</v>
       </c>
       <c r="F321" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G321" t="s">
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>436</v>
+        <v>686</v>
       </c>
       <c r="I321" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
       <c r="J321" t="s">
-        <v>660</v>
+        <v>57</v>
       </c>
       <c r="K321" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L321" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="M321" t="s">
         <v>679</v>
@@ -20476,7 +20476,7 @@
         <v>156</v>
       </c>
       <c r="P321" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
       <c r="Q321" t="s">
         <v>47</v>
@@ -20499,28 +20499,28 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>157</v>
+        <v>700</v>
       </c>
       <c r="F322" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G322" t="s">
         <v>41</v>
       </c>
       <c r="H322" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="I322" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="J322" t="s">
-        <v>698</v>
+        <v>247</v>
       </c>
       <c r="K322" t="s">
-        <v>699</v>
+        <v>247</v>
       </c>
       <c r="L322" t="s">
-        <v>700</v>
+        <v>34</v>
       </c>
       <c r="M322" t="s">
         <v>679</v>
@@ -20532,7 +20532,7 @@
         <v>156</v>
       </c>
       <c r="P322" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="Q322" t="s">
         <v>47</v>
@@ -20555,7 +20555,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>654</v>
+        <v>157</v>
       </c>
       <c r="F323" t="s">
         <v>173</v>
@@ -20564,19 +20564,19 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
-        <v>701</v>
+        <v>470</v>
       </c>
       <c r="I323" t="s">
-        <v>702</v>
+        <v>680</v>
       </c>
       <c r="J323" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="K323" t="s">
         <v>86</v>
       </c>
       <c r="L323" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="M323" t="s">
         <v>679</v>
@@ -20588,7 +20588,7 @@
         <v>156</v>
       </c>
       <c r="P323" t="s">
-        <v>702</v>
+        <v>680</v>
       </c>
       <c r="Q323" t="s">
         <v>47</v>
@@ -20611,28 +20611,28 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>704</v>
+        <v>654</v>
       </c>
       <c r="F324" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G324" t="s">
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>701</v>
+        <v>636</v>
       </c>
       <c r="I324" t="s">
         <v>673</v>
       </c>
       <c r="J324" t="s">
-        <v>57</v>
+        <v>664</v>
       </c>
       <c r="K324" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L324" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="M324" t="s">
         <v>679</v>
@@ -20667,7 +20667,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>157</v>
+        <v>654</v>
       </c>
       <c r="F325" t="s">
         <v>173</v>
@@ -20676,13 +20676,13 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
-        <v>470</v>
+        <v>704</v>
       </c>
       <c r="I325" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="J325" t="s">
-        <v>698</v>
+        <v>664</v>
       </c>
       <c r="K325" t="s">
         <v>86</v>
@@ -20700,7 +20700,7 @@
         <v>156</v>
       </c>
       <c r="P325" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="Q325" t="s">
         <v>47</v>
@@ -20738,7 +20738,7 @@
         <v>708</v>
       </c>
       <c r="J326" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K326" t="s">
         <v>86</v>
@@ -20844,10 +20844,10 @@
         <v>41</v>
       </c>
       <c r="H328" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I328" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J328" t="s">
         <v>176</v>
@@ -20868,7 +20868,7 @@
         <v>156</v>
       </c>
       <c r="P328" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="Q328" t="s">
         <v>47</v>
@@ -20956,10 +20956,10 @@
         <v>41</v>
       </c>
       <c r="H330" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I330" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J330" t="s">
         <v>176</v>
@@ -20980,7 +20980,7 @@
         <v>156</v>
       </c>
       <c r="P330" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="Q330" t="s">
         <v>47</v>
@@ -21578,7 +21578,7 @@
         <v>746</v>
       </c>
       <c r="J341" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K341" t="s">
         <v>247</v>
@@ -21628,7 +21628,7 @@
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I342" t="s">
         <v>751</v>
@@ -21858,7 +21858,7 @@
         <v>764</v>
       </c>
       <c r="J346" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K346" t="s">
         <v>86</v>
@@ -22026,7 +22026,7 @@
         <v>776</v>
       </c>
       <c r="J349" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K349" t="s">
         <v>75</v>
@@ -22194,7 +22194,7 @@
         <v>785</v>
       </c>
       <c r="J352" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K352" t="s">
         <v>247</v>
@@ -22309,7 +22309,7 @@
         <v>275</v>
       </c>
       <c r="K354" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="L354" t="s">
         <v>793</v>
@@ -22421,7 +22421,7 @@
         <v>275</v>
       </c>
       <c r="K356" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="L356" t="s">
         <v>801</v>
@@ -22698,7 +22698,7 @@
         <v>818</v>
       </c>
       <c r="J361" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K361" t="s">
         <v>86</v>
@@ -22916,19 +22916,19 @@
         <v>41</v>
       </c>
       <c r="H365" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="I365" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="J365" t="s">
         <v>294</v>
       </c>
       <c r="K365" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="L365" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M365" t="s">
         <v>833</v>
@@ -22940,7 +22940,7 @@
         <v>156</v>
       </c>
       <c r="P365" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="Q365" t="s">
         <v>47</v>
@@ -22972,7 +22972,7 @@
         <v>41</v>
       </c>
       <c r="H366" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="I366" t="s">
         <v>837</v>
@@ -22981,7 +22981,7 @@
         <v>294</v>
       </c>
       <c r="K366" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="L366" t="s">
         <v>838</v>
@@ -23034,13 +23034,13 @@
         <v>841</v>
       </c>
       <c r="J367" t="s">
-        <v>807</v>
+        <v>842</v>
       </c>
       <c r="K367" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="L367" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="M367" t="s">
         <v>833</v>
@@ -23075,7 +23075,7 @@
         <v>34</v>
       </c>
       <c r="E368" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="F368" t="s">
         <v>173</v>
@@ -23084,16 +23084,16 @@
         <v>41</v>
       </c>
       <c r="H368" t="s">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="I368" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J368" t="s">
-        <v>845</v>
+        <v>247</v>
       </c>
       <c r="K368" t="s">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="L368" t="s">
         <v>846</v>
@@ -23108,7 +23108,7 @@
         <v>156</v>
       </c>
       <c r="P368" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="Q368" t="s">
         <v>47</v>
@@ -23202,13 +23202,13 @@
         <v>851</v>
       </c>
       <c r="J370" t="s">
-        <v>247</v>
+        <v>852</v>
       </c>
       <c r="K370" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L370" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M370" t="s">
         <v>833</v>
@@ -23243,7 +23243,7 @@
         <v>34</v>
       </c>
       <c r="E371" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F371" t="s">
         <v>173</v>
@@ -23252,19 +23252,19 @@
         <v>41</v>
       </c>
       <c r="H371" t="s">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="I371" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="J371" t="s">
-        <v>855</v>
+        <v>807</v>
       </c>
       <c r="K371" t="s">
         <v>86</v>
       </c>
       <c r="L371" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="M371" t="s">
         <v>833</v>
@@ -23276,7 +23276,7 @@
         <v>156</v>
       </c>
       <c r="P371" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="Q371" t="s">
         <v>47</v>
@@ -23594,7 +23594,7 @@
         <v>877</v>
       </c>
       <c r="J377" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K377" t="s">
         <v>86</v>
@@ -23818,7 +23818,7 @@
         <v>895</v>
       </c>
       <c r="J381" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K381" t="s">
         <v>86</v>
@@ -23930,7 +23930,7 @@
         <v>903</v>
       </c>
       <c r="J383" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="K383" t="s">
         <v>86</v>
@@ -24083,7 +24083,7 @@
         <v>33</v>
       </c>
       <c r="E386" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F386" t="s">
         <v>173</v>

--- a/xlsx/dre/DRE_05_2026.xlsx
+++ b/xlsx/dre/DRE_05_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8572" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8572" uniqueCount="1053">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -1585,6 +1585,51 @@
     <t>05/08/26</t>
   </si>
   <si>
+    <t>01/07/26</t>
+  </si>
+  <si>
+    <t>R$  738,38</t>
+  </si>
+  <si>
+    <t>R$  378,22</t>
+  </si>
+  <si>
+    <t>David Alves</t>
+  </si>
+  <si>
+    <t>R$  210,00</t>
+  </si>
+  <si>
+    <t>adm/0</t>
+  </si>
+  <si>
+    <t>DAVID ALVES</t>
+  </si>
+  <si>
+    <t>R$  680,27</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  226,76</t>
+  </si>
+  <si>
+    <t>40901/1</t>
+  </si>
+  <si>
+    <t>R$  612,81</t>
+  </si>
+  <si>
+    <t>40901DOUGLASJOS</t>
+  </si>
+  <si>
+    <t>R$  1.007,63</t>
+  </si>
+  <si>
+    <t>73501SilvioOP</t>
+  </si>
+  <si>
     <t>75901/1</t>
   </si>
   <si>
@@ -1600,58 +1645,13 @@
     <t>R$  277,04</t>
   </si>
   <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  226,76</t>
-  </si>
-  <si>
-    <t>R$  378,22</t>
-  </si>
-  <si>
-    <t>01/07/26</t>
-  </si>
-  <si>
-    <t>R$  738,38</t>
-  </si>
-  <si>
-    <t>David Alves</t>
-  </si>
-  <si>
-    <t>R$  210,00</t>
-  </si>
-  <si>
-    <t>40901/1</t>
-  </si>
-  <si>
-    <t>R$  612,81</t>
-  </si>
-  <si>
-    <t>40901DOUGLASJOS</t>
-  </si>
-  <si>
-    <t>R$  1.007,63</t>
-  </si>
-  <si>
-    <t>73501SilvioOP</t>
-  </si>
-  <si>
-    <t>adm/0</t>
-  </si>
-  <si>
-    <t>DAVID ALVES</t>
-  </si>
-  <si>
-    <t>R$  680,27</t>
-  </si>
-  <si>
     <t>DECORA INTERIORES LTDA</t>
   </si>
   <si>
+    <t>R$  75,71</t>
+  </si>
+  <si>
     <t>R$  437,64</t>
-  </si>
-  <si>
-    <t>R$  75,71</t>
   </si>
   <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
@@ -2070,6 +2070,60 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Fixo/1</t>
+  </si>
+  <si>
+    <t>R$  54,24</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  1.285,29</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
     <t>R$  2.536,00</t>
   </si>
   <si>
@@ -2082,12 +2136,6 @@
     <t>Salário Fixo -Eric Serpa 2026</t>
   </si>
   <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
     <t>Denny Lucas do Carmo Pereira</t>
   </si>
   <si>
@@ -2097,51 +2145,15 @@
     <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  1.285,29</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
     <t>660/1</t>
   </si>
   <si>
     <t>adiantamento</t>
   </si>
   <si>
-    <t>Fixo/1</t>
-  </si>
-  <si>
-    <t>R$  54,24</t>
-  </si>
-  <si>
     <t>Bianca Rodrigues - Salário fixo 2026</t>
   </si>
   <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
     <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
   </si>
   <si>
@@ -2149,15 +2161,6 @@
   </si>
   <si>
     <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -15235,7 +15238,7 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>519</v>
+        <v>230</v>
       </c>
       <c r="F228" t="s">
         <v>203</v>
@@ -15247,13 +15250,13 @@
         <v>516</v>
       </c>
       <c r="I228" t="s">
-        <v>520</v>
+        <v>461</v>
       </c>
       <c r="J228" t="s">
-        <v>134</v>
+        <v>519</v>
       </c>
       <c r="K228" t="s">
-        <v>247</v>
+        <v>51</v>
       </c>
       <c r="L228" t="s">
         <v>34</v>
@@ -15265,10 +15268,10 @@
         <v>47</v>
       </c>
       <c r="O228" t="s">
-        <v>521</v>
+        <v>143</v>
       </c>
       <c r="P228" t="s">
-        <v>520</v>
+        <v>461</v>
       </c>
       <c r="Q228" t="s">
         <v>47</v>
@@ -15291,7 +15294,7 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>522</v>
+        <v>202</v>
       </c>
       <c r="F229" t="s">
         <v>203</v>
@@ -15303,13 +15306,13 @@
         <v>516</v>
       </c>
       <c r="I229" t="s">
-        <v>523</v>
+        <v>457</v>
       </c>
       <c r="J229" t="s">
-        <v>134</v>
+        <v>519</v>
       </c>
       <c r="K229" t="s">
-        <v>247</v>
+        <v>120</v>
       </c>
       <c r="L229" t="s">
         <v>34</v>
@@ -15321,10 +15324,10 @@
         <v>47</v>
       </c>
       <c r="O229" t="s">
-        <v>358</v>
+        <v>206</v>
       </c>
       <c r="P229" t="s">
-        <v>523</v>
+        <v>457</v>
       </c>
       <c r="Q229" t="s">
         <v>47</v>
@@ -15347,7 +15350,7 @@
         <v>34</v>
       </c>
       <c r="E230" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="F230" t="s">
         <v>203</v>
@@ -15356,16 +15359,16 @@
         <v>41</v>
       </c>
       <c r="H230" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="I230" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="J230" t="s">
-        <v>134</v>
+        <v>519</v>
       </c>
       <c r="K230" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="L230" t="s">
         <v>34</v>
@@ -15377,10 +15380,10 @@
         <v>47</v>
       </c>
       <c r="O230" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="P230" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="Q230" t="s">
         <v>47</v>
@@ -15415,10 +15418,10 @@
         <v>516</v>
       </c>
       <c r="I231" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="J231" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K231" t="s">
         <v>70</v>
@@ -15436,7 +15439,7 @@
         <v>106</v>
       </c>
       <c r="P231" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="Q231" t="s">
         <v>47</v>
@@ -15459,7 +15462,7 @@
         <v>34</v>
       </c>
       <c r="E232" t="s">
-        <v>228</v>
+        <v>439</v>
       </c>
       <c r="F232" t="s">
         <v>203</v>
@@ -15468,13 +15471,13 @@
         <v>41</v>
       </c>
       <c r="H232" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="I232" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="J232" t="s">
-        <v>527</v>
+        <v>134</v>
       </c>
       <c r="K232" t="s">
         <v>66</v>
@@ -15489,10 +15492,10 @@
         <v>47</v>
       </c>
       <c r="O232" t="s">
-        <v>353</v>
+        <v>138</v>
       </c>
       <c r="P232" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="Q232" t="s">
         <v>47</v>
@@ -15515,25 +15518,25 @@
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>439</v>
+        <v>524</v>
       </c>
       <c r="F233" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
       </c>
       <c r="H233" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="I233" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="J233" t="s">
         <v>134</v>
       </c>
       <c r="K233" t="s">
-        <v>66</v>
+        <v>247</v>
       </c>
       <c r="L233" t="s">
         <v>34</v>
@@ -15545,10 +15548,10 @@
         <v>47</v>
       </c>
       <c r="O233" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="P233" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="Q233" t="s">
         <v>47</v>
@@ -15571,7 +15574,7 @@
         <v>34</v>
       </c>
       <c r="E234" t="s">
-        <v>531</v>
+        <v>215</v>
       </c>
       <c r="F234" t="s">
         <v>203</v>
@@ -15580,16 +15583,16 @@
         <v>41</v>
       </c>
       <c r="H234" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="I234" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="J234" t="s">
         <v>134</v>
       </c>
       <c r="K234" t="s">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15601,10 +15604,10 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>533</v>
+        <v>361</v>
       </c>
       <c r="P234" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="Q234" t="s">
         <v>47</v>
@@ -15627,7 +15630,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>230</v>
+        <v>529</v>
       </c>
       <c r="F235" t="s">
         <v>203</v>
@@ -15636,16 +15639,16 @@
         <v>41</v>
       </c>
       <c r="H235" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="I235" t="s">
-        <v>461</v>
+        <v>530</v>
       </c>
       <c r="J235" t="s">
-        <v>527</v>
+        <v>134</v>
       </c>
       <c r="K235" t="s">
-        <v>51</v>
+        <v>247</v>
       </c>
       <c r="L235" t="s">
         <v>34</v>
@@ -15657,10 +15660,10 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>143</v>
+        <v>531</v>
       </c>
       <c r="P235" t="s">
-        <v>461</v>
+        <v>530</v>
       </c>
       <c r="Q235" t="s">
         <v>47</v>
@@ -15695,7 +15698,7 @@
         <v>516</v>
       </c>
       <c r="I236" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="J236" t="s">
         <v>134</v>
@@ -15716,7 +15719,7 @@
         <v>103</v>
       </c>
       <c r="P236" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="Q236" t="s">
         <v>47</v>
@@ -15769,7 +15772,7 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="P237" t="s">
         <v>425</v>
@@ -15795,19 +15798,19 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F238" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G238" t="s">
         <v>41</v>
       </c>
       <c r="H238" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="I238" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J238" t="s">
         <v>134</v>
@@ -15825,10 +15828,10 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>156</v>
+        <v>536</v>
       </c>
       <c r="P238" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="Q238" t="s">
         <v>47</v>
@@ -15851,7 +15854,7 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>202</v>
+        <v>537</v>
       </c>
       <c r="F239" t="s">
         <v>203</v>
@@ -15863,13 +15866,13 @@
         <v>516</v>
       </c>
       <c r="I239" t="s">
-        <v>457</v>
+        <v>538</v>
       </c>
       <c r="J239" t="s">
-        <v>527</v>
+        <v>134</v>
       </c>
       <c r="K239" t="s">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15881,10 +15884,10 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>206</v>
+        <v>358</v>
       </c>
       <c r="P239" t="s">
-        <v>457</v>
+        <v>538</v>
       </c>
       <c r="Q239" t="s">
         <v>47</v>
@@ -15907,7 +15910,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="F240" t="s">
         <v>500</v>
@@ -15922,10 +15925,10 @@
         <v>540</v>
       </c>
       <c r="J240" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="K240" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15963,7 +15966,7 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F241" t="s">
         <v>500</v>
@@ -15978,10 +15981,10 @@
         <v>541</v>
       </c>
       <c r="J241" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="K241" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -20051,28 +20054,28 @@
         <v>33</v>
       </c>
       <c r="E314" t="s">
-        <v>157</v>
+        <v>680</v>
       </c>
       <c r="F314" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G314" t="s">
         <v>41</v>
       </c>
       <c r="H314" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="I314" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J314" t="s">
-        <v>681</v>
+        <v>247</v>
       </c>
       <c r="K314" t="s">
-        <v>682</v>
+        <v>247</v>
       </c>
       <c r="L314" t="s">
-        <v>683</v>
+        <v>34</v>
       </c>
       <c r="M314" t="s">
         <v>679</v>
@@ -20084,7 +20087,7 @@
         <v>156</v>
       </c>
       <c r="P314" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Q314" t="s">
         <v>47</v>
@@ -20122,13 +20125,13 @@
         <v>673</v>
       </c>
       <c r="J315" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K315" t="s">
         <v>247</v>
       </c>
       <c r="L315" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="M315" t="s">
         <v>679</v>
@@ -20172,19 +20175,19 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="I316" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="J316" t="s">
-        <v>664</v>
+        <v>294</v>
       </c>
       <c r="K316" t="s">
-        <v>86</v>
+        <v>247</v>
       </c>
       <c r="L316" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="M316" t="s">
         <v>679</v>
@@ -20196,7 +20199,7 @@
         <v>156</v>
       </c>
       <c r="P316" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -20219,7 +20222,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F317" t="s">
         <v>173</v>
@@ -20228,19 +20231,19 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
-        <v>689</v>
+        <v>417</v>
       </c>
       <c r="I317" t="s">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="J317" t="s">
-        <v>294</v>
+        <v>687</v>
       </c>
       <c r="K317" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L317" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="M317" t="s">
         <v>679</v>
@@ -20252,7 +20255,7 @@
         <v>156</v>
       </c>
       <c r="P317" t="s">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -20275,7 +20278,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="F318" t="s">
         <v>173</v>
@@ -20284,19 +20287,19 @@
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>417</v>
+        <v>689</v>
       </c>
       <c r="I318" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J318" t="s">
-        <v>692</v>
+        <v>664</v>
       </c>
       <c r="K318" t="s">
         <v>86</v>
       </c>
       <c r="L318" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="M318" t="s">
         <v>679</v>
@@ -20308,7 +20311,7 @@
         <v>156</v>
       </c>
       <c r="P318" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="Q318" t="s">
         <v>47</v>
@@ -20340,10 +20343,10 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="I319" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="J319" t="s">
         <v>664</v>
@@ -20352,7 +20355,7 @@
         <v>86</v>
       </c>
       <c r="L319" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="M319" t="s">
         <v>679</v>
@@ -20364,7 +20367,7 @@
         <v>156</v>
       </c>
       <c r="P319" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="Q319" t="s">
         <v>47</v>
@@ -20396,10 +20399,10 @@
         <v>41</v>
       </c>
       <c r="H320" t="s">
-        <v>436</v>
+        <v>636</v>
       </c>
       <c r="I320" t="s">
-        <v>695</v>
+        <v>673</v>
       </c>
       <c r="J320" t="s">
         <v>664</v>
@@ -20408,7 +20411,7 @@
         <v>86</v>
       </c>
       <c r="L320" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="M320" t="s">
         <v>679</v>
@@ -20420,7 +20423,7 @@
         <v>156</v>
       </c>
       <c r="P320" t="s">
-        <v>695</v>
+        <v>673</v>
       </c>
       <c r="Q320" t="s">
         <v>47</v>
@@ -20443,28 +20446,28 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>698</v>
+        <v>654</v>
       </c>
       <c r="F321" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G321" t="s">
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="I321" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="J321" t="s">
-        <v>57</v>
+        <v>664</v>
       </c>
       <c r="K321" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L321" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="M321" t="s">
         <v>679</v>
@@ -20476,7 +20479,7 @@
         <v>156</v>
       </c>
       <c r="P321" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="Q321" t="s">
         <v>47</v>
@@ -20499,28 +20502,28 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
+        <v>157</v>
+      </c>
+      <c r="F322" t="s">
+        <v>173</v>
+      </c>
+      <c r="G322" t="s">
+        <v>41</v>
+      </c>
+      <c r="H322" t="s">
+        <v>497</v>
+      </c>
+      <c r="I322" t="s">
+        <v>698</v>
+      </c>
+      <c r="J322" t="s">
+        <v>699</v>
+      </c>
+      <c r="K322" t="s">
         <v>700</v>
       </c>
-      <c r="F322" t="s">
-        <v>199</v>
-      </c>
-      <c r="G322" t="s">
-        <v>41</v>
-      </c>
-      <c r="H322" t="s">
-        <v>493</v>
-      </c>
-      <c r="I322" t="s">
+      <c r="L322" t="s">
         <v>701</v>
-      </c>
-      <c r="J322" t="s">
-        <v>247</v>
-      </c>
-      <c r="K322" t="s">
-        <v>247</v>
-      </c>
-      <c r="L322" t="s">
-        <v>34</v>
       </c>
       <c r="M322" t="s">
         <v>679</v>
@@ -20532,7 +20535,7 @@
         <v>156</v>
       </c>
       <c r="P322" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="Q322" t="s">
         <v>47</v>
@@ -20555,7 +20558,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>157</v>
+        <v>654</v>
       </c>
       <c r="F323" t="s">
         <v>173</v>
@@ -20564,19 +20567,19 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
-        <v>470</v>
+        <v>702</v>
       </c>
       <c r="I323" t="s">
-        <v>680</v>
+        <v>703</v>
       </c>
       <c r="J323" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="K323" t="s">
         <v>86</v>
       </c>
       <c r="L323" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="M323" t="s">
         <v>679</v>
@@ -20588,7 +20591,7 @@
         <v>156</v>
       </c>
       <c r="P323" t="s">
-        <v>680</v>
+        <v>703</v>
       </c>
       <c r="Q323" t="s">
         <v>47</v>
@@ -20611,28 +20614,28 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>654</v>
+        <v>705</v>
       </c>
       <c r="F324" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G324" t="s">
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>636</v>
+        <v>702</v>
       </c>
       <c r="I324" t="s">
         <v>673</v>
       </c>
       <c r="J324" t="s">
-        <v>664</v>
+        <v>57</v>
       </c>
       <c r="K324" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L324" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="M324" t="s">
         <v>679</v>
@@ -20667,7 +20670,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>654</v>
+        <v>157</v>
       </c>
       <c r="F325" t="s">
         <v>173</v>
@@ -20676,19 +20679,19 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
-        <v>704</v>
+        <v>470</v>
       </c>
       <c r="I325" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="J325" t="s">
-        <v>664</v>
+        <v>699</v>
       </c>
       <c r="K325" t="s">
         <v>86</v>
       </c>
       <c r="L325" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M325" t="s">
         <v>679</v>
@@ -20700,7 +20703,7 @@
         <v>156</v>
       </c>
       <c r="P325" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="Q325" t="s">
         <v>47</v>
@@ -20732,10 +20735,10 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I326" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J326" t="s">
         <v>664</v>
@@ -20744,7 +20747,7 @@
         <v>86</v>
       </c>
       <c r="L326" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M326" t="s">
         <v>679</v>
@@ -20756,7 +20759,7 @@
         <v>156</v>
       </c>
       <c r="P326" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Q326" t="s">
         <v>47</v>
@@ -20767,13 +20770,13 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="1">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B327" t="s" s="1">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C327" t="s" s="1">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D327" t="s" s="1">
         <v>33</v>
@@ -20823,13 +20826,13 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
+        <v>713</v>
+      </c>
+      <c r="B328" t="s">
         <v>712</v>
       </c>
-      <c r="B328" t="s">
-        <v>711</v>
-      </c>
       <c r="C328" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D328" t="s">
         <v>33</v>
@@ -20856,10 +20859,10 @@
         <v>44</v>
       </c>
       <c r="L328" t="s">
+        <v>714</v>
+      </c>
+      <c r="M328" t="s">
         <v>713</v>
-      </c>
-      <c r="M328" t="s">
-        <v>712</v>
       </c>
       <c r="N328" t="s">
         <v>47</v>
@@ -20879,13 +20882,13 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="1">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B329" t="s" s="1">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C329" t="s" s="1">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D329" t="s" s="1">
         <v>33</v>
@@ -20935,13 +20938,13 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
+        <v>717</v>
+      </c>
+      <c r="B330" t="s">
         <v>716</v>
       </c>
-      <c r="B330" t="s">
-        <v>715</v>
-      </c>
       <c r="C330" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D330" t="s">
         <v>33</v>
@@ -20968,10 +20971,10 @@
         <v>44</v>
       </c>
       <c r="L330" t="s">
+        <v>718</v>
+      </c>
+      <c r="M330" t="s">
         <v>717</v>
-      </c>
-      <c r="M330" t="s">
-        <v>716</v>
       </c>
       <c r="N330" t="s">
         <v>47</v>
@@ -20991,13 +20994,13 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="1">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B331" t="s" s="1">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C331" t="s" s="1">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D331" t="s" s="1">
         <v>33</v>
@@ -21047,13 +21050,13 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
+        <v>721</v>
+      </c>
+      <c r="B332" t="s">
         <v>720</v>
       </c>
-      <c r="B332" t="s">
-        <v>719</v>
-      </c>
       <c r="C332" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D332" t="s">
         <v>33</v>
@@ -21068,10 +21071,10 @@
         <v>41</v>
       </c>
       <c r="H332" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I332" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J332" t="s">
         <v>176</v>
@@ -21080,10 +21083,10 @@
         <v>44</v>
       </c>
       <c r="L332" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M332" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N332" t="s">
         <v>47</v>
@@ -21092,7 +21095,7 @@
         <v>156</v>
       </c>
       <c r="P332" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="Q332" t="s">
         <v>47</v>
@@ -21103,13 +21106,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="1">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B333" t="s" s="1">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C333" t="s" s="1">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D333" t="s" s="1">
         <v>33</v>
@@ -21159,13 +21162,13 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
+        <v>727</v>
+      </c>
+      <c r="B334" t="s">
         <v>726</v>
       </c>
-      <c r="B334" t="s">
-        <v>725</v>
-      </c>
       <c r="C334" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D334" t="s">
         <v>33</v>
@@ -21183,7 +21186,7 @@
         <v>539</v>
       </c>
       <c r="I334" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="J334" t="s">
         <v>176</v>
@@ -21195,7 +21198,7 @@
         <v>34</v>
       </c>
       <c r="M334" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N334" t="s">
         <v>47</v>
@@ -21215,13 +21218,13 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="1">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B335" t="s" s="1">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C335" t="s" s="1">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D335" t="s" s="1">
         <v>33</v>
@@ -21271,13 +21274,13 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="1">
+        <v>731</v>
+      </c>
+      <c r="B336" t="s" s="1">
         <v>730</v>
       </c>
-      <c r="B336" t="s" s="1">
-        <v>729</v>
-      </c>
       <c r="C336" t="s" s="1">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D336" t="s" s="1">
         <v>33</v>
@@ -21327,19 +21330,19 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B337" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C337" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D337" t="s">
         <v>33</v>
       </c>
       <c r="E337" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F337" t="s">
         <v>199</v>
@@ -21351,19 +21354,19 @@
         <v>417</v>
       </c>
       <c r="I337" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J337" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="K337" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L337" t="s">
         <v>34</v>
       </c>
       <c r="M337" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N337" t="s">
         <v>47</v>
@@ -21372,7 +21375,7 @@
         <v>156</v>
       </c>
       <c r="P337" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="Q337" t="s">
         <v>47</v>
@@ -21383,7 +21386,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B338" t="s">
         <v>34</v>
@@ -21395,7 +21398,7 @@
         <v>34</v>
       </c>
       <c r="E338" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F338" t="s">
         <v>199</v>
@@ -21407,10 +21410,10 @@
         <v>493</v>
       </c>
       <c r="I338" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="J338" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K338" t="s">
         <v>247</v>
@@ -21419,7 +21422,7 @@
         <v>34</v>
       </c>
       <c r="M338" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N338" t="s">
         <v>47</v>
@@ -21428,7 +21431,7 @@
         <v>156</v>
       </c>
       <c r="P338" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="Q338" t="s">
         <v>47</v>
@@ -21439,13 +21442,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="1">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B339" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C339" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D339" t="s" s="1">
         <v>33</v>
@@ -21495,13 +21498,13 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="1">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B340" t="s" s="1">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C340" t="s" s="1">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D340" t="s" s="1">
         <v>33</v>
@@ -21551,19 +21554,19 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B341" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C341" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D341" t="s">
         <v>33</v>
       </c>
       <c r="E341" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F341" t="s">
         <v>173</v>
@@ -21572,10 +21575,10 @@
         <v>41</v>
       </c>
       <c r="H341" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I341" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J341" t="s">
         <v>664</v>
@@ -21584,10 +21587,10 @@
         <v>247</v>
       </c>
       <c r="L341" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M341" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N341" t="s">
         <v>47</v>
@@ -21596,7 +21599,7 @@
         <v>156</v>
       </c>
       <c r="P341" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="Q341" t="s">
         <v>47</v>
@@ -21607,19 +21610,19 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B342" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C342" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D342" t="s">
         <v>33</v>
       </c>
       <c r="E342" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F342" t="s">
         <v>199</v>
@@ -21631,7 +21634,7 @@
         <v>154</v>
       </c>
       <c r="I342" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J342" t="s">
         <v>247</v>
@@ -21643,7 +21646,7 @@
         <v>34</v>
       </c>
       <c r="M342" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N342" t="s">
         <v>47</v>
@@ -21652,7 +21655,7 @@
         <v>156</v>
       </c>
       <c r="P342" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Q342" t="s">
         <v>47</v>
@@ -21663,13 +21666,13 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="1">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B343" t="s" s="1">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C343" t="s" s="1">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D343" t="s" s="1">
         <v>33</v>
@@ -21719,19 +21722,19 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
+        <v>755</v>
+      </c>
+      <c r="B344" t="s">
         <v>754</v>
       </c>
-      <c r="B344" t="s">
-        <v>753</v>
-      </c>
       <c r="C344" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D344" t="s">
         <v>33</v>
       </c>
       <c r="E344" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F344" t="s">
         <v>173</v>
@@ -21740,22 +21743,22 @@
         <v>41</v>
       </c>
       <c r="H344" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I344" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J344" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K344" t="s">
         <v>100</v>
       </c>
       <c r="L344" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M344" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N344" t="s">
         <v>47</v>
@@ -21764,7 +21767,7 @@
         <v>156</v>
       </c>
       <c r="P344" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Q344" t="s">
         <v>47</v>
@@ -21775,13 +21778,13 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="1">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B345" t="s" s="1">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C345" t="s" s="1">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D345" t="s" s="1">
         <v>33</v>
@@ -21831,13 +21834,13 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
+        <v>763</v>
+      </c>
+      <c r="B346" t="s">
         <v>762</v>
       </c>
-      <c r="B346" t="s">
-        <v>761</v>
-      </c>
       <c r="C346" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D346" t="s">
         <v>33</v>
@@ -21852,10 +21855,10 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="I346" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J346" t="s">
         <v>664</v>
@@ -21864,10 +21867,10 @@
         <v>86</v>
       </c>
       <c r="L346" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M346" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N346" t="s">
         <v>47</v>
@@ -21876,7 +21879,7 @@
         <v>156</v>
       </c>
       <c r="P346" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="Q346" t="s">
         <v>47</v>
@@ -21887,13 +21890,13 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="1">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B347" t="s" s="1">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C347" t="s" s="1">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D347" t="s" s="1">
         <v>33</v>
@@ -21943,19 +21946,19 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B348" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C348" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D348" t="s">
         <v>33</v>
       </c>
       <c r="E348" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F348" t="s">
         <v>173</v>
@@ -21964,22 +21967,22 @@
         <v>41</v>
       </c>
       <c r="H348" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I348" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="J348" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K348" t="s">
         <v>66</v>
       </c>
       <c r="L348" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M348" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N348" t="s">
         <v>47</v>
@@ -21988,7 +21991,7 @@
         <v>156</v>
       </c>
       <c r="P348" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Q348" t="s">
         <v>47</v>
@@ -21999,13 +22002,13 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B349" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C349" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D349" t="s">
         <v>33</v>
@@ -22020,10 +22023,10 @@
         <v>41</v>
       </c>
       <c r="H349" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I349" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J349" t="s">
         <v>664</v>
@@ -22032,10 +22035,10 @@
         <v>75</v>
       </c>
       <c r="L349" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M349" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N349" t="s">
         <v>47</v>
@@ -22044,7 +22047,7 @@
         <v>156</v>
       </c>
       <c r="P349" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="Q349" t="s">
         <v>47</v>
@@ -22055,13 +22058,13 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="1">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B350" t="s" s="1">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C350" t="s" s="1">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D350" t="s" s="1">
         <v>33</v>
@@ -22111,19 +22114,19 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
+        <v>781</v>
+      </c>
+      <c r="B351" t="s">
         <v>780</v>
       </c>
-      <c r="B351" t="s">
-        <v>779</v>
-      </c>
       <c r="C351" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D351" t="s">
         <v>33</v>
       </c>
       <c r="E351" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F351" t="s">
         <v>199</v>
@@ -22132,10 +22135,10 @@
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I351" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="J351" t="s">
         <v>79</v>
@@ -22147,7 +22150,7 @@
         <v>34</v>
       </c>
       <c r="M351" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N351" t="s">
         <v>47</v>
@@ -22156,7 +22159,7 @@
         <v>156</v>
       </c>
       <c r="P351" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="Q351" t="s">
         <v>47</v>
@@ -22167,7 +22170,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B352" t="s">
         <v>34</v>
@@ -22179,7 +22182,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F352" t="s">
         <v>173</v>
@@ -22188,10 +22191,10 @@
         <v>41</v>
       </c>
       <c r="H352" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="I352" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="J352" t="s">
         <v>664</v>
@@ -22200,10 +22203,10 @@
         <v>247</v>
       </c>
       <c r="L352" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M352" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N352" t="s">
         <v>47</v>
@@ -22212,7 +22215,7 @@
         <v>156</v>
       </c>
       <c r="P352" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Q352" t="s">
         <v>47</v>
@@ -22223,13 +22226,13 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="1">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B353" t="s" s="1">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C353" t="s" s="1">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D353" t="s" s="1">
         <v>33</v>
@@ -22279,19 +22282,19 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
+        <v>790</v>
+      </c>
+      <c r="B354" t="s">
         <v>789</v>
       </c>
-      <c r="B354" t="s">
-        <v>788</v>
-      </c>
       <c r="C354" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D354" t="s">
         <v>33</v>
       </c>
       <c r="E354" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F354" t="s">
         <v>199</v>
@@ -22300,10 +22303,10 @@
         <v>41</v>
       </c>
       <c r="H354" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="I354" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="J354" t="s">
         <v>275</v>
@@ -22312,10 +22315,10 @@
         <v>45</v>
       </c>
       <c r="L354" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="M354" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N354" t="s">
         <v>47</v>
@@ -22324,7 +22327,7 @@
         <v>156</v>
       </c>
       <c r="P354" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="Q354" t="s">
         <v>47</v>
@@ -22335,7 +22338,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B355" t="s">
         <v>34</v>
@@ -22347,7 +22350,7 @@
         <v>34</v>
       </c>
       <c r="E355" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F355" t="s">
         <v>199</v>
@@ -22356,10 +22359,10 @@
         <v>41</v>
       </c>
       <c r="H355" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="I355" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="J355" t="s">
         <v>66</v>
@@ -22368,10 +22371,10 @@
         <v>56</v>
       </c>
       <c r="L355" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M355" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N355" t="s">
         <v>47</v>
@@ -22380,7 +22383,7 @@
         <v>156</v>
       </c>
       <c r="P355" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="Q355" t="s">
         <v>47</v>
@@ -22391,7 +22394,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B356" t="s">
         <v>34</v>
@@ -22403,7 +22406,7 @@
         <v>34</v>
       </c>
       <c r="E356" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F356" t="s">
         <v>199</v>
@@ -22412,10 +22415,10 @@
         <v>41</v>
       </c>
       <c r="H356" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="I356" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="J356" t="s">
         <v>275</v>
@@ -22424,10 +22427,10 @@
         <v>86</v>
       </c>
       <c r="L356" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M356" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N356" t="s">
         <v>47</v>
@@ -22436,7 +22439,7 @@
         <v>156</v>
       </c>
       <c r="P356" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="Q356" t="s">
         <v>47</v>
@@ -22447,7 +22450,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B357" t="s">
         <v>34</v>
@@ -22459,7 +22462,7 @@
         <v>34</v>
       </c>
       <c r="E357" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F357" t="s">
         <v>199</v>
@@ -22468,7 +22471,7 @@
         <v>41</v>
       </c>
       <c r="H357" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I357" t="s">
         <v>624</v>
@@ -22480,10 +22483,10 @@
         <v>100</v>
       </c>
       <c r="L357" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M357" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N357" t="s">
         <v>47</v>
@@ -22503,7 +22506,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B358" t="s">
         <v>34</v>
@@ -22515,7 +22518,7 @@
         <v>34</v>
       </c>
       <c r="E358" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F358" t="s">
         <v>173</v>
@@ -22527,19 +22530,19 @@
         <v>292</v>
       </c>
       <c r="I358" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="J358" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K358" t="s">
         <v>86</v>
       </c>
       <c r="L358" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M358" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N358" t="s">
         <v>47</v>
@@ -22548,7 +22551,7 @@
         <v>156</v>
       </c>
       <c r="P358" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="Q358" t="s">
         <v>47</v>
@@ -22559,7 +22562,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B359" t="s">
         <v>34</v>
@@ -22571,7 +22574,7 @@
         <v>34</v>
       </c>
       <c r="E359" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F359" t="s">
         <v>199</v>
@@ -22580,10 +22583,10 @@
         <v>41</v>
       </c>
       <c r="H359" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I359" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="J359" t="s">
         <v>56</v>
@@ -22592,10 +22595,10 @@
         <v>61</v>
       </c>
       <c r="L359" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M359" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N359" t="s">
         <v>47</v>
@@ -22604,7 +22607,7 @@
         <v>156</v>
       </c>
       <c r="P359" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="Q359" t="s">
         <v>47</v>
@@ -22615,13 +22618,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="1">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B360" t="s" s="1">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C360" t="s" s="1">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D360" t="s" s="1">
         <v>33</v>
@@ -22671,13 +22674,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B361" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C361" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D361" t="s">
         <v>33</v>
@@ -22692,10 +22695,10 @@
         <v>41</v>
       </c>
       <c r="H361" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="I361" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="J361" t="s">
         <v>664</v>
@@ -22704,10 +22707,10 @@
         <v>86</v>
       </c>
       <c r="L361" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="M361" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N361" t="s">
         <v>47</v>
@@ -22716,7 +22719,7 @@
         <v>156</v>
       </c>
       <c r="P361" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="Q361" t="s">
         <v>47</v>
@@ -22727,19 +22730,19 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B362" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C362" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D362" t="s">
         <v>33</v>
       </c>
       <c r="E362" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F362" t="s">
         <v>173</v>
@@ -22748,22 +22751,22 @@
         <v>41</v>
       </c>
       <c r="H362" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I362" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J362" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K362" t="s">
         <v>56</v>
       </c>
       <c r="L362" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M362" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="N362" t="s">
         <v>47</v>
@@ -22772,7 +22775,7 @@
         <v>156</v>
       </c>
       <c r="P362" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="Q362" t="s">
         <v>47</v>
@@ -22783,19 +22786,19 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B363" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C363" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D363" t="s">
         <v>33</v>
       </c>
       <c r="E363" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F363" t="s">
         <v>173</v>
@@ -22804,22 +22807,22 @@
         <v>41</v>
       </c>
       <c r="H363" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I363" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="J363" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K363" t="s">
         <v>86</v>
       </c>
       <c r="L363" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="M363" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N363" t="s">
         <v>47</v>
@@ -22828,7 +22831,7 @@
         <v>156</v>
       </c>
       <c r="P363" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="Q363" t="s">
         <v>47</v>
@@ -22839,13 +22842,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="1">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B364" t="s" s="1">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C364" t="s" s="1">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D364" t="s" s="1">
         <v>33</v>
@@ -22895,13 +22898,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
+        <v>834</v>
+      </c>
+      <c r="B365" t="s">
         <v>833</v>
       </c>
-      <c r="B365" t="s">
-        <v>832</v>
-      </c>
       <c r="C365" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D365" t="s">
         <v>33</v>
@@ -22916,10 +22919,10 @@
         <v>41</v>
       </c>
       <c r="H365" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I365" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="J365" t="s">
         <v>294</v>
@@ -22928,10 +22931,10 @@
         <v>86</v>
       </c>
       <c r="L365" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M365" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N365" t="s">
         <v>47</v>
@@ -22940,7 +22943,7 @@
         <v>156</v>
       </c>
       <c r="P365" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="Q365" t="s">
         <v>47</v>
@@ -22951,7 +22954,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B366" t="s">
         <v>34</v>
@@ -22972,10 +22975,10 @@
         <v>41</v>
       </c>
       <c r="H366" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I366" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="J366" t="s">
         <v>294</v>
@@ -22984,10 +22987,10 @@
         <v>62</v>
       </c>
       <c r="L366" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="M366" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N366" t="s">
         <v>47</v>
@@ -22996,7 +22999,7 @@
         <v>156</v>
       </c>
       <c r="P366" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="Q366" t="s">
         <v>47</v>
@@ -23007,7 +23010,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B367" t="s">
         <v>34</v>
@@ -23019,7 +23022,7 @@
         <v>34</v>
       </c>
       <c r="E367" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="F367" t="s">
         <v>173</v>
@@ -23028,22 +23031,22 @@
         <v>41</v>
       </c>
       <c r="H367" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="I367" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="J367" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="K367" t="s">
         <v>57</v>
       </c>
       <c r="L367" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="M367" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N367" t="s">
         <v>47</v>
@@ -23052,7 +23055,7 @@
         <v>156</v>
       </c>
       <c r="P367" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="Q367" t="s">
         <v>47</v>
@@ -23063,7 +23066,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B368" t="s">
         <v>34</v>
@@ -23075,7 +23078,7 @@
         <v>34</v>
       </c>
       <c r="E368" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F368" t="s">
         <v>173</v>
@@ -23084,10 +23087,10 @@
         <v>41</v>
       </c>
       <c r="H368" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I368" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="J368" t="s">
         <v>247</v>
@@ -23096,10 +23099,10 @@
         <v>247</v>
       </c>
       <c r="L368" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="M368" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N368" t="s">
         <v>47</v>
@@ -23108,7 +23111,7 @@
         <v>156</v>
       </c>
       <c r="P368" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="Q368" t="s">
         <v>47</v>
@@ -23119,7 +23122,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B369" t="s">
         <v>34</v>
@@ -23131,7 +23134,7 @@
         <v>34</v>
       </c>
       <c r="E369" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F369" t="s">
         <v>173</v>
@@ -23140,10 +23143,10 @@
         <v>41</v>
       </c>
       <c r="H369" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I369" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J369" t="s">
         <v>247</v>
@@ -23152,10 +23155,10 @@
         <v>247</v>
       </c>
       <c r="L369" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="M369" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N369" t="s">
         <v>47</v>
@@ -23164,7 +23167,7 @@
         <v>156</v>
       </c>
       <c r="P369" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Q369" t="s">
         <v>47</v>
@@ -23175,7 +23178,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B370" t="s">
         <v>34</v>
@@ -23187,7 +23190,7 @@
         <v>34</v>
       </c>
       <c r="E370" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F370" t="s">
         <v>173</v>
@@ -23196,22 +23199,22 @@
         <v>41</v>
       </c>
       <c r="H370" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I370" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="J370" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K370" t="s">
         <v>86</v>
       </c>
       <c r="L370" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M370" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N370" t="s">
         <v>47</v>
@@ -23220,7 +23223,7 @@
         <v>156</v>
       </c>
       <c r="P370" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="Q370" t="s">
         <v>47</v>
@@ -23231,7 +23234,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B371" t="s">
         <v>34</v>
@@ -23243,7 +23246,7 @@
         <v>34</v>
       </c>
       <c r="E371" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F371" t="s">
         <v>173</v>
@@ -23252,22 +23255,22 @@
         <v>41</v>
       </c>
       <c r="H371" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I371" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J371" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K371" t="s">
         <v>86</v>
       </c>
       <c r="L371" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="M371" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N371" t="s">
         <v>47</v>
@@ -23276,7 +23279,7 @@
         <v>156</v>
       </c>
       <c r="P371" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="Q371" t="s">
         <v>47</v>
@@ -23287,13 +23290,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="1">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B372" t="s" s="1">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C372" t="s" s="1">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D372" t="s" s="1">
         <v>33</v>
@@ -23343,19 +23346,19 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
+        <v>860</v>
+      </c>
+      <c r="B373" t="s">
         <v>859</v>
       </c>
-      <c r="B373" t="s">
-        <v>858</v>
-      </c>
       <c r="C373" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D373" t="s">
         <v>33</v>
       </c>
       <c r="E373" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F373" t="s">
         <v>173</v>
@@ -23367,19 +23370,19 @@
         <v>470</v>
       </c>
       <c r="I373" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J373" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K373" t="s">
         <v>86</v>
       </c>
       <c r="L373" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M373" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N373" t="s">
         <v>47</v>
@@ -23388,7 +23391,7 @@
         <v>156</v>
       </c>
       <c r="P373" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Q373" t="s">
         <v>47</v>
@@ -23399,7 +23402,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B374" t="s">
         <v>34</v>
@@ -23411,7 +23414,7 @@
         <v>34</v>
       </c>
       <c r="E374" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F374" t="s">
         <v>199</v>
@@ -23420,10 +23423,10 @@
         <v>41</v>
       </c>
       <c r="H374" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="I374" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="J374" t="s">
         <v>61</v>
@@ -23432,10 +23435,10 @@
         <v>79</v>
       </c>
       <c r="L374" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M374" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N374" t="s">
         <v>47</v>
@@ -23444,7 +23447,7 @@
         <v>156</v>
       </c>
       <c r="P374" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="Q374" t="s">
         <v>47</v>
@@ -23455,13 +23458,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B375" t="s" s="1">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C375" t="s" s="1">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D375" t="s" s="1">
         <v>33</v>
@@ -23511,19 +23514,19 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B376" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C376" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D376" t="s">
         <v>33</v>
       </c>
       <c r="E376" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F376" t="s">
         <v>199</v>
@@ -23532,10 +23535,10 @@
         <v>41</v>
       </c>
       <c r="H376" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="I376" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J376" t="s">
         <v>61</v>
@@ -23547,7 +23550,7 @@
         <v>34</v>
       </c>
       <c r="M376" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="N376" t="s">
         <v>47</v>
@@ -23556,7 +23559,7 @@
         <v>156</v>
       </c>
       <c r="P376" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Q376" t="s">
         <v>47</v>
@@ -23567,13 +23570,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B377" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C377" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D377" t="s">
         <v>33</v>
@@ -23588,10 +23591,10 @@
         <v>41</v>
       </c>
       <c r="H377" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="I377" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="J377" t="s">
         <v>664</v>
@@ -23600,10 +23603,10 @@
         <v>86</v>
       </c>
       <c r="L377" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M377" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="N377" t="s">
         <v>47</v>
@@ -23612,7 +23615,7 @@
         <v>156</v>
       </c>
       <c r="P377" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="Q377" t="s">
         <v>47</v>
@@ -23623,13 +23626,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="1">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B378" t="s" s="1">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C378" t="s" s="1">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D378" t="s" s="1">
         <v>33</v>
@@ -23679,13 +23682,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B379" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C379" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D379" t="s">
         <v>33</v>
@@ -23700,10 +23703,10 @@
         <v>41</v>
       </c>
       <c r="H379" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="I379" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="J379" t="s">
         <v>176</v>
@@ -23712,10 +23715,10 @@
         <v>189</v>
       </c>
       <c r="L379" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="M379" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="N379" t="s">
         <v>47</v>
@@ -23724,7 +23727,7 @@
         <v>156</v>
       </c>
       <c r="P379" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="Q379" t="s">
         <v>47</v>
@@ -23735,19 +23738,19 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B380" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C380" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D380" t="s">
         <v>33</v>
       </c>
       <c r="E380" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F380" t="s">
         <v>199</v>
@@ -23756,10 +23759,10 @@
         <v>41</v>
       </c>
       <c r="H380" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="I380" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="J380" t="s">
         <v>56</v>
@@ -23768,10 +23771,10 @@
         <v>61</v>
       </c>
       <c r="L380" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M380" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="N380" t="s">
         <v>47</v>
@@ -23780,7 +23783,7 @@
         <v>156</v>
       </c>
       <c r="P380" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="Q380" t="s">
         <v>47</v>
@@ -23791,13 +23794,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B381" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C381" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D381" t="s">
         <v>33</v>
@@ -23812,10 +23815,10 @@
         <v>41</v>
       </c>
       <c r="H381" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="I381" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="J381" t="s">
         <v>664</v>
@@ -23824,10 +23827,10 @@
         <v>86</v>
       </c>
       <c r="L381" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="M381" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="N381" t="s">
         <v>47</v>
@@ -23836,7 +23839,7 @@
         <v>156</v>
       </c>
       <c r="P381" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="Q381" t="s">
         <v>47</v>
@@ -23847,7 +23850,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B382" t="s">
         <v>34</v>
@@ -23859,7 +23862,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F382" t="s">
         <v>173</v>
@@ -23868,10 +23871,10 @@
         <v>41</v>
       </c>
       <c r="H382" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I382" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="J382" t="s">
         <v>652</v>
@@ -23880,10 +23883,10 @@
         <v>51</v>
       </c>
       <c r="L382" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M382" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="N382" t="s">
         <v>47</v>
@@ -23892,7 +23895,7 @@
         <v>156</v>
       </c>
       <c r="P382" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="Q382" t="s">
         <v>47</v>
@@ -23903,13 +23906,13 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B383" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C383" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D383" t="s">
         <v>33</v>
@@ -23924,22 +23927,22 @@
         <v>41</v>
       </c>
       <c r="H383" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="I383" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="J383" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K383" t="s">
         <v>86</v>
       </c>
       <c r="L383" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M383" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="N383" t="s">
         <v>47</v>
@@ -23948,7 +23951,7 @@
         <v>156</v>
       </c>
       <c r="P383" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="Q383" t="s">
         <v>47</v>
@@ -23959,13 +23962,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="1">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B384" t="s" s="1">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C384" t="s" s="1">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D384" t="s" s="1">
         <v>33</v>
@@ -24015,13 +24018,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="1">
+        <v>908</v>
+      </c>
+      <c r="B385" t="s" s="1">
         <v>907</v>
       </c>
-      <c r="B385" t="s" s="1">
-        <v>906</v>
-      </c>
       <c r="C385" t="s" s="1">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D385" t="s" s="1">
         <v>33</v>
@@ -24071,13 +24074,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B386" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C386" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D386" t="s">
         <v>33</v>
@@ -24092,22 +24095,22 @@
         <v>41</v>
       </c>
       <c r="H386" t="s">
+        <v>910</v>
+      </c>
+      <c r="I386" t="s">
+        <v>911</v>
+      </c>
+      <c r="J386" t="s">
+        <v>912</v>
+      </c>
+      <c r="K386" t="s">
+        <v>913</v>
+      </c>
+      <c r="L386" t="s">
+        <v>914</v>
+      </c>
+      <c r="M386" t="s">
         <v>909</v>
-      </c>
-      <c r="I386" t="s">
-        <v>910</v>
-      </c>
-      <c r="J386" t="s">
-        <v>911</v>
-      </c>
-      <c r="K386" t="s">
-        <v>912</v>
-      </c>
-      <c r="L386" t="s">
-        <v>913</v>
-      </c>
-      <c r="M386" t="s">
-        <v>908</v>
       </c>
       <c r="N386" t="s">
         <v>47</v>
@@ -24116,7 +24119,7 @@
         <v>156</v>
       </c>
       <c r="P386" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="Q386" t="s">
         <v>47</v>
@@ -24127,13 +24130,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="1">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B387" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C387" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D387" t="s" s="1">
         <v>33</v>
@@ -24183,13 +24186,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="1">
+        <v>917</v>
+      </c>
+      <c r="B388" t="s" s="1">
         <v>916</v>
       </c>
-      <c r="B388" t="s" s="1">
-        <v>915</v>
-      </c>
       <c r="C388" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D388" t="s" s="1">
         <v>33</v>
@@ -24239,13 +24242,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="1">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B389" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C389" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D389" t="s" s="1">
         <v>33</v>
@@ -24295,19 +24298,19 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B390" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C390" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D390" t="s">
         <v>33</v>
       </c>
       <c r="E390" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F390" t="s">
         <v>199</v>
@@ -24316,10 +24319,10 @@
         <v>41</v>
       </c>
       <c r="H390" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="I390" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="J390" t="s">
         <v>275</v>
@@ -24331,7 +24334,7 @@
         <v>34</v>
       </c>
       <c r="M390" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="N390" t="s">
         <v>47</v>
@@ -24340,7 +24343,7 @@
         <v>156</v>
       </c>
       <c r="P390" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="Q390" t="s">
         <v>47</v>
@@ -24351,13 +24354,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="1">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B391" t="s" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C391" t="s" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D391" t="s" s="1">
         <v>33</v>
@@ -24407,13 +24410,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="1">
+        <v>925</v>
+      </c>
+      <c r="B392" t="s" s="1">
         <v>924</v>
       </c>
-      <c r="B392" t="s" s="1">
-        <v>923</v>
-      </c>
       <c r="C392" t="s" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D392" t="s" s="1">
         <v>33</v>
@@ -24463,13 +24466,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="1">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B393" t="s" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C393" t="s" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D393" t="s" s="1">
         <v>33</v>
@@ -24519,13 +24522,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B394" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C394" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D394" t="s">
         <v>33</v>
@@ -24540,10 +24543,10 @@
         <v>41</v>
       </c>
       <c r="H394" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I394" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="J394" t="s">
         <v>113</v>
@@ -24552,10 +24555,10 @@
         <v>113</v>
       </c>
       <c r="L394" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M394" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N394" t="s">
         <v>47</v>
@@ -24564,7 +24567,7 @@
         <v>427</v>
       </c>
       <c r="P394" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="Q394" t="s">
         <v>47</v>
@@ -24575,7 +24578,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B395" t="s">
         <v>34</v>
@@ -24596,10 +24599,10 @@
         <v>41</v>
       </c>
       <c r="H395" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I395" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J395" t="s">
         <v>113</v>
@@ -24608,10 +24611,10 @@
         <v>113</v>
       </c>
       <c r="L395" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M395" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N395" t="s">
         <v>47</v>
@@ -24620,7 +24623,7 @@
         <v>490</v>
       </c>
       <c r="P395" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="Q395" t="s">
         <v>47</v>
@@ -24631,7 +24634,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B396" t="s">
         <v>34</v>
@@ -24652,10 +24655,10 @@
         <v>41</v>
       </c>
       <c r="H396" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I396" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="J396" t="s">
         <v>66</v>
@@ -24664,10 +24667,10 @@
         <v>66</v>
       </c>
       <c r="L396" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M396" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N396" t="s">
         <v>47</v>
@@ -24687,7 +24690,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B397" t="s">
         <v>34</v>
@@ -24708,10 +24711,10 @@
         <v>41</v>
       </c>
       <c r="H397" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I397" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="J397" t="s">
         <v>120</v>
@@ -24720,10 +24723,10 @@
         <v>120</v>
       </c>
       <c r="L397" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M397" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N397" t="s">
         <v>47</v>
@@ -24743,7 +24746,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B398" t="s">
         <v>34</v>
@@ -24764,10 +24767,10 @@
         <v>41</v>
       </c>
       <c r="H398" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I398" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="J398" t="s">
         <v>66</v>
@@ -24776,10 +24779,10 @@
         <v>66</v>
       </c>
       <c r="L398" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M398" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N398" t="s">
         <v>47</v>
@@ -24788,7 +24791,7 @@
         <v>389</v>
       </c>
       <c r="P398" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="Q398" t="s">
         <v>47</v>
@@ -24799,7 +24802,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B399" t="s">
         <v>34</v>
@@ -24820,10 +24823,10 @@
         <v>41</v>
       </c>
       <c r="H399" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I399" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="J399" t="s">
         <v>75</v>
@@ -24832,10 +24835,10 @@
         <v>75</v>
       </c>
       <c r="L399" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M399" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N399" t="s">
         <v>47</v>
@@ -24844,7 +24847,7 @@
         <v>76</v>
       </c>
       <c r="P399" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="Q399" t="s">
         <v>47</v>
@@ -24855,7 +24858,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B400" t="s">
         <v>34</v>
@@ -24876,10 +24879,10 @@
         <v>41</v>
       </c>
       <c r="H400" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I400" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="J400" t="s">
         <v>51</v>
@@ -24888,10 +24891,10 @@
         <v>51</v>
       </c>
       <c r="L400" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M400" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N400" t="s">
         <v>47</v>
@@ -24900,7 +24903,7 @@
         <v>143</v>
       </c>
       <c r="P400" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="Q400" t="s">
         <v>47</v>
@@ -24911,7 +24914,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B401" t="s">
         <v>34</v>
@@ -24932,22 +24935,22 @@
         <v>41</v>
       </c>
       <c r="H401" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I401" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="J401" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="K401" t="s">
         <v>45</v>
       </c>
       <c r="L401" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M401" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N401" t="s">
         <v>47</v>
@@ -24956,7 +24959,7 @@
         <v>358</v>
       </c>
       <c r="P401" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="Q401" t="s">
         <v>47</v>
@@ -24967,7 +24970,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B402" t="s">
         <v>34</v>
@@ -24988,10 +24991,10 @@
         <v>41</v>
       </c>
       <c r="H402" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I402" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J402" t="s">
         <v>86</v>
@@ -25000,10 +25003,10 @@
         <v>86</v>
       </c>
       <c r="L402" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M402" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N402" t="s">
         <v>47</v>
@@ -25012,7 +25015,7 @@
         <v>103</v>
       </c>
       <c r="P402" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="Q402" t="s">
         <v>47</v>
@@ -25023,7 +25026,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B403" t="s">
         <v>34</v>
@@ -25044,10 +25047,10 @@
         <v>41</v>
       </c>
       <c r="H403" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I403" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="J403" t="s">
         <v>62</v>
@@ -25056,10 +25059,10 @@
         <v>62</v>
       </c>
       <c r="L403" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M403" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N403" t="s">
         <v>47</v>
@@ -25068,7 +25071,7 @@
         <v>456</v>
       </c>
       <c r="P403" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="Q403" t="s">
         <v>47</v>
@@ -25079,7 +25082,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B404" t="s">
         <v>34</v>
@@ -25100,10 +25103,10 @@
         <v>41</v>
       </c>
       <c r="H404" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I404" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="J404" t="s">
         <v>66</v>
@@ -25112,10 +25115,10 @@
         <v>66</v>
       </c>
       <c r="L404" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M404" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N404" t="s">
         <v>47</v>
@@ -25124,7 +25127,7 @@
         <v>353</v>
       </c>
       <c r="P404" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="Q404" t="s">
         <v>47</v>
@@ -25135,7 +25138,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B405" t="s">
         <v>34</v>
@@ -25156,10 +25159,10 @@
         <v>41</v>
       </c>
       <c r="H405" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I405" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="J405" t="s">
         <v>70</v>
@@ -25168,10 +25171,10 @@
         <v>70</v>
       </c>
       <c r="L405" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M405" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N405" t="s">
         <v>47</v>
@@ -25180,7 +25183,7 @@
         <v>106</v>
       </c>
       <c r="P405" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="Q405" t="s">
         <v>47</v>
@@ -25191,7 +25194,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B406" t="s">
         <v>34</v>
@@ -25212,10 +25215,10 @@
         <v>41</v>
       </c>
       <c r="H406" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I406" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="J406" t="s">
         <v>62</v>
@@ -25224,10 +25227,10 @@
         <v>62</v>
       </c>
       <c r="L406" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M406" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N406" t="s">
         <v>47</v>
@@ -25236,7 +25239,7 @@
         <v>453</v>
       </c>
       <c r="P406" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="Q406" t="s">
         <v>47</v>
@@ -25247,7 +25250,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B407" t="s">
         <v>34</v>
@@ -25268,10 +25271,10 @@
         <v>41</v>
       </c>
       <c r="H407" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I407" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J407" t="s">
         <v>52</v>
@@ -25280,10 +25283,10 @@
         <v>52</v>
       </c>
       <c r="L407" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M407" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N407" t="s">
         <v>47</v>
@@ -25292,7 +25295,7 @@
         <v>239</v>
       </c>
       <c r="P407" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="Q407" t="s">
         <v>47</v>
@@ -25303,7 +25306,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B408" t="s">
         <v>34</v>
@@ -25324,10 +25327,10 @@
         <v>41</v>
       </c>
       <c r="H408" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I408" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J408" t="s">
         <v>57</v>
@@ -25336,19 +25339,19 @@
         <v>57</v>
       </c>
       <c r="L408" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M408" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N408" t="s">
         <v>47</v>
       </c>
       <c r="O408" t="s">
+        <v>947</v>
+      </c>
+      <c r="P408" t="s">
         <v>946</v>
-      </c>
-      <c r="P408" t="s">
-        <v>945</v>
       </c>
       <c r="Q408" t="s">
         <v>47</v>
@@ -25359,7 +25362,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="1">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B409" t="s" s="1">
         <v>32</v>
@@ -25415,7 +25418,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="1">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B410" t="s" s="1">
         <v>32</v>
@@ -25471,7 +25474,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B411" t="s">
         <v>32</v>
@@ -25527,7 +25530,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="1">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B412" t="s" s="1">
         <v>168</v>
@@ -25583,7 +25586,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B413" t="s">
         <v>168</v>
@@ -25639,13 +25642,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="1">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B414" t="s" s="1">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C414" t="s" s="1">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D414" t="s" s="1">
         <v>33</v>
@@ -25695,7 +25698,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B415" t="s" s="1">
         <v>192</v>
@@ -25751,7 +25754,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="1">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B416" t="s" s="1">
         <v>194</v>
@@ -25807,7 +25810,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B417" t="s">
         <v>194</v>
@@ -25863,7 +25866,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="1">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B418" t="s" s="1">
         <v>334</v>
@@ -25919,7 +25922,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B419" t="s">
         <v>334</v>
@@ -25975,13 +25978,13 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="1">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B420" t="s" s="1">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C420" t="s" s="1">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D420" t="s" s="1">
         <v>33</v>
@@ -26031,13 +26034,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="1">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B421" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C421" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D421" t="s" s="1">
         <v>33</v>
@@ -26087,7 +26090,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="1">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B422" t="s" s="1">
         <v>410</v>
@@ -26143,7 +26146,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="1">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B423" t="s" s="1">
         <v>412</v>
@@ -26199,7 +26202,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B424" t="s">
         <v>412</v>
@@ -26255,7 +26258,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="1">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B425" t="s" s="1">
         <v>569</v>
@@ -26311,7 +26314,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B426" t="s">
         <v>569</v>
@@ -26367,7 +26370,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="1">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B427" t="s" s="1">
         <v>574</v>
@@ -26423,7 +26426,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B428" t="s">
         <v>576</v>
@@ -26479,7 +26482,7 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B429" t="s">
         <v>617</v>
@@ -26535,7 +26538,7 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B430" t="s">
         <v>626</v>
@@ -26591,7 +26594,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B431" t="s">
         <v>633</v>
@@ -26647,7 +26650,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B432" t="s">
         <v>640</v>
@@ -26703,7 +26706,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B433" t="s">
         <v>648</v>
@@ -26759,7 +26762,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="1">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B434" t="s" s="1">
         <v>667</v>
@@ -26815,7 +26818,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="1">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B435" t="s" s="1">
         <v>669</v>
@@ -26871,7 +26874,7 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B436" t="s">
         <v>671</v>
@@ -26927,7 +26930,7 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B437" t="s">
         <v>676</v>
@@ -26983,13 +26986,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B438" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C438" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D438" t="s">
         <v>33</v>
@@ -27039,13 +27042,13 @@
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B439" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C439" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D439" t="s">
         <v>33</v>
@@ -27095,13 +27098,13 @@
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B440" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C440" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D440" t="s">
         <v>33</v>
@@ -27151,13 +27154,13 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="1">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B441" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C441" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D441" t="s" s="1">
         <v>33</v>
@@ -27207,13 +27210,13 @@
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B442" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C442" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D442" t="s">
         <v>33</v>
@@ -27263,13 +27266,13 @@
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B443" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C443" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D443" t="s">
         <v>33</v>
@@ -27319,13 +27322,13 @@
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B444" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C444" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D444" t="s">
         <v>33</v>
@@ -27375,13 +27378,13 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B445" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C445" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D445" t="s">
         <v>33</v>
@@ -27431,13 +27434,13 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B446" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C446" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D446" t="s">
         <v>33</v>
@@ -27487,13 +27490,13 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B447" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C447" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D447" t="s">
         <v>33</v>
@@ -27543,13 +27546,13 @@
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B448" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C448" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D448" t="s">
         <v>33</v>
@@ -27599,13 +27602,13 @@
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B449" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C449" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D449" t="s">
         <v>33</v>
@@ -27655,13 +27658,13 @@
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B450" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C450" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D450" t="s">
         <v>33</v>
@@ -27711,13 +27714,13 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B451" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C451" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D451" t="s">
         <v>33</v>
@@ -27767,13 +27770,13 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B452" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C452" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D452" t="s">
         <v>33</v>
@@ -27823,13 +27826,13 @@
     </row>
     <row r="453">
       <c r="A453" t="s" s="1">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B453" t="s" s="1">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C453" t="s" s="1">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D453" t="s" s="1">
         <v>33</v>
@@ -27879,13 +27882,13 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B454" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C454" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D454" t="s">
         <v>33</v>
@@ -27935,13 +27938,13 @@
     </row>
     <row r="455">
       <c r="A455" t="s" s="1">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B455" t="s" s="1">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C455" t="s" s="1">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D455" t="s" s="1">
         <v>33</v>
@@ -27991,13 +27994,13 @@
     </row>
     <row r="456">
       <c r="A456" t="s" s="1">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B456" t="s" s="1">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C456" t="s" s="1">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D456" t="s" s="1">
         <v>33</v>
@@ -28047,13 +28050,13 @@
     </row>
     <row r="457">
       <c r="A457" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B457" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C457" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D457" t="s" s="1">
         <v>33</v>
@@ -28103,13 +28106,13 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B458" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C458" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D458" t="s">
         <v>33</v>
@@ -28159,13 +28162,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B459" t="s" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C459" t="s" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D459" t="s" s="1">
         <v>33</v>
@@ -28215,13 +28218,13 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B460" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C460" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D460" t="s">
         <v>33</v>
@@ -28271,13 +28274,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="1">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B461" t="s" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C461" t="s" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D461" t="s" s="1">
         <v>33</v>
@@ -28327,13 +28330,13 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="1">
+        <v>1007</v>
+      </c>
+      <c r="B462" t="s" s="1">
         <v>1006</v>
       </c>
-      <c r="B462" t="s" s="1">
-        <v>1005</v>
-      </c>
       <c r="C462" t="s" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D462" t="s" s="1">
         <v>33</v>
@@ -28383,13 +28386,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B463" t="s" s="1">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C463" t="s" s="1">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D463" t="s" s="1">
         <v>33</v>
@@ -28439,7 +28442,7 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="1">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B464" t="s" s="1">
         <v>32</v>
@@ -28495,13 +28498,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B465" t="s" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C465" t="s" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D465" t="s" s="1">
         <v>33</v>
@@ -28551,7 +28554,7 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B466" t="s">
         <v>168</v>
@@ -28607,7 +28610,7 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B467" t="s">
         <v>192</v>
@@ -28663,7 +28666,7 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B468" t="s">
         <v>410</v>
@@ -28719,13 +28722,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B469" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C469" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D469" t="s">
         <v>33</v>
@@ -28775,13 +28778,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B470" t="s" s="1">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C470" t="s" s="1">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D470" t="s" s="1">
         <v>33</v>
@@ -28831,7 +28834,7 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B471" t="s">
         <v>667</v>
@@ -28887,13 +28890,13 @@
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B472" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C472" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D472" t="s">
         <v>33</v>
@@ -28943,7 +28946,7 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B473" t="s">
         <v>32</v>
@@ -28999,13 +29002,13 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B474" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C474" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D474" t="s">
         <v>33</v>
@@ -29055,13 +29058,13 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B475" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C475" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D475" t="s">
         <v>33</v>
@@ -29111,7 +29114,7 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B476" t="s">
         <v>194</v>
@@ -29167,7 +29170,7 @@
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B477" t="s">
         <v>412</v>
@@ -29223,7 +29226,7 @@
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B478" t="s">
         <v>669</v>
@@ -29279,13 +29282,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B479" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C479" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D479" t="s">
         <v>33</v>
@@ -29335,7 +29338,7 @@
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B480" t="s">
         <v>168</v>
@@ -29391,13 +29394,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B481" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C481" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D481" t="s">
         <v>33</v>
@@ -29447,13 +29450,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B482" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C482" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D482" t="s">
         <v>33</v>
@@ -29503,13 +29506,13 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="1">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B483" t="s" s="1">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C483" t="s" s="1">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D483" t="s" s="1">
         <v>33</v>
@@ -29559,16 +29562,16 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="1">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B484" t="s" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C484" t="s" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D484" t="s" s="1">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E484" t="s" s="1">
         <v>34</v>
@@ -29615,16 +29618,16 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="1">
+        <v>1037</v>
+      </c>
+      <c r="B485" t="s" s="1">
+        <v>1038</v>
+      </c>
+      <c r="C485" t="s" s="1">
+        <v>1038</v>
+      </c>
+      <c r="D485" t="s" s="1">
         <v>1036</v>
-      </c>
-      <c r="B485" t="s" s="1">
-        <v>1037</v>
-      </c>
-      <c r="C485" t="s" s="1">
-        <v>1037</v>
-      </c>
-      <c r="D485" t="s" s="1">
-        <v>1035</v>
       </c>
       <c r="E485" t="s" s="1">
         <v>34</v>
@@ -29671,16 +29674,16 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="1">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B486" t="s" s="1">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C486" t="s" s="1">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D486" t="s" s="1">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E486" t="s" s="1">
         <v>34</v>
@@ -29727,13 +29730,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B487" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C487" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D487" t="s">
         <v>33</v>
@@ -29783,19 +29786,19 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B488" t="s">
         <v>1042</v>
       </c>
-      <c r="B488" t="s">
-        <v>1041</v>
-      </c>
       <c r="C488" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D488" t="s">
         <v>33</v>
       </c>
       <c r="E488" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F488" t="s">
         <v>40</v>
@@ -29804,10 +29807,10 @@
         <v>41</v>
       </c>
       <c r="H488" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="I488" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="J488" t="s">
         <v>62</v>
@@ -29816,10 +29819,10 @@
         <v>100</v>
       </c>
       <c r="L488" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="M488" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="N488" t="s">
         <v>47</v>
@@ -29828,7 +29831,7 @@
         <v>156</v>
       </c>
       <c r="P488" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="Q488" t="s">
         <v>47</v>
@@ -29839,7 +29842,7 @@
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B489" t="s">
         <v>34</v>
@@ -29851,7 +29854,7 @@
         <v>34</v>
       </c>
       <c r="E489" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F489" t="s">
         <v>40</v>
@@ -29863,7 +29866,7 @@
         <v>158</v>
       </c>
       <c r="I489" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="J489" t="s">
         <v>330</v>
@@ -29872,10 +29875,10 @@
         <v>120</v>
       </c>
       <c r="L489" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="M489" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="N489" t="s">
         <v>47</v>
@@ -29884,7 +29887,7 @@
         <v>156</v>
       </c>
       <c r="P489" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="Q489" t="s">
         <v>47</v>
@@ -29895,7 +29898,7 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B490" t="s">
         <v>34</v>
@@ -29907,7 +29910,7 @@
         <v>34</v>
       </c>
       <c r="E490" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F490" t="s">
         <v>40</v>
@@ -29916,7 +29919,7 @@
         <v>41</v>
       </c>
       <c r="H490" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="I490" t="s">
         <v>102</v>
@@ -29928,10 +29931,10 @@
         <v>56</v>
       </c>
       <c r="L490" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="M490" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="N490" t="s">
         <v>47</v>

--- a/xlsx/dre/DRE_05_2026.xlsx
+++ b/xlsx/dre/DRE_05_2026.xlsx
@@ -795,40 +795,81 @@
     <t>R$ 4.229,40</t>
   </si>
   <si>
-    <t>674/1</t>
+    <t>73/5</t>
+  </si>
+  <si>
+    <t>PFP</t>
+  </si>
+  <si>
+    <t>MP  MARKFERRAGENS</t>
+  </si>
+  <si>
+    <t>R$  100,31</t>
+  </si>
+  <si>
+    <t>18/09/26</t>
+  </si>
+  <si>
+    <t>Forest</t>
+  </si>
+  <si>
+    <t>Usinagem CNC</t>
+  </si>
+  <si>
+    <t>686/1</t>
+  </si>
+  <si>
+    <t>FERRAGENS FLORESTA EIRELI EPP</t>
+  </si>
+  <si>
+    <t>R$  280,54</t>
+  </si>
+  <si>
+    <t>29/06/26</t>
+  </si>
+  <si>
+    <t>30/05/26</t>
+  </si>
+  <si>
+    <t>Perlare</t>
+  </si>
+  <si>
+    <t>R$  324,53</t>
+  </si>
+  <si>
+    <t>678/1</t>
+  </si>
+  <si>
+    <t>Ecsul</t>
+  </si>
+  <si>
+    <t>R$  221,20</t>
+  </si>
+  <si>
+    <t>05/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fitas de Led e conectores para cliente montagem do Eraldo
+</t>
+  </si>
+  <si>
+    <t>73/4</t>
+  </si>
+  <si>
+    <t>677/1</t>
   </si>
   <si>
     <t>Leo Madeiras</t>
   </si>
   <si>
-    <t>R$  171,60</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>16/05/26</t>
-  </si>
-  <si>
-    <t>Forest</t>
-  </si>
-  <si>
-    <t>Usinagem CNC</t>
-  </si>
-  <si>
-    <t>73/6</t>
-  </si>
-  <si>
-    <t>MP  MARKFERRAGENS</t>
-  </si>
-  <si>
-    <t>R$  100,31</t>
-  </si>
-  <si>
-    <t>01/08/26</t>
-  </si>
-  <si>
-    <t>Suportes dos banheiros cliente Abrafoton</t>
+    <t>R$  113,98</t>
+  </si>
+  <si>
+    <t>14/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tupia laminadora estoque
+</t>
   </si>
   <si>
     <t>680/1</t>
@@ -838,19 +879,34 @@
   </si>
   <si>
     <t>R$  159,80</t>
-  </si>
-  <si>
-    <t>05/06/26</t>
   </si>
   <si>
     <t xml:space="preserve">fresa para tupia
 </t>
   </si>
   <si>
-    <t>Perlare</t>
-  </si>
-  <si>
-    <t>R$  324,53</t>
+    <t>674/1</t>
+  </si>
+  <si>
+    <t>R$  171,60</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>16/05/26</t>
+  </si>
+  <si>
+    <t>73/3</t>
+  </si>
+  <si>
+    <t>665/1</t>
+  </si>
+  <si>
+    <t>R$  255,24</t>
+  </si>
+  <si>
+    <t>09/06/26</t>
   </si>
   <si>
     <t>679/1</t>
@@ -866,28 +922,7 @@
 </t>
   </si>
   <si>
-    <t>73/4</t>
-  </si>
-  <si>
-    <t>PFP</t>
-  </si>
-  <si>
-    <t>18/09/26</t>
-  </si>
-  <si>
-    <t>686/1</t>
-  </si>
-  <si>
-    <t>FERRAGENS FLORESTA EIRELI EPP</t>
-  </si>
-  <si>
-    <t>R$  280,54</t>
-  </si>
-  <si>
-    <t>29/06/26</t>
-  </si>
-  <si>
-    <t>30/05/26</t>
+    <t>73/2</t>
   </si>
   <si>
     <t>9/5</t>
@@ -905,19 +940,53 @@
     <t>Grapa</t>
   </si>
   <si>
-    <t>73/3</t>
-  </si>
-  <si>
-    <t>73/2</t>
-  </si>
-  <si>
-    <t>665/1</t>
-  </si>
-  <si>
-    <t>R$  255,24</t>
-  </si>
-  <si>
-    <t>09/06/26</t>
+    <t>17/1</t>
+  </si>
+  <si>
+    <t>R$  58,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reembolso tapete cozinha MP
+</t>
+  </si>
+  <si>
+    <t>73/6</t>
+  </si>
+  <si>
+    <t>01/08/26</t>
+  </si>
+  <si>
+    <t>Suportes dos banheiros cliente Abrafoton</t>
+  </si>
+  <si>
+    <t>650/1</t>
+  </si>
+  <si>
+    <t>R$  305,48</t>
+  </si>
+  <si>
+    <t>estoque</t>
+  </si>
+  <si>
+    <t>666/1</t>
+  </si>
+  <si>
+    <t>R$  267,50</t>
+  </si>
+  <si>
+    <t>682/1</t>
+  </si>
+  <si>
+    <t>R$  168,33</t>
+  </si>
+  <si>
+    <t>19/06/26</t>
+  </si>
+  <si>
+    <t>73/1</t>
+  </si>
+  <si>
+    <t>635/1</t>
   </si>
   <si>
     <t>671/1</t>
@@ -928,71 +997,6 @@
   <si>
     <t xml:space="preserve">kit 4 luminárias de emergencia
 </t>
-  </si>
-  <si>
-    <t>666/1</t>
-  </si>
-  <si>
-    <t>R$  267,50</t>
-  </si>
-  <si>
-    <t>650/1</t>
-  </si>
-  <si>
-    <t>R$  305,48</t>
-  </si>
-  <si>
-    <t>estoque</t>
-  </si>
-  <si>
-    <t>681/1</t>
-  </si>
-  <si>
-    <t>R$  147,90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor	Fornecedor	Descrição
-29,9	Mercado livre	ganchos cliente angela
-118	Mercado Livre	Placas sinalizadoras
-</t>
-  </si>
-  <si>
-    <t>635/1</t>
-  </si>
-  <si>
-    <t>73/1</t>
-  </si>
-  <si>
-    <t>17/1</t>
-  </si>
-  <si>
-    <t>R$  58,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reembolso tapete cozinha MP
-</t>
-  </si>
-  <si>
-    <t>678/1</t>
-  </si>
-  <si>
-    <t>Ecsul</t>
-  </si>
-  <si>
-    <t>R$  221,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fitas de Led e conectores para cliente montagem do Eraldo
-</t>
-  </si>
-  <si>
-    <t>682/1</t>
-  </si>
-  <si>
-    <t>R$  168,33</t>
-  </si>
-  <si>
-    <t>19/06/26</t>
   </si>
   <si>
     <t>750/1</t>
@@ -1011,22 +1015,18 @@
 </t>
   </si>
   <si>
-    <t>677/1</t>
-  </si>
-  <si>
-    <t>R$  113,98</t>
-  </si>
-  <si>
-    <t>14/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tupia laminadora estoque
+    <t>681/1</t>
+  </si>
+  <si>
+    <t>R$  147,90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor	Fornecedor	Descrição
+29,9	Mercado livre	ganchos cliente angela
+118	Mercado Livre	Placas sinalizadoras
 </t>
   </si>
   <si>
-    <t>73/5</t>
-  </si>
-  <si>
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
@@ -1312,12 +1312,12 @@
     <t>79701SelmaMA</t>
   </si>
   <si>
+    <t>R$  28,23</t>
+  </si>
+  <si>
     <t>R$  539,27</t>
   </si>
   <si>
-    <t>R$  28,23</t>
-  </si>
-  <si>
     <t>4.03.01.02.02 Comissões vendas</t>
   </si>
   <si>
@@ -1588,18 +1588,33 @@
     <t>01/07/26</t>
   </si>
   <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  226,76</t>
+  </si>
+  <si>
+    <t>40901/1</t>
+  </si>
+  <si>
+    <t>R$  612,81</t>
+  </si>
+  <si>
+    <t>40901DOUGLASJOS</t>
+  </si>
+  <si>
+    <t>David Alves</t>
+  </si>
+  <si>
+    <t>R$  210,00</t>
+  </si>
+  <si>
+    <t>R$  378,22</t>
+  </si>
+  <si>
     <t>R$  738,38</t>
   </si>
   <si>
-    <t>R$  378,22</t>
-  </si>
-  <si>
-    <t>David Alves</t>
-  </si>
-  <si>
-    <t>R$  210,00</t>
-  </si>
-  <si>
     <t>adm/0</t>
   </si>
   <si>
@@ -1609,21 +1624,6 @@
     <t>R$  680,27</t>
   </si>
   <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  226,76</t>
-  </si>
-  <si>
-    <t>40901/1</t>
-  </si>
-  <si>
-    <t>R$  612,81</t>
-  </si>
-  <si>
-    <t>40901DOUGLASJOS</t>
-  </si>
-  <si>
     <t>R$  1.007,63</t>
   </si>
   <si>
@@ -1648,12 +1648,12 @@
     <t>DECORA INTERIORES LTDA</t>
   </si>
   <si>
+    <t>R$  437,64</t>
+  </si>
+  <si>
     <t>R$  75,71</t>
   </si>
   <si>
-    <t>R$  437,64</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1765,9 +1765,93 @@
     <t>Uber</t>
   </si>
   <si>
+    <t>R$  10,24</t>
+  </si>
+  <si>
     <t>R$  23,08</t>
   </si>
   <si>
+    <t>76901U/0</t>
+  </si>
+  <si>
+    <t>R$  22,50</t>
+  </si>
+  <si>
+    <t>R$  26,94</t>
+  </si>
+  <si>
+    <t>R$  50,44</t>
+  </si>
+  <si>
+    <t>ADM/0</t>
+  </si>
+  <si>
+    <t>R$  122,15</t>
+  </si>
+  <si>
+    <t>46201UB/0</t>
+  </si>
+  <si>
+    <t>R$  27,08</t>
+  </si>
+  <si>
+    <t>46201ANGELASC</t>
+  </si>
+  <si>
+    <t>29901/0</t>
+  </si>
+  <si>
+    <t>R$  64,87</t>
+  </si>
+  <si>
+    <t>29901FL8</t>
+  </si>
+  <si>
+    <t>30301/0</t>
+  </si>
+  <si>
+    <t>R$  14,43</t>
+  </si>
+  <si>
+    <t>30301GiseleO</t>
+  </si>
+  <si>
+    <t>40701U/0</t>
+  </si>
+  <si>
+    <t>R$  14,51</t>
+  </si>
+  <si>
+    <t>40701julianMac</t>
+  </si>
+  <si>
+    <t>48101/0</t>
+  </si>
+  <si>
+    <t>R$  55,10</t>
+  </si>
+  <si>
+    <t>48101AngelaFCJ</t>
+  </si>
+  <si>
+    <t>39801/0</t>
+  </si>
+  <si>
+    <t>R$  13,97</t>
+  </si>
+  <si>
+    <t>39801CleaRH</t>
+  </si>
+  <si>
+    <t>47101u/0</t>
+  </si>
+  <si>
+    <t>R$  12,93</t>
+  </si>
+  <si>
+    <t>47101MarciaOA</t>
+  </si>
+  <si>
     <t>29201/0</t>
   </si>
   <si>
@@ -1777,88 +1861,7 @@
     <t>29201LuizAMB</t>
   </si>
   <si>
-    <t>29901/0</t>
-  </si>
-  <si>
-    <t>R$  64,87</t>
-  </si>
-  <si>
-    <t>29901FL8</t>
-  </si>
-  <si>
     <t>R$  63,76</t>
-  </si>
-  <si>
-    <t>76901U/0</t>
-  </si>
-  <si>
-    <t>R$  22,50</t>
-  </si>
-  <si>
-    <t>30301/0</t>
-  </si>
-  <si>
-    <t>R$  14,43</t>
-  </si>
-  <si>
-    <t>30301GiseleO</t>
-  </si>
-  <si>
-    <t>40701U/0</t>
-  </si>
-  <si>
-    <t>R$  14,51</t>
-  </si>
-  <si>
-    <t>40701julianMac</t>
-  </si>
-  <si>
-    <t>48101/0</t>
-  </si>
-  <si>
-    <t>R$  55,10</t>
-  </si>
-  <si>
-    <t>48101AngelaFCJ</t>
-  </si>
-  <si>
-    <t>R$  26,94</t>
-  </si>
-  <si>
-    <t>39801/0</t>
-  </si>
-  <si>
-    <t>R$  13,97</t>
-  </si>
-  <si>
-    <t>39801CleaRH</t>
-  </si>
-  <si>
-    <t>R$  50,44</t>
-  </si>
-  <si>
-    <t>ADM/0</t>
-  </si>
-  <si>
-    <t>R$  122,15</t>
-  </si>
-  <si>
-    <t>46201UB/0</t>
-  </si>
-  <si>
-    <t>R$  27,08</t>
-  </si>
-  <si>
-    <t>46201ANGELASC</t>
-  </si>
-  <si>
-    <t>47101u/0</t>
-  </si>
-  <si>
-    <t>R$  12,93</t>
-  </si>
-  <si>
-    <t>47101MarciaOA</t>
   </si>
   <si>
     <t>676/1</t>
@@ -1874,9 +1877,6 @@
 </t>
   </si>
   <si>
-    <t>R$  10,24</t>
-  </si>
-  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -2076,34 +2076,82 @@
     <t>R$  54,24</t>
   </si>
   <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.645,57</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>19/05/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
     <t>12/02/26</t>
   </si>
   <si>
     <t>Fernanda Dochvat - Fixo 2026</t>
   </si>
   <si>
+    <t>R$  1.285,29</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
+    <t>660/1</t>
+  </si>
+  <si>
+    <t>adiantamento</t>
+  </si>
+  <si>
     <t>Rubens Felipe de Siqueira Costa</t>
   </si>
   <si>
     <t>Rubens - Pagamento 2026</t>
   </si>
   <si>
-    <t>R$  1.285,29</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.687,39</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
   </si>
   <si>
     <t>GUTEMBERG DIAS GOMES</t>
@@ -2113,54 +2161,6 @@
   </si>
   <si>
     <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>19/05/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.645,57</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>660/1</t>
-  </si>
-  <si>
-    <t>adiantamento</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.687,39</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -7177,22 +7177,22 @@
         <v>260</v>
       </c>
       <c r="F84" t="s">
-        <v>199</v>
+        <v>261</v>
       </c>
       <c r="G84" t="s">
         <v>41</v>
       </c>
       <c r="H84" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J84" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K84" t="s">
-        <v>264</v>
+        <v>57</v>
       </c>
       <c r="L84" t="s">
         <v>34</v>
@@ -7204,13 +7204,13 @@
         <v>47</v>
       </c>
       <c r="O84" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="P84" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="Q84" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R84" t="s">
         <v>34</v>
@@ -7289,7 +7289,7 @@
         <v>267</v>
       </c>
       <c r="F86" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G86" t="s">
         <v>41</v>
@@ -7304,10 +7304,10 @@
         <v>270</v>
       </c>
       <c r="K86" t="s">
-        <v>57</v>
+        <v>271</v>
       </c>
       <c r="L86" t="s">
-        <v>271</v>
+        <v>34</v>
       </c>
       <c r="M86" t="s">
         <v>258</v>
@@ -7316,7 +7316,7 @@
         <v>47</v>
       </c>
       <c r="O86" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="P86" t="s">
         <v>269</v>
@@ -7342,7 +7342,7 @@
         <v>34</v>
       </c>
       <c r="E87" t="s">
-        <v>272</v>
+        <v>213</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
@@ -7351,19 +7351,19 @@
         <v>41</v>
       </c>
       <c r="H87" t="s">
+        <v>272</v>
+      </c>
+      <c r="I87" t="s">
         <v>273</v>
       </c>
-      <c r="I87" t="s">
-        <v>274</v>
-      </c>
       <c r="J87" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="K87" t="s">
-        <v>86</v>
+        <v>247</v>
       </c>
       <c r="L87" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="M87" t="s">
         <v>258</v>
@@ -7372,10 +7372,10 @@
         <v>47</v>
       </c>
       <c r="O87" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="P87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q87" t="s">
         <v>47</v>
@@ -7398,7 +7398,7 @@
         <v>34</v>
       </c>
       <c r="E88" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="F88" t="s">
         <v>199</v>
@@ -7407,19 +7407,19 @@
         <v>41</v>
       </c>
       <c r="H88" t="s">
+        <v>275</v>
+      </c>
+      <c r="I88" t="s">
+        <v>276</v>
+      </c>
+      <c r="J88" t="s">
         <v>277</v>
       </c>
-      <c r="I88" t="s">
+      <c r="K88" t="s">
+        <v>45</v>
+      </c>
+      <c r="L88" t="s">
         <v>278</v>
-      </c>
-      <c r="J88" t="s">
-        <v>247</v>
-      </c>
-      <c r="K88" t="s">
-        <v>247</v>
-      </c>
-      <c r="L88" t="s">
-        <v>34</v>
       </c>
       <c r="M88" t="s">
         <v>258</v>
@@ -7428,10 +7428,10 @@
         <v>47</v>
       </c>
       <c r="O88" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Q88" t="s">
         <v>47</v>
@@ -7457,25 +7457,25 @@
         <v>279</v>
       </c>
       <c r="F89" t="s">
-        <v>199</v>
+        <v>261</v>
       </c>
       <c r="G89" t="s">
         <v>41</v>
       </c>
       <c r="H89" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="I89" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="J89" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="K89" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="L89" t="s">
-        <v>282</v>
+        <v>34</v>
       </c>
       <c r="M89" t="s">
         <v>258</v>
@@ -7484,13 +7484,13 @@
         <v>47</v>
       </c>
       <c r="O89" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="P89" t="s">
-        <v>281</v>
+        <v>34</v>
       </c>
       <c r="Q89" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R89" t="s">
         <v>34</v>
@@ -7510,28 +7510,28 @@
         <v>34</v>
       </c>
       <c r="E90" t="s">
+        <v>280</v>
+      </c>
+      <c r="F90" t="s">
+        <v>199</v>
+      </c>
+      <c r="G90" t="s">
+        <v>41</v>
+      </c>
+      <c r="H90" t="s">
+        <v>281</v>
+      </c>
+      <c r="I90" t="s">
+        <v>282</v>
+      </c>
+      <c r="J90" t="s">
+        <v>277</v>
+      </c>
+      <c r="K90" t="s">
         <v>283</v>
       </c>
-      <c r="F90" t="s">
+      <c r="L90" t="s">
         <v>284</v>
-      </c>
-      <c r="G90" t="s">
-        <v>41</v>
-      </c>
-      <c r="H90" t="s">
-        <v>268</v>
-      </c>
-      <c r="I90" t="s">
-        <v>269</v>
-      </c>
-      <c r="J90" t="s">
-        <v>285</v>
-      </c>
-      <c r="K90" t="s">
-        <v>57</v>
-      </c>
-      <c r="L90" t="s">
-        <v>34</v>
       </c>
       <c r="M90" t="s">
         <v>258</v>
@@ -7540,13 +7540,13 @@
         <v>47</v>
       </c>
       <c r="O90" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="P90" t="s">
-        <v>34</v>
+        <v>282</v>
       </c>
       <c r="Q90" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R90" t="s">
         <v>34</v>
@@ -7566,7 +7566,7 @@
         <v>34</v>
       </c>
       <c r="E91" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F91" t="s">
         <v>199</v>
@@ -7575,19 +7575,19 @@
         <v>41</v>
       </c>
       <c r="H91" t="s">
+        <v>286</v>
+      </c>
+      <c r="I91" t="s">
         <v>287</v>
       </c>
-      <c r="I91" t="s">
+      <c r="J91" t="s">
+        <v>277</v>
+      </c>
+      <c r="K91" t="s">
+        <v>86</v>
+      </c>
+      <c r="L91" t="s">
         <v>288</v>
-      </c>
-      <c r="J91" t="s">
-        <v>289</v>
-      </c>
-      <c r="K91" t="s">
-        <v>290</v>
-      </c>
-      <c r="L91" t="s">
-        <v>34</v>
       </c>
       <c r="M91" t="s">
         <v>258</v>
@@ -7599,7 +7599,7 @@
         <v>156</v>
       </c>
       <c r="P91" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q91" t="s">
         <v>47</v>
@@ -7622,28 +7622,28 @@
         <v>34</v>
       </c>
       <c r="E92" t="s">
+        <v>289</v>
+      </c>
+      <c r="F92" t="s">
+        <v>199</v>
+      </c>
+      <c r="G92" t="s">
+        <v>41</v>
+      </c>
+      <c r="H92" t="s">
+        <v>281</v>
+      </c>
+      <c r="I92" t="s">
+        <v>290</v>
+      </c>
+      <c r="J92" t="s">
         <v>291</v>
       </c>
-      <c r="F92" t="s">
-        <v>173</v>
-      </c>
-      <c r="G92" t="s">
-        <v>41</v>
-      </c>
-      <c r="H92" t="s">
+      <c r="K92" t="s">
         <v>292</v>
       </c>
-      <c r="I92" t="s">
-        <v>293</v>
-      </c>
-      <c r="J92" t="s">
-        <v>294</v>
-      </c>
-      <c r="K92" t="s">
-        <v>86</v>
-      </c>
       <c r="L92" t="s">
-        <v>295</v>
+        <v>34</v>
       </c>
       <c r="M92" t="s">
         <v>258</v>
@@ -7655,7 +7655,7 @@
         <v>156</v>
       </c>
       <c r="P92" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q92" t="s">
         <v>47</v>
@@ -7678,22 +7678,22 @@
         <v>34</v>
       </c>
       <c r="E93" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F93" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="G93" t="s">
         <v>41</v>
       </c>
       <c r="H93" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="I93" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J93" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="K93" t="s">
         <v>57</v>
@@ -7734,10 +7734,10 @@
         <v>34</v>
       </c>
       <c r="E94" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F94" t="s">
-        <v>284</v>
+        <v>199</v>
       </c>
       <c r="G94" t="s">
         <v>41</v>
@@ -7746,13 +7746,13 @@
         <v>268</v>
       </c>
       <c r="I94" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="J94" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="K94" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L94" t="s">
         <v>34</v>
@@ -7764,13 +7764,13 @@
         <v>47</v>
       </c>
       <c r="O94" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>34</v>
+        <v>295</v>
       </c>
       <c r="Q94" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R94" t="s">
         <v>34</v>
@@ -7790,7 +7790,7 @@
         <v>34</v>
       </c>
       <c r="E95" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F95" t="s">
         <v>199</v>
@@ -7799,19 +7799,19 @@
         <v>41</v>
       </c>
       <c r="H95" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="I95" t="s">
         <v>299</v>
       </c>
       <c r="J95" t="s">
+        <v>277</v>
+      </c>
+      <c r="K95" t="s">
+        <v>100</v>
+      </c>
+      <c r="L95" t="s">
         <v>300</v>
-      </c>
-      <c r="K95" t="s">
-        <v>44</v>
-      </c>
-      <c r="L95" t="s">
-        <v>34</v>
       </c>
       <c r="M95" t="s">
         <v>258</v>
@@ -7849,25 +7849,25 @@
         <v>301</v>
       </c>
       <c r="F96" t="s">
-        <v>199</v>
+        <v>261</v>
       </c>
       <c r="G96" t="s">
         <v>41</v>
       </c>
       <c r="H96" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="I96" t="s">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="J96" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="K96" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="L96" t="s">
-        <v>303</v>
+        <v>34</v>
       </c>
       <c r="M96" t="s">
         <v>258</v>
@@ -7876,13 +7876,13 @@
         <v>47</v>
       </c>
       <c r="O96" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="P96" t="s">
-        <v>302</v>
+        <v>34</v>
       </c>
       <c r="Q96" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R96" t="s">
         <v>34</v>
@@ -7902,28 +7902,28 @@
         <v>34</v>
       </c>
       <c r="E97" t="s">
+        <v>302</v>
+      </c>
+      <c r="F97" t="s">
+        <v>173</v>
+      </c>
+      <c r="G97" t="s">
+        <v>41</v>
+      </c>
+      <c r="H97" t="s">
+        <v>303</v>
+      </c>
+      <c r="I97" t="s">
         <v>304</v>
       </c>
-      <c r="F97" t="s">
-        <v>199</v>
-      </c>
-      <c r="G97" t="s">
-        <v>41</v>
-      </c>
-      <c r="H97" t="s">
-        <v>287</v>
-      </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>305</v>
       </c>
-      <c r="J97" t="s">
-        <v>275</v>
-      </c>
       <c r="K97" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="L97" t="s">
-        <v>34</v>
+        <v>306</v>
       </c>
       <c r="M97" t="s">
         <v>258</v>
@@ -7935,7 +7935,7 @@
         <v>156</v>
       </c>
       <c r="P97" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q97" t="s">
         <v>47</v>
@@ -7958,28 +7958,28 @@
         <v>34</v>
       </c>
       <c r="E98" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F98" t="s">
-        <v>199</v>
+        <v>40</v>
       </c>
       <c r="G98" t="s">
         <v>41</v>
       </c>
       <c r="H98" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
       <c r="I98" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J98" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L98" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M98" t="s">
         <v>258</v>
@@ -7991,7 +7991,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q98" t="s">
         <v>47</v>
@@ -8014,28 +8014,28 @@
         <v>34</v>
       </c>
       <c r="E99" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F99" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G99" t="s">
         <v>41</v>
       </c>
       <c r="H99" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="I99" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="J99" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="K99" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="L99" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M99" t="s">
         <v>258</v>
@@ -8044,10 +8044,10 @@
         <v>47</v>
       </c>
       <c r="O99" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="P99" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="Q99" t="s">
         <v>47</v>
@@ -8070,7 +8070,7 @@
         <v>34</v>
       </c>
       <c r="E100" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F100" t="s">
         <v>199</v>
@@ -8079,19 +8079,19 @@
         <v>41</v>
       </c>
       <c r="H100" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="I100" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="J100" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="K100" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="L100" t="s">
-        <v>34</v>
+        <v>315</v>
       </c>
       <c r="M100" t="s">
         <v>258</v>
@@ -8103,7 +8103,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="Q100" t="s">
         <v>47</v>
@@ -8126,10 +8126,10 @@
         <v>34</v>
       </c>
       <c r="E101" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F101" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G101" t="s">
         <v>41</v>
@@ -8138,16 +8138,16 @@
         <v>268</v>
       </c>
       <c r="I101" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
       <c r="J101" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K101" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="L101" t="s">
-        <v>271</v>
+        <v>34</v>
       </c>
       <c r="M101" t="s">
         <v>258</v>
@@ -8156,10 +8156,10 @@
         <v>47</v>
       </c>
       <c r="O101" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
       <c r="Q101" t="s">
         <v>47</v>
@@ -8182,28 +8182,28 @@
         <v>34</v>
       </c>
       <c r="E102" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F102" t="s">
-        <v>40</v>
+        <v>199</v>
       </c>
       <c r="G102" t="s">
         <v>41</v>
       </c>
       <c r="H102" t="s">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="I102" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J102" t="s">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="K102" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="L102" t="s">
-        <v>316</v>
+        <v>34</v>
       </c>
       <c r="M102" t="s">
         <v>258</v>
@@ -8215,7 +8215,7 @@
         <v>156</v>
       </c>
       <c r="P102" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q102" t="s">
         <v>47</v>
@@ -8238,28 +8238,28 @@
         <v>34</v>
       </c>
       <c r="E103" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F103" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G103" t="s">
         <v>41</v>
       </c>
       <c r="H103" t="s">
-        <v>318</v>
+        <v>262</v>
       </c>
       <c r="I103" t="s">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="J103" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="K103" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="L103" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="M103" t="s">
         <v>258</v>
@@ -8268,10 +8268,10 @@
         <v>47</v>
       </c>
       <c r="O103" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="P103" t="s">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="Q103" t="s">
         <v>47</v>
@@ -8294,7 +8294,7 @@
         <v>34</v>
       </c>
       <c r="E104" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F104" t="s">
         <v>199</v>
@@ -8303,16 +8303,16 @@
         <v>41</v>
       </c>
       <c r="H104" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="I104" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="J104" t="s">
-        <v>323</v>
+        <v>100</v>
       </c>
       <c r="K104" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="L104" t="s">
         <v>34</v>
@@ -8327,7 +8327,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="Q104" t="s">
         <v>47</v>
@@ -8350,7 +8350,7 @@
         <v>34</v>
       </c>
       <c r="E105" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F105" t="s">
         <v>199</v>
@@ -8359,19 +8359,19 @@
         <v>41</v>
       </c>
       <c r="H105" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="I105" t="s">
+        <v>324</v>
+      </c>
+      <c r="J105" t="s">
+        <v>277</v>
+      </c>
+      <c r="K105" t="s">
+        <v>126</v>
+      </c>
+      <c r="L105" t="s">
         <v>325</v>
-      </c>
-      <c r="J105" t="s">
-        <v>326</v>
-      </c>
-      <c r="K105" t="s">
-        <v>57</v>
-      </c>
-      <c r="L105" t="s">
-        <v>327</v>
       </c>
       <c r="M105" t="s">
         <v>258</v>
@@ -8380,10 +8380,10 @@
         <v>47</v>
       </c>
       <c r="O105" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="P105" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q105" t="s">
         <v>47</v>
@@ -8406,7 +8406,7 @@
         <v>34</v>
       </c>
       <c r="E106" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F106" t="s">
         <v>199</v>
@@ -8415,19 +8415,19 @@
         <v>41</v>
       </c>
       <c r="H106" t="s">
-        <v>261</v>
+        <v>303</v>
       </c>
       <c r="I106" t="s">
+        <v>327</v>
+      </c>
+      <c r="J106" t="s">
+        <v>328</v>
+      </c>
+      <c r="K106" t="s">
+        <v>57</v>
+      </c>
+      <c r="L106" t="s">
         <v>329</v>
-      </c>
-      <c r="J106" t="s">
-        <v>275</v>
-      </c>
-      <c r="K106" t="s">
-        <v>330</v>
-      </c>
-      <c r="L106" t="s">
-        <v>331</v>
       </c>
       <c r="M106" t="s">
         <v>258</v>
@@ -8436,10 +8436,10 @@
         <v>47</v>
       </c>
       <c r="O106" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="P106" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q106" t="s">
         <v>47</v>
@@ -8462,28 +8462,28 @@
         <v>34</v>
       </c>
       <c r="E107" t="s">
+        <v>330</v>
+      </c>
+      <c r="F107" t="s">
+        <v>199</v>
+      </c>
+      <c r="G107" t="s">
+        <v>41</v>
+      </c>
+      <c r="H107" t="s">
+        <v>303</v>
+      </c>
+      <c r="I107" t="s">
+        <v>331</v>
+      </c>
+      <c r="J107" t="s">
+        <v>277</v>
+      </c>
+      <c r="K107" t="s">
+        <v>45</v>
+      </c>
+      <c r="L107" t="s">
         <v>332</v>
-      </c>
-      <c r="F107" t="s">
-        <v>284</v>
-      </c>
-      <c r="G107" t="s">
-        <v>41</v>
-      </c>
-      <c r="H107" t="s">
-        <v>268</v>
-      </c>
-      <c r="I107" t="s">
-        <v>269</v>
-      </c>
-      <c r="J107" t="s">
-        <v>285</v>
-      </c>
-      <c r="K107" t="s">
-        <v>57</v>
-      </c>
-      <c r="L107" t="s">
-        <v>34</v>
       </c>
       <c r="M107" t="s">
         <v>258</v>
@@ -8492,13 +8492,13 @@
         <v>47</v>
       </c>
       <c r="O107" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>34</v>
+        <v>331</v>
       </c>
       <c r="Q107" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R107" t="s">
         <v>34</v>
@@ -11374,7 +11374,7 @@
         <v>34</v>
       </c>
       <c r="E159" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="F159" t="s">
         <v>203</v>
@@ -11404,7 +11404,7 @@
         <v>47</v>
       </c>
       <c r="O159" t="s">
-        <v>389</v>
+        <v>239</v>
       </c>
       <c r="P159" t="s">
         <v>428</v>
@@ -11430,7 +11430,7 @@
         <v>34</v>
       </c>
       <c r="E160" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="F160" t="s">
         <v>203</v>
@@ -11460,7 +11460,7 @@
         <v>47</v>
       </c>
       <c r="O160" t="s">
-        <v>239</v>
+        <v>389</v>
       </c>
       <c r="P160" t="s">
         <v>429</v>
@@ -12394,7 +12394,7 @@
         <v>448</v>
       </c>
       <c r="I177" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J177" t="s">
         <v>134</v>
@@ -12415,7 +12415,7 @@
         <v>389</v>
       </c>
       <c r="P177" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q177" t="s">
         <v>47</v>
@@ -15350,7 +15350,7 @@
         <v>34</v>
       </c>
       <c r="E230" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="F230" t="s">
         <v>203</v>
@@ -15359,16 +15359,16 @@
         <v>41</v>
       </c>
       <c r="H230" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="I230" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J230" t="s">
-        <v>519</v>
+        <v>134</v>
       </c>
       <c r="K230" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L230" t="s">
         <v>34</v>
@@ -15380,10 +15380,10 @@
         <v>47</v>
       </c>
       <c r="O230" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="P230" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q230" t="s">
         <v>47</v>
@@ -15406,7 +15406,7 @@
         <v>34</v>
       </c>
       <c r="E231" t="s">
-        <v>198</v>
+        <v>522</v>
       </c>
       <c r="F231" t="s">
         <v>203</v>
@@ -15415,16 +15415,16 @@
         <v>41</v>
       </c>
       <c r="H231" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="I231" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J231" t="s">
-        <v>519</v>
+        <v>134</v>
       </c>
       <c r="K231" t="s">
-        <v>70</v>
+        <v>247</v>
       </c>
       <c r="L231" t="s">
         <v>34</v>
@@ -15436,10 +15436,10 @@
         <v>47</v>
       </c>
       <c r="O231" t="s">
-        <v>106</v>
+        <v>524</v>
       </c>
       <c r="P231" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="Q231" t="s">
         <v>47</v>
@@ -15471,10 +15471,10 @@
         <v>41</v>
       </c>
       <c r="H232" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="I232" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J232" t="s">
         <v>134</v>
@@ -15495,7 +15495,7 @@
         <v>138</v>
       </c>
       <c r="P232" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="Q232" t="s">
         <v>47</v>
@@ -15518,25 +15518,25 @@
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>524</v>
+        <v>198</v>
       </c>
       <c r="F233" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
       </c>
       <c r="H233" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="I233" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J233" t="s">
-        <v>134</v>
+        <v>519</v>
       </c>
       <c r="K233" t="s">
-        <v>247</v>
+        <v>70</v>
       </c>
       <c r="L233" t="s">
         <v>34</v>
@@ -15548,10 +15548,10 @@
         <v>47</v>
       </c>
       <c r="O233" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="P233" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Q233" t="s">
         <v>47</v>
@@ -15574,7 +15574,7 @@
         <v>34</v>
       </c>
       <c r="E234" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="F234" t="s">
         <v>203</v>
@@ -15583,16 +15583,16 @@
         <v>41</v>
       </c>
       <c r="H234" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="I234" t="s">
         <v>528</v>
       </c>
       <c r="J234" t="s">
-        <v>134</v>
+        <v>519</v>
       </c>
       <c r="K234" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15604,7 +15604,7 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="P234" t="s">
         <v>528</v>
@@ -15633,16 +15633,16 @@
         <v>529</v>
       </c>
       <c r="F235" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G235" t="s">
         <v>41</v>
       </c>
       <c r="H235" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="I235" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J235" t="s">
         <v>134</v>
@@ -15660,10 +15660,10 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
+        <v>156</v>
+      </c>
+      <c r="P235" t="s">
         <v>531</v>
-      </c>
-      <c r="P235" t="s">
-        <v>530</v>
       </c>
       <c r="Q235" t="s">
         <v>47</v>
@@ -15910,7 +15910,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F240" t="s">
         <v>500</v>
@@ -15925,10 +15925,10 @@
         <v>540</v>
       </c>
       <c r="J240" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="K240" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15966,7 +15966,7 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="F241" t="s">
         <v>500</v>
@@ -15975,16 +15975,16 @@
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>539</v>
+        <v>436</v>
       </c>
       <c r="I241" t="s">
-        <v>541</v>
+        <v>428</v>
       </c>
       <c r="J241" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="K241" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -16022,7 +16022,7 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="F242" t="s">
         <v>500</v>
@@ -16031,16 +16031,16 @@
         <v>41</v>
       </c>
       <c r="H242" t="s">
-        <v>436</v>
+        <v>539</v>
       </c>
       <c r="I242" t="s">
-        <v>429</v>
+        <v>541</v>
       </c>
       <c r="J242" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="K242" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -17254,7 +17254,7 @@
         <v>33</v>
       </c>
       <c r="E264" t="s">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="F264" t="s">
         <v>199</v>
@@ -17269,10 +17269,10 @@
         <v>579</v>
       </c>
       <c r="J264" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="K264" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="L264" t="s">
         <v>34</v>
@@ -17284,7 +17284,7 @@
         <v>47</v>
       </c>
       <c r="O264" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="P264" t="s">
         <v>579</v>
@@ -17310,7 +17310,7 @@
         <v>34</v>
       </c>
       <c r="E265" t="s">
-        <v>580</v>
+        <v>81</v>
       </c>
       <c r="F265" t="s">
         <v>199</v>
@@ -17322,13 +17322,13 @@
         <v>578</v>
       </c>
       <c r="I265" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J265" t="s">
-        <v>275</v>
+        <v>57</v>
       </c>
       <c r="K265" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="L265" t="s">
         <v>34</v>
@@ -17340,10 +17340,10 @@
         <v>47</v>
       </c>
       <c r="O265" t="s">
-        <v>582</v>
+        <v>83</v>
       </c>
       <c r="P265" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q265" t="s">
         <v>47</v>
@@ -17366,7 +17366,7 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F266" t="s">
         <v>199</v>
@@ -17378,13 +17378,13 @@
         <v>578</v>
       </c>
       <c r="I266" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J266" t="s">
-        <v>275</v>
+        <v>86</v>
       </c>
       <c r="K266" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="L266" t="s">
         <v>34</v>
@@ -17396,10 +17396,10 @@
         <v>47</v>
       </c>
       <c r="O266" t="s">
-        <v>585</v>
+        <v>103</v>
       </c>
       <c r="P266" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Q266" t="s">
         <v>47</v>
@@ -17422,7 +17422,7 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>71</v>
+        <v>397</v>
       </c>
       <c r="F267" t="s">
         <v>199</v>
@@ -17434,13 +17434,13 @@
         <v>578</v>
       </c>
       <c r="I267" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="J267" t="s">
-        <v>518</v>
+        <v>66</v>
       </c>
       <c r="K267" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="L267" t="s">
         <v>34</v>
@@ -17452,10 +17452,10 @@
         <v>47</v>
       </c>
       <c r="O267" t="s">
-        <v>76</v>
+        <v>353</v>
       </c>
       <c r="P267" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="Q267" t="s">
         <v>47</v>
@@ -17478,7 +17478,7 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>587</v>
+        <v>135</v>
       </c>
       <c r="F268" t="s">
         <v>199</v>
@@ -17490,13 +17490,13 @@
         <v>578</v>
       </c>
       <c r="I268" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="J268" t="s">
-        <v>86</v>
+        <v>518</v>
       </c>
       <c r="K268" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="L268" t="s">
         <v>34</v>
@@ -17508,10 +17508,10 @@
         <v>47</v>
       </c>
       <c r="O268" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="P268" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="Q268" t="s">
         <v>47</v>
@@ -17534,7 +17534,7 @@
         <v>34</v>
       </c>
       <c r="E269" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F269" t="s">
         <v>199</v>
@@ -17546,10 +17546,10 @@
         <v>578</v>
       </c>
       <c r="I269" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="J269" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K269" t="s">
         <v>125</v>
@@ -17564,10 +17564,10 @@
         <v>47</v>
       </c>
       <c r="O269" t="s">
-        <v>591</v>
+        <v>156</v>
       </c>
       <c r="P269" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="Q269" t="s">
         <v>47</v>
@@ -17590,7 +17590,7 @@
         <v>34</v>
       </c>
       <c r="E270" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F270" t="s">
         <v>199</v>
@@ -17602,13 +17602,13 @@
         <v>578</v>
       </c>
       <c r="I270" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="J270" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K270" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L270" t="s">
         <v>34</v>
@@ -17620,10 +17620,10 @@
         <v>47</v>
       </c>
       <c r="O270" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="P270" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="Q270" t="s">
         <v>47</v>
@@ -17646,7 +17646,7 @@
         <v>34</v>
       </c>
       <c r="E271" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F271" t="s">
         <v>199</v>
@@ -17658,10 +17658,10 @@
         <v>578</v>
       </c>
       <c r="I271" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="J271" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K271" t="s">
         <v>125</v>
@@ -17676,10 +17676,10 @@
         <v>47</v>
       </c>
       <c r="O271" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="P271" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="Q271" t="s">
         <v>47</v>
@@ -17702,7 +17702,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>397</v>
+        <v>593</v>
       </c>
       <c r="F272" t="s">
         <v>199</v>
@@ -17714,13 +17714,13 @@
         <v>578</v>
       </c>
       <c r="I272" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="J272" t="s">
-        <v>66</v>
+        <v>277</v>
       </c>
       <c r="K272" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="L272" t="s">
         <v>34</v>
@@ -17732,10 +17732,10 @@
         <v>47</v>
       </c>
       <c r="O272" t="s">
-        <v>353</v>
+        <v>595</v>
       </c>
       <c r="P272" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="Q272" t="s">
         <v>47</v>
@@ -17758,7 +17758,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F273" t="s">
         <v>199</v>
@@ -17770,10 +17770,10 @@
         <v>578</v>
       </c>
       <c r="I273" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="J273" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K273" t="s">
         <v>125</v>
@@ -17788,10 +17788,10 @@
         <v>47</v>
       </c>
       <c r="O273" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="P273" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -17814,7 +17814,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>135</v>
+        <v>599</v>
       </c>
       <c r="F274" t="s">
         <v>199</v>
@@ -17826,13 +17826,13 @@
         <v>578</v>
       </c>
       <c r="I274" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J274" t="s">
-        <v>518</v>
+        <v>277</v>
       </c>
       <c r="K274" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="L274" t="s">
         <v>34</v>
@@ -17844,10 +17844,10 @@
         <v>47</v>
       </c>
       <c r="O274" t="s">
-        <v>138</v>
+        <v>601</v>
       </c>
       <c r="P274" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="Q274" t="s">
         <v>47</v>
@@ -17870,7 +17870,7 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F275" t="s">
         <v>199</v>
@@ -17882,10 +17882,10 @@
         <v>578</v>
       </c>
       <c r="I275" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J275" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K275" t="s">
         <v>125</v>
@@ -17900,10 +17900,10 @@
         <v>47</v>
       </c>
       <c r="O275" t="s">
-        <v>156</v>
+        <v>604</v>
       </c>
       <c r="P275" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q275" t="s">
         <v>47</v>
@@ -17941,10 +17941,10 @@
         <v>606</v>
       </c>
       <c r="J276" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K276" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L276" t="s">
         <v>34</v>
@@ -17997,7 +17997,7 @@
         <v>609</v>
       </c>
       <c r="J277" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K277" t="s">
         <v>125</v>
@@ -18038,7 +18038,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>611</v>
+        <v>71</v>
       </c>
       <c r="F278" t="s">
         <v>199</v>
@@ -18047,19 +18047,19 @@
         <v>41</v>
       </c>
       <c r="H278" t="s">
-        <v>612</v>
+        <v>578</v>
       </c>
       <c r="I278" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J278" t="s">
-        <v>275</v>
+        <v>518</v>
       </c>
       <c r="K278" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="L278" t="s">
-        <v>614</v>
+        <v>34</v>
       </c>
       <c r="M278" t="s">
         <v>577</v>
@@ -18068,10 +18068,10 @@
         <v>47</v>
       </c>
       <c r="O278" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="P278" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="Q278" t="s">
         <v>47</v>
@@ -18094,7 +18094,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>249</v>
+        <v>612</v>
       </c>
       <c r="F279" t="s">
         <v>199</v>
@@ -18103,19 +18103,19 @@
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="I279" t="s">
+        <v>614</v>
+      </c>
+      <c r="J279" t="s">
+        <v>277</v>
+      </c>
+      <c r="K279" t="s">
+        <v>126</v>
+      </c>
+      <c r="L279" t="s">
         <v>615</v>
-      </c>
-      <c r="J279" t="s">
-        <v>120</v>
-      </c>
-      <c r="K279" t="s">
-        <v>120</v>
-      </c>
-      <c r="L279" t="s">
-        <v>34</v>
       </c>
       <c r="M279" t="s">
         <v>577</v>
@@ -18124,10 +18124,10 @@
         <v>47</v>
       </c>
       <c r="O279" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="P279" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="Q279" t="s">
         <v>47</v>
@@ -18769,7 +18769,7 @@
         <v>211</v>
       </c>
       <c r="F291" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
@@ -18825,7 +18825,7 @@
         <v>499</v>
       </c>
       <c r="F292" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="G292" t="s">
         <v>41</v>
@@ -19061,7 +19061,7 @@
         <v>630</v>
       </c>
       <c r="J296" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K296" t="s">
         <v>126</v>
@@ -19285,10 +19285,10 @@
         <v>644</v>
       </c>
       <c r="J300" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="K300" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="L300" t="s">
         <v>34</v>
@@ -19341,10 +19341,10 @@
         <v>644</v>
       </c>
       <c r="J301" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="K301" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="L301" t="s">
         <v>34</v>
@@ -19397,10 +19397,10 @@
         <v>644</v>
       </c>
       <c r="J302" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="K302" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="L302" t="s">
         <v>34</v>
@@ -19565,7 +19565,7 @@
         <v>656</v>
       </c>
       <c r="J305" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="K305" t="s">
         <v>86</v>
@@ -19624,7 +19624,7 @@
         <v>182</v>
       </c>
       <c r="K306" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="L306" t="s">
         <v>661</v>
@@ -20110,7 +20110,7 @@
         <v>34</v>
       </c>
       <c r="E315" t="s">
-        <v>157</v>
+        <v>654</v>
       </c>
       <c r="F315" t="s">
         <v>173</v>
@@ -20119,19 +20119,19 @@
         <v>41</v>
       </c>
       <c r="H315" t="s">
-        <v>516</v>
+        <v>682</v>
       </c>
       <c r="I315" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="J315" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="K315" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L315" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M315" t="s">
         <v>679</v>
@@ -20143,7 +20143,7 @@
         <v>156</v>
       </c>
       <c r="P315" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="Q315" t="s">
         <v>47</v>
@@ -20175,19 +20175,19 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="I316" t="s">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="J316" t="s">
-        <v>294</v>
+        <v>664</v>
       </c>
       <c r="K316" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L316" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M316" t="s">
         <v>679</v>
@@ -20199,7 +20199,7 @@
         <v>156</v>
       </c>
       <c r="P316" t="s">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -20222,7 +20222,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>658</v>
+        <v>157</v>
       </c>
       <c r="F317" t="s">
         <v>173</v>
@@ -20231,19 +20231,19 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
-        <v>417</v>
+        <v>497</v>
       </c>
       <c r="I317" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="J317" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K317" t="s">
-        <v>86</v>
+        <v>690</v>
       </c>
       <c r="L317" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="M317" t="s">
         <v>679</v>
@@ -20255,7 +20255,7 @@
         <v>156</v>
       </c>
       <c r="P317" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -20287,10 +20287,10 @@
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="I318" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="J318" t="s">
         <v>664</v>
@@ -20299,7 +20299,7 @@
         <v>86</v>
       </c>
       <c r="L318" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="M318" t="s">
         <v>679</v>
@@ -20311,7 +20311,7 @@
         <v>156</v>
       </c>
       <c r="P318" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="Q318" t="s">
         <v>47</v>
@@ -20334,7 +20334,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>654</v>
+        <v>157</v>
       </c>
       <c r="F319" t="s">
         <v>173</v>
@@ -20343,19 +20343,19 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
-        <v>692</v>
+        <v>516</v>
       </c>
       <c r="I319" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="J319" t="s">
-        <v>664</v>
+        <v>694</v>
       </c>
       <c r="K319" t="s">
-        <v>86</v>
+        <v>247</v>
       </c>
       <c r="L319" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M319" t="s">
         <v>679</v>
@@ -20367,7 +20367,7 @@
         <v>156</v>
       </c>
       <c r="P319" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="Q319" t="s">
         <v>47</v>
@@ -20390,7 +20390,7 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F320" t="s">
         <v>173</v>
@@ -20399,19 +20399,19 @@
         <v>41</v>
       </c>
       <c r="H320" t="s">
-        <v>636</v>
+        <v>417</v>
       </c>
       <c r="I320" t="s">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="J320" t="s">
-        <v>664</v>
+        <v>697</v>
       </c>
       <c r="K320" t="s">
         <v>86</v>
       </c>
       <c r="L320" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="M320" t="s">
         <v>679</v>
@@ -20423,7 +20423,7 @@
         <v>156</v>
       </c>
       <c r="P320" t="s">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="Q320" t="s">
         <v>47</v>
@@ -20446,28 +20446,28 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>654</v>
+        <v>699</v>
       </c>
       <c r="F321" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G321" t="s">
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="I321" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
       <c r="J321" t="s">
-        <v>664</v>
+        <v>57</v>
       </c>
       <c r="K321" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L321" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="M321" t="s">
         <v>679</v>
@@ -20479,7 +20479,7 @@
         <v>156</v>
       </c>
       <c r="P321" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
       <c r="Q321" t="s">
         <v>47</v>
@@ -20502,7 +20502,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>157</v>
+        <v>654</v>
       </c>
       <c r="F322" t="s">
         <v>173</v>
@@ -20511,19 +20511,19 @@
         <v>41</v>
       </c>
       <c r="H322" t="s">
-        <v>497</v>
+        <v>701</v>
       </c>
       <c r="I322" t="s">
-        <v>698</v>
+        <v>673</v>
       </c>
       <c r="J322" t="s">
-        <v>699</v>
+        <v>305</v>
       </c>
       <c r="K322" t="s">
-        <v>700</v>
+        <v>247</v>
       </c>
       <c r="L322" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M322" t="s">
         <v>679</v>
@@ -20535,7 +20535,7 @@
         <v>156</v>
       </c>
       <c r="P322" t="s">
-        <v>698</v>
+        <v>673</v>
       </c>
       <c r="Q322" t="s">
         <v>47</v>
@@ -20558,7 +20558,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>654</v>
+        <v>157</v>
       </c>
       <c r="F323" t="s">
         <v>173</v>
@@ -20567,19 +20567,19 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
-        <v>702</v>
+        <v>470</v>
       </c>
       <c r="I323" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="J323" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
       <c r="K323" t="s">
         <v>86</v>
       </c>
       <c r="L323" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="M323" t="s">
         <v>679</v>
@@ -20591,7 +20591,7 @@
         <v>156</v>
       </c>
       <c r="P323" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="Q323" t="s">
         <v>47</v>
@@ -20614,28 +20614,28 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>705</v>
+        <v>654</v>
       </c>
       <c r="F324" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G324" t="s">
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>702</v>
+        <v>636</v>
       </c>
       <c r="I324" t="s">
         <v>673</v>
       </c>
       <c r="J324" t="s">
-        <v>57</v>
+        <v>664</v>
       </c>
       <c r="K324" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L324" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="M324" t="s">
         <v>679</v>
@@ -20670,7 +20670,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>157</v>
+        <v>654</v>
       </c>
       <c r="F325" t="s">
         <v>173</v>
@@ -20679,13 +20679,13 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
-        <v>470</v>
+        <v>705</v>
       </c>
       <c r="I325" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="J325" t="s">
-        <v>699</v>
+        <v>664</v>
       </c>
       <c r="K325" t="s">
         <v>86</v>
@@ -20703,7 +20703,7 @@
         <v>156</v>
       </c>
       <c r="P325" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="Q325" t="s">
         <v>47</v>
@@ -21177,7 +21177,7 @@
         <v>172</v>
       </c>
       <c r="F334" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="G334" t="s">
         <v>41</v>
@@ -22309,7 +22309,7 @@
         <v>793</v>
       </c>
       <c r="J354" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K354" t="s">
         <v>45</v>
@@ -22421,7 +22421,7 @@
         <v>801</v>
       </c>
       <c r="J356" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K356" t="s">
         <v>86</v>
@@ -22527,7 +22527,7 @@
         <v>41</v>
       </c>
       <c r="H358" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="I358" t="s">
         <v>807</v>
@@ -22925,7 +22925,7 @@
         <v>836</v>
       </c>
       <c r="J365" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="K365" t="s">
         <v>86</v>
@@ -22981,7 +22981,7 @@
         <v>838</v>
       </c>
       <c r="J366" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="K366" t="s">
         <v>62</v>
@@ -24325,7 +24325,7 @@
         <v>922</v>
       </c>
       <c r="J390" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K390" t="s">
         <v>126</v>
@@ -29869,7 +29869,7 @@
         <v>1049</v>
       </c>
       <c r="J489" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="K489" t="s">
         <v>120</v>

--- a/xlsx/dre/DRE_05_2026.xlsx
+++ b/xlsx/dre/DRE_05_2026.xlsx
@@ -474,6 +474,33 @@
     <t>R$ 1.846,76</t>
   </si>
   <si>
+    <t>INSS/0</t>
+  </si>
+  <si>
+    <t>INSS- Previdenciária</t>
+  </si>
+  <si>
+    <t>R$  1.191,99</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>1/4</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  476,46</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>IRRF/2</t>
   </si>
   <si>
@@ -481,33 +508,6 @@
   </si>
   <si>
     <t>R$  178,31</t>
-  </si>
-  <si>
-    <t>ADM</t>
-  </si>
-  <si>
-    <t>1/4</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  476,46</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
-  </si>
-  <si>
-    <t>INSS/0</t>
-  </si>
-  <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
-    <t>R$  1.191,99</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -1726,12 +1726,12 @@
     <t>DSR maio26/1</t>
   </si>
   <si>
+    <t>R$  480,34</t>
+  </si>
+  <si>
     <t>R$  1.008,15</t>
   </si>
   <si>
-    <t>R$  480,34</t>
-  </si>
-  <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
   </si>
   <si>
@@ -1765,21 +1765,75 @@
     <t>Uber</t>
   </si>
   <si>
-    <t>R$  10,24</t>
-  </si>
-  <si>
     <t>R$  23,08</t>
   </si>
   <si>
+    <t>29201/0</t>
+  </si>
+  <si>
+    <t>R$  13,43</t>
+  </si>
+  <si>
+    <t>29201LuizAMB</t>
+  </si>
+  <si>
+    <t>29901/0</t>
+  </si>
+  <si>
+    <t>R$  64,87</t>
+  </si>
+  <si>
+    <t>29901FL8</t>
+  </si>
+  <si>
+    <t>R$  63,76</t>
+  </si>
+  <si>
     <t>76901U/0</t>
   </si>
   <si>
     <t>R$  22,50</t>
   </si>
   <si>
+    <t>30301/0</t>
+  </si>
+  <si>
+    <t>R$  14,43</t>
+  </si>
+  <si>
+    <t>30301GiseleO</t>
+  </si>
+  <si>
+    <t>40701U/0</t>
+  </si>
+  <si>
+    <t>R$  14,51</t>
+  </si>
+  <si>
+    <t>40701julianMac</t>
+  </si>
+  <si>
+    <t>48101/0</t>
+  </si>
+  <si>
+    <t>R$  55,10</t>
+  </si>
+  <si>
+    <t>48101AngelaFCJ</t>
+  </si>
+  <si>
     <t>R$  26,94</t>
   </si>
   <si>
+    <t>39801/0</t>
+  </si>
+  <si>
+    <t>R$  13,97</t>
+  </si>
+  <si>
+    <t>39801CleaRH</t>
+  </si>
+  <si>
     <t>R$  50,44</t>
   </si>
   <si>
@@ -1798,51 +1852,6 @@
     <t>46201ANGELASC</t>
   </si>
   <si>
-    <t>29901/0</t>
-  </si>
-  <si>
-    <t>R$  64,87</t>
-  </si>
-  <si>
-    <t>29901FL8</t>
-  </si>
-  <si>
-    <t>30301/0</t>
-  </si>
-  <si>
-    <t>R$  14,43</t>
-  </si>
-  <si>
-    <t>30301GiseleO</t>
-  </si>
-  <si>
-    <t>40701U/0</t>
-  </si>
-  <si>
-    <t>R$  14,51</t>
-  </si>
-  <si>
-    <t>40701julianMac</t>
-  </si>
-  <si>
-    <t>48101/0</t>
-  </si>
-  <si>
-    <t>R$  55,10</t>
-  </si>
-  <si>
-    <t>48101AngelaFCJ</t>
-  </si>
-  <si>
-    <t>39801/0</t>
-  </si>
-  <si>
-    <t>R$  13,97</t>
-  </si>
-  <si>
-    <t>39801CleaRH</t>
-  </si>
-  <si>
     <t>47101u/0</t>
   </si>
   <si>
@@ -1850,18 +1859,6 @@
   </si>
   <si>
     <t>47101MarciaOA</t>
-  </si>
-  <si>
-    <t>29201/0</t>
-  </si>
-  <si>
-    <t>R$  13,43</t>
-  </si>
-  <si>
-    <t>29201LuizAMB</t>
-  </si>
-  <si>
-    <t>R$  63,76</t>
   </si>
   <si>
     <t>676/1</t>
@@ -1877,6 +1874,9 @@
 </t>
   </si>
   <si>
+    <t>R$  10,24</t>
+  </si>
+  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -1956,21 +1956,21 @@
     <t>4.03.03.08.01 Brindes para clientes (CV)</t>
   </si>
   <si>
+    <t>BRINDE CLIENTES/0</t>
+  </si>
+  <si>
+    <t>Licoretto Bebidas</t>
+  </si>
+  <si>
+    <t>R$  159,96</t>
+  </si>
+  <si>
+    <t>BRINDE CLIENTES 2/0</t>
+  </si>
+  <si>
     <t>BRINDE CLIENTES 3/0</t>
   </si>
   <si>
-    <t>Licoretto Bebidas</t>
-  </si>
-  <si>
-    <t>R$  159,96</t>
-  </si>
-  <si>
-    <t>BRINDE CLIENTES 2/0</t>
-  </si>
-  <si>
-    <t>BRINDE CLIENTES/0</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -2004,6 +2004,18 @@
     <t>Google 2026</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
     <t>1/3</t>
   </si>
   <si>
@@ -2016,18 +2028,6 @@
     <t>Facebook 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -2403,16 +2403,16 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
-    <t>668/1</t>
-  </si>
-  <si>
-    <t>Shopee</t>
-  </si>
-  <si>
-    <t>R$  177,42</t>
-  </si>
-  <si>
-    <t>Papel interfolhado, esfregão</t>
+    <t>672/1</t>
+  </si>
+  <si>
+    <t>Lojas Mel</t>
+  </si>
+  <si>
+    <t>R$  19,99</t>
+  </si>
+  <si>
+    <t>Material limpeza</t>
   </si>
   <si>
     <t>651/1</t>
@@ -2428,16 +2428,16 @@
 </t>
   </si>
   <si>
-    <t>672/1</t>
-  </si>
-  <si>
-    <t>Lojas Mel</t>
-  </si>
-  <si>
-    <t>R$  19,99</t>
-  </si>
-  <si>
-    <t>Material limpeza</t>
+    <t>668/1</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>R$  177,42</t>
+  </si>
+  <si>
+    <t>Papel interfolhado, esfregão</t>
   </si>
   <si>
     <t>634/1</t>
@@ -2536,6 +2536,12 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>D4 sign</t>
   </si>
   <si>
@@ -2545,10 +2551,13 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
+    <t>61/1</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  95,73</t>
   </si>
   <si>
     <t>64/12</t>
@@ -2594,15 +2603,6 @@
   </si>
   <si>
     <t>Promob 2026/2</t>
-  </si>
-  <si>
-    <t>61/1</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  95,73</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -16871,7 +16871,7 @@
         <v>41</v>
       </c>
       <c r="H257" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="I257" t="s">
         <v>566</v>
@@ -16927,7 +16927,7 @@
         <v>41</v>
       </c>
       <c r="H258" t="s">
-        <v>493</v>
+        <v>417</v>
       </c>
       <c r="I258" t="s">
         <v>567</v>
@@ -17254,7 +17254,7 @@
         <v>33</v>
       </c>
       <c r="E264" t="s">
-        <v>249</v>
+        <v>81</v>
       </c>
       <c r="F264" t="s">
         <v>199</v>
@@ -17269,10 +17269,10 @@
         <v>579</v>
       </c>
       <c r="J264" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="K264" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="L264" t="s">
         <v>34</v>
@@ -17284,7 +17284,7 @@
         <v>47</v>
       </c>
       <c r="O264" t="s">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="P264" t="s">
         <v>579</v>
@@ -17310,7 +17310,7 @@
         <v>34</v>
       </c>
       <c r="E265" t="s">
-        <v>81</v>
+        <v>580</v>
       </c>
       <c r="F265" t="s">
         <v>199</v>
@@ -17322,13 +17322,13 @@
         <v>578</v>
       </c>
       <c r="I265" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J265" t="s">
-        <v>57</v>
+        <v>277</v>
       </c>
       <c r="K265" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="L265" t="s">
         <v>34</v>
@@ -17340,10 +17340,10 @@
         <v>47</v>
       </c>
       <c r="O265" t="s">
-        <v>83</v>
+        <v>582</v>
       </c>
       <c r="P265" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Q265" t="s">
         <v>47</v>
@@ -17366,7 +17366,7 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F266" t="s">
         <v>199</v>
@@ -17378,13 +17378,13 @@
         <v>578</v>
       </c>
       <c r="I266" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J266" t="s">
-        <v>86</v>
+        <v>277</v>
       </c>
       <c r="K266" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="L266" t="s">
         <v>34</v>
@@ -17396,10 +17396,10 @@
         <v>47</v>
       </c>
       <c r="O266" t="s">
-        <v>103</v>
+        <v>585</v>
       </c>
       <c r="P266" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q266" t="s">
         <v>47</v>
@@ -17422,7 +17422,7 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>397</v>
+        <v>71</v>
       </c>
       <c r="F267" t="s">
         <v>199</v>
@@ -17434,13 +17434,13 @@
         <v>578</v>
       </c>
       <c r="I267" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J267" t="s">
-        <v>66</v>
+        <v>518</v>
       </c>
       <c r="K267" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L267" t="s">
         <v>34</v>
@@ -17452,10 +17452,10 @@
         <v>47</v>
       </c>
       <c r="O267" t="s">
-        <v>353</v>
+        <v>76</v>
       </c>
       <c r="P267" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="Q267" t="s">
         <v>47</v>
@@ -17478,7 +17478,7 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>135</v>
+        <v>587</v>
       </c>
       <c r="F268" t="s">
         <v>199</v>
@@ -17490,13 +17490,13 @@
         <v>578</v>
       </c>
       <c r="I268" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="J268" t="s">
-        <v>518</v>
+        <v>86</v>
       </c>
       <c r="K268" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="L268" t="s">
         <v>34</v>
@@ -17508,10 +17508,10 @@
         <v>47</v>
       </c>
       <c r="O268" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="P268" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="Q268" t="s">
         <v>47</v>
@@ -17534,7 +17534,7 @@
         <v>34</v>
       </c>
       <c r="E269" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F269" t="s">
         <v>199</v>
@@ -17546,7 +17546,7 @@
         <v>578</v>
       </c>
       <c r="I269" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="J269" t="s">
         <v>277</v>
@@ -17564,10 +17564,10 @@
         <v>47</v>
       </c>
       <c r="O269" t="s">
-        <v>156</v>
+        <v>591</v>
       </c>
       <c r="P269" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="Q269" t="s">
         <v>47</v>
@@ -17590,7 +17590,7 @@
         <v>34</v>
       </c>
       <c r="E270" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="F270" t="s">
         <v>199</v>
@@ -17602,13 +17602,13 @@
         <v>578</v>
       </c>
       <c r="I270" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="J270" t="s">
         <v>277</v>
       </c>
       <c r="K270" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L270" t="s">
         <v>34</v>
@@ -17620,10 +17620,10 @@
         <v>47</v>
       </c>
       <c r="O270" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="P270" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="Q270" t="s">
         <v>47</v>
@@ -17646,7 +17646,7 @@
         <v>34</v>
       </c>
       <c r="E271" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F271" t="s">
         <v>199</v>
@@ -17658,7 +17658,7 @@
         <v>578</v>
       </c>
       <c r="I271" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="J271" t="s">
         <v>277</v>
@@ -17676,10 +17676,10 @@
         <v>47</v>
       </c>
       <c r="O271" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="P271" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="Q271" t="s">
         <v>47</v>
@@ -17702,7 +17702,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>593</v>
+        <v>397</v>
       </c>
       <c r="F272" t="s">
         <v>199</v>
@@ -17714,13 +17714,13 @@
         <v>578</v>
       </c>
       <c r="I272" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="J272" t="s">
-        <v>277</v>
+        <v>66</v>
       </c>
       <c r="K272" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="L272" t="s">
         <v>34</v>
@@ -17732,10 +17732,10 @@
         <v>47</v>
       </c>
       <c r="O272" t="s">
-        <v>595</v>
+        <v>353</v>
       </c>
       <c r="P272" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="Q272" t="s">
         <v>47</v>
@@ -17758,7 +17758,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="F273" t="s">
         <v>199</v>
@@ -17770,7 +17770,7 @@
         <v>578</v>
       </c>
       <c r="I273" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="J273" t="s">
         <v>277</v>
@@ -17788,10 +17788,10 @@
         <v>47</v>
       </c>
       <c r="O273" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="P273" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -17814,7 +17814,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>599</v>
+        <v>135</v>
       </c>
       <c r="F274" t="s">
         <v>199</v>
@@ -17826,13 +17826,13 @@
         <v>578</v>
       </c>
       <c r="I274" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="J274" t="s">
-        <v>277</v>
+        <v>518</v>
       </c>
       <c r="K274" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="L274" t="s">
         <v>34</v>
@@ -17844,10 +17844,10 @@
         <v>47</v>
       </c>
       <c r="O274" t="s">
-        <v>601</v>
+        <v>138</v>
       </c>
       <c r="P274" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Q274" t="s">
         <v>47</v>
@@ -17870,7 +17870,7 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F275" t="s">
         <v>199</v>
@@ -17882,7 +17882,7 @@
         <v>578</v>
       </c>
       <c r="I275" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J275" t="s">
         <v>277</v>
@@ -17900,10 +17900,10 @@
         <v>47</v>
       </c>
       <c r="O275" t="s">
+        <v>156</v>
+      </c>
+      <c r="P275" t="s">
         <v>604</v>
-      </c>
-      <c r="P275" t="s">
-        <v>603</v>
       </c>
       <c r="Q275" t="s">
         <v>47</v>
@@ -17944,7 +17944,7 @@
         <v>277</v>
       </c>
       <c r="K276" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L276" t="s">
         <v>34</v>
@@ -18038,7 +18038,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>71</v>
+        <v>611</v>
       </c>
       <c r="F278" t="s">
         <v>199</v>
@@ -18047,19 +18047,19 @@
         <v>41</v>
       </c>
       <c r="H278" t="s">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="I278" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J278" t="s">
-        <v>518</v>
+        <v>277</v>
       </c>
       <c r="K278" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="L278" t="s">
-        <v>34</v>
+        <v>614</v>
       </c>
       <c r="M278" t="s">
         <v>577</v>
@@ -18068,10 +18068,10 @@
         <v>47</v>
       </c>
       <c r="O278" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="Q278" t="s">
         <v>47</v>
@@ -18094,7 +18094,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>612</v>
+        <v>249</v>
       </c>
       <c r="F279" t="s">
         <v>199</v>
@@ -18103,19 +18103,19 @@
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>613</v>
+        <v>578</v>
       </c>
       <c r="I279" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J279" t="s">
-        <v>277</v>
+        <v>120</v>
       </c>
       <c r="K279" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="L279" t="s">
-        <v>615</v>
+        <v>34</v>
       </c>
       <c r="M279" t="s">
         <v>577</v>
@@ -18124,10 +18124,10 @@
         <v>47</v>
       </c>
       <c r="O279" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="P279" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="Q279" t="s">
         <v>47</v>
@@ -18262,10 +18262,10 @@
         <v>33</v>
       </c>
       <c r="E282" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="F282" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
@@ -18292,7 +18292,7 @@
         <v>47</v>
       </c>
       <c r="O282" t="s">
-        <v>622</v>
+        <v>389</v>
       </c>
       <c r="P282" t="s">
         <v>621</v>
@@ -18374,7 +18374,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F284" t="s">
         <v>173</v>
@@ -18389,10 +18389,10 @@
         <v>621</v>
       </c>
       <c r="J284" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K284" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="L284" t="s">
         <v>34</v>
@@ -18404,7 +18404,7 @@
         <v>47</v>
       </c>
       <c r="O284" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="P284" t="s">
         <v>621</v>
@@ -18430,7 +18430,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="F285" t="s">
         <v>173</v>
@@ -18445,10 +18445,10 @@
         <v>621</v>
       </c>
       <c r="J285" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="K285" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18460,7 +18460,7 @@
         <v>47</v>
       </c>
       <c r="O285" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="P285" t="s">
         <v>621</v>
@@ -18486,10 +18486,10 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>228</v>
+        <v>101</v>
       </c>
       <c r="F286" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
@@ -18501,10 +18501,10 @@
         <v>621</v>
       </c>
       <c r="J286" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="K286" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -18516,7 +18516,7 @@
         <v>47</v>
       </c>
       <c r="O286" t="s">
-        <v>353</v>
+        <v>103</v>
       </c>
       <c r="P286" t="s">
         <v>621</v>
@@ -18542,7 +18542,7 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="F287" t="s">
         <v>173</v>
@@ -18572,7 +18572,7 @@
         <v>47</v>
       </c>
       <c r="O287" t="s">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="P287" t="s">
         <v>621</v>
@@ -18598,10 +18598,10 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="F288" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G288" t="s">
         <v>41</v>
@@ -18613,10 +18613,10 @@
         <v>621</v>
       </c>
       <c r="J288" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K288" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18628,7 +18628,7 @@
         <v>47</v>
       </c>
       <c r="O288" t="s">
-        <v>106</v>
+        <v>622</v>
       </c>
       <c r="P288" t="s">
         <v>621</v>
@@ -18654,7 +18654,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="F289" t="s">
         <v>173</v>
@@ -18669,10 +18669,10 @@
         <v>621</v>
       </c>
       <c r="J289" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="K289" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="L289" t="s">
         <v>34</v>
@@ -18684,7 +18684,7 @@
         <v>47</v>
       </c>
       <c r="O289" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="P289" t="s">
         <v>621</v>
@@ -18710,10 +18710,10 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="F290" t="s">
-        <v>199</v>
+        <v>261</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
@@ -18725,10 +18725,10 @@
         <v>621</v>
       </c>
       <c r="J290" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="K290" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="L290" t="s">
         <v>34</v>
@@ -18740,13 +18740,13 @@
         <v>47</v>
       </c>
       <c r="O290" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="P290" t="s">
-        <v>621</v>
+        <v>34</v>
       </c>
       <c r="Q290" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R290" t="s">
         <v>34</v>
@@ -18766,10 +18766,10 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="F291" t="s">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
@@ -18781,10 +18781,10 @@
         <v>621</v>
       </c>
       <c r="J291" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="K291" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="L291" t="s">
         <v>34</v>
@@ -18796,13 +18796,13 @@
         <v>47</v>
       </c>
       <c r="O291" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="P291" t="s">
-        <v>34</v>
+        <v>621</v>
       </c>
       <c r="Q291" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R291" t="s">
         <v>34</v>
@@ -18822,10 +18822,10 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>499</v>
+        <v>213</v>
       </c>
       <c r="F292" t="s">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="G292" t="s">
         <v>41</v>
@@ -18837,10 +18837,10 @@
         <v>621</v>
       </c>
       <c r="J292" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="K292" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="L292" t="s">
         <v>34</v>
@@ -18852,13 +18852,13 @@
         <v>47</v>
       </c>
       <c r="O292" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="P292" t="s">
-        <v>34</v>
+        <v>621</v>
       </c>
       <c r="Q292" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R292" t="s">
         <v>34</v>
@@ -18934,10 +18934,10 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>213</v>
+        <v>499</v>
       </c>
       <c r="F294" t="s">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="G294" t="s">
         <v>41</v>
@@ -18949,10 +18949,10 @@
         <v>621</v>
       </c>
       <c r="J294" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="K294" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="L294" t="s">
         <v>34</v>
@@ -18964,13 +18964,13 @@
         <v>47</v>
       </c>
       <c r="O294" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="P294" t="s">
-        <v>621</v>
+        <v>34</v>
       </c>
       <c r="Q294" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R294" t="s">
         <v>34</v>
@@ -19606,7 +19606,7 @@
         <v>34</v>
       </c>
       <c r="E306" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="F306" t="s">
         <v>173</v>
@@ -19615,16 +19615,16 @@
         <v>41</v>
       </c>
       <c r="H306" t="s">
+        <v>658</v>
+      </c>
+      <c r="I306" t="s">
         <v>659</v>
       </c>
-      <c r="I306" t="s">
+      <c r="J306" t="s">
         <v>660</v>
       </c>
-      <c r="J306" t="s">
-        <v>182</v>
-      </c>
       <c r="K306" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="L306" t="s">
         <v>661</v>
@@ -19639,7 +19639,7 @@
         <v>156</v>
       </c>
       <c r="P306" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="Q306" t="s">
         <v>47</v>
@@ -19662,7 +19662,7 @@
         <v>34</v>
       </c>
       <c r="E307" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="F307" t="s">
         <v>173</v>
@@ -19671,16 +19671,16 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I307" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="J307" t="s">
-        <v>664</v>
+        <v>182</v>
       </c>
       <c r="K307" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="L307" t="s">
         <v>665</v>
@@ -19695,7 +19695,7 @@
         <v>156</v>
       </c>
       <c r="P307" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Q307" t="s">
         <v>47</v>
@@ -19901,7 +19901,7 @@
         <v>673</v>
       </c>
       <c r="J311" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K311" t="s">
         <v>86</v>
@@ -20125,7 +20125,7 @@
         <v>683</v>
       </c>
       <c r="J315" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K315" t="s">
         <v>86</v>
@@ -20181,7 +20181,7 @@
         <v>686</v>
       </c>
       <c r="J316" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K316" t="s">
         <v>86</v>
@@ -20293,7 +20293,7 @@
         <v>683</v>
       </c>
       <c r="J318" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K318" t="s">
         <v>86</v>
@@ -20390,7 +20390,7 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="F320" t="s">
         <v>173</v>
@@ -20629,7 +20629,7 @@
         <v>673</v>
       </c>
       <c r="J324" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K324" t="s">
         <v>86</v>
@@ -20685,7 +20685,7 @@
         <v>706</v>
       </c>
       <c r="J325" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K325" t="s">
         <v>86</v>
@@ -20741,7 +20741,7 @@
         <v>709</v>
       </c>
       <c r="J326" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K326" t="s">
         <v>86</v>
@@ -20847,10 +20847,10 @@
         <v>41</v>
       </c>
       <c r="H328" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I328" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J328" t="s">
         <v>176</v>
@@ -20871,7 +20871,7 @@
         <v>156</v>
       </c>
       <c r="P328" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="Q328" t="s">
         <v>47</v>
@@ -20959,10 +20959,10 @@
         <v>41</v>
       </c>
       <c r="H330" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I330" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J330" t="s">
         <v>176</v>
@@ -20983,7 +20983,7 @@
         <v>156</v>
       </c>
       <c r="P330" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="Q330" t="s">
         <v>47</v>
@@ -21581,7 +21581,7 @@
         <v>747</v>
       </c>
       <c r="J341" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K341" t="s">
         <v>247</v>
@@ -21631,7 +21631,7 @@
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I342" t="s">
         <v>752</v>
@@ -21861,7 +21861,7 @@
         <v>765</v>
       </c>
       <c r="J346" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K346" t="s">
         <v>86</v>
@@ -22029,7 +22029,7 @@
         <v>777</v>
       </c>
       <c r="J349" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K349" t="s">
         <v>75</v>
@@ -22197,7 +22197,7 @@
         <v>786</v>
       </c>
       <c r="J352" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K352" t="s">
         <v>247</v>
@@ -22312,7 +22312,7 @@
         <v>277</v>
       </c>
       <c r="K354" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="L354" t="s">
         <v>794</v>
@@ -22424,7 +22424,7 @@
         <v>277</v>
       </c>
       <c r="K356" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="L356" t="s">
         <v>802</v>
@@ -22701,7 +22701,7 @@
         <v>819</v>
       </c>
       <c r="J361" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K361" t="s">
         <v>86</v>
@@ -22919,19 +22919,19 @@
         <v>41</v>
       </c>
       <c r="H365" t="s">
+        <v>829</v>
+      </c>
+      <c r="I365" t="s">
         <v>835</v>
-      </c>
-      <c r="I365" t="s">
-        <v>836</v>
       </c>
       <c r="J365" t="s">
         <v>305</v>
       </c>
       <c r="K365" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="L365" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="M365" t="s">
         <v>834</v>
@@ -22943,7 +22943,7 @@
         <v>156</v>
       </c>
       <c r="P365" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="Q365" t="s">
         <v>47</v>
@@ -22975,7 +22975,7 @@
         <v>41</v>
       </c>
       <c r="H366" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="I366" t="s">
         <v>838</v>
@@ -22984,7 +22984,7 @@
         <v>305</v>
       </c>
       <c r="K366" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="L366" t="s">
         <v>839</v>
@@ -23037,13 +23037,13 @@
         <v>842</v>
       </c>
       <c r="J367" t="s">
-        <v>843</v>
+        <v>808</v>
       </c>
       <c r="K367" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="L367" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="M367" t="s">
         <v>834</v>
@@ -23078,7 +23078,7 @@
         <v>34</v>
       </c>
       <c r="E368" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="F368" t="s">
         <v>173</v>
@@ -23087,16 +23087,16 @@
         <v>41</v>
       </c>
       <c r="H368" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="I368" t="s">
+        <v>845</v>
+      </c>
+      <c r="J368" t="s">
         <v>846</v>
       </c>
-      <c r="J368" t="s">
-        <v>247</v>
-      </c>
       <c r="K368" t="s">
-        <v>247</v>
+        <v>57</v>
       </c>
       <c r="L368" t="s">
         <v>847</v>
@@ -23111,7 +23111,7 @@
         <v>156</v>
       </c>
       <c r="P368" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="Q368" t="s">
         <v>47</v>
@@ -23205,13 +23205,13 @@
         <v>852</v>
       </c>
       <c r="J370" t="s">
+        <v>247</v>
+      </c>
+      <c r="K370" t="s">
+        <v>247</v>
+      </c>
+      <c r="L370" t="s">
         <v>853</v>
-      </c>
-      <c r="K370" t="s">
-        <v>86</v>
-      </c>
-      <c r="L370" t="s">
-        <v>854</v>
       </c>
       <c r="M370" t="s">
         <v>834</v>
@@ -23246,7 +23246,7 @@
         <v>34</v>
       </c>
       <c r="E371" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F371" t="s">
         <v>173</v>
@@ -23255,19 +23255,19 @@
         <v>41</v>
       </c>
       <c r="H371" t="s">
+        <v>829</v>
+      </c>
+      <c r="I371" t="s">
+        <v>855</v>
+      </c>
+      <c r="J371" t="s">
         <v>856</v>
-      </c>
-      <c r="I371" t="s">
-        <v>857</v>
-      </c>
-      <c r="J371" t="s">
-        <v>808</v>
       </c>
       <c r="K371" t="s">
         <v>86</v>
       </c>
       <c r="L371" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M371" t="s">
         <v>834</v>
@@ -23279,7 +23279,7 @@
         <v>156</v>
       </c>
       <c r="P371" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="Q371" t="s">
         <v>47</v>
@@ -23597,7 +23597,7 @@
         <v>878</v>
       </c>
       <c r="J377" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K377" t="s">
         <v>86</v>
@@ -23821,7 +23821,7 @@
         <v>896</v>
       </c>
       <c r="J381" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K381" t="s">
         <v>86</v>
@@ -23933,7 +23933,7 @@
         <v>904</v>
       </c>
       <c r="J383" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="K383" t="s">
         <v>86</v>
@@ -24086,7 +24086,7 @@
         <v>33</v>
       </c>
       <c r="E386" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="F386" t="s">
         <v>173</v>

--- a/xlsx/dre/DRE_05_2026.xlsx
+++ b/xlsx/dre/DRE_05_2026.xlsx
@@ -474,6 +474,33 @@
     <t>R$ 1.846,76</t>
   </si>
   <si>
+    <t>IRRF/2</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>R$  178,31</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>1/4</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  476,46</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>INSS/0</t>
   </si>
   <si>
@@ -483,33 +510,6 @@
     <t>R$  1.191,99</t>
   </si>
   <si>
-    <t>ADM</t>
-  </si>
-  <si>
-    <t>1/4</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  476,46</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
-  </si>
-  <si>
-    <t>IRRF/2</t>
-  </si>
-  <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>R$  178,31</t>
-  </si>
-  <si>
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
@@ -795,27 +795,86 @@
     <t>R$ 4.229,40</t>
   </si>
   <si>
-    <t>73/5</t>
+    <t>674/1</t>
+  </si>
+  <si>
+    <t>Leo Madeiras</t>
+  </si>
+  <si>
+    <t>R$  171,60</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>16/05/26</t>
+  </si>
+  <si>
+    <t>Forest</t>
+  </si>
+  <si>
+    <t>Usinagem CNC</t>
+  </si>
+  <si>
+    <t>73/6</t>
+  </si>
+  <si>
+    <t>MP  MARKFERRAGENS</t>
+  </si>
+  <si>
+    <t>R$  100,31</t>
+  </si>
+  <si>
+    <t>01/08/26</t>
+  </si>
+  <si>
+    <t>Suportes dos banheiros cliente Abrafoton</t>
+  </si>
+  <si>
+    <t>680/1</t>
+  </si>
+  <si>
+    <t>Magazine Stroebel</t>
+  </si>
+  <si>
+    <t>R$  159,80</t>
+  </si>
+  <si>
+    <t>05/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresa para tupia
+</t>
+  </si>
+  <si>
+    <t>Perlare</t>
+  </si>
+  <si>
+    <t>R$  324,53</t>
+  </si>
+  <si>
+    <t>679/1</t>
+  </si>
+  <si>
+    <t>Wat Fix</t>
+  </si>
+  <si>
+    <t>R$  5,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arruelas cliente angela
+</t>
+  </si>
+  <si>
+    <t>73/4</t>
   </si>
   <si>
     <t>PFP</t>
   </si>
   <si>
-    <t>MP  MARKFERRAGENS</t>
-  </si>
-  <si>
-    <t>R$  100,31</t>
-  </si>
-  <si>
     <t>18/09/26</t>
   </si>
   <si>
-    <t>Forest</t>
-  </si>
-  <si>
-    <t>Usinagem CNC</t>
-  </si>
-  <si>
     <t>686/1</t>
   </si>
   <si>
@@ -831,10 +890,87 @@
     <t>30/05/26</t>
   </si>
   <si>
-    <t>Perlare</t>
-  </si>
-  <si>
-    <t>R$  324,53</t>
+    <t>9/5</t>
+  </si>
+  <si>
+    <t>Mercado livre</t>
+  </si>
+  <si>
+    <t>R$  91,85</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>Grapa</t>
+  </si>
+  <si>
+    <t>73/3</t>
+  </si>
+  <si>
+    <t>73/2</t>
+  </si>
+  <si>
+    <t>665/1</t>
+  </si>
+  <si>
+    <t>R$  255,24</t>
+  </si>
+  <si>
+    <t>09/06/26</t>
+  </si>
+  <si>
+    <t>671/1</t>
+  </si>
+  <si>
+    <t>R$  57,94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kit 4 luminárias de emergencia
+</t>
+  </si>
+  <si>
+    <t>666/1</t>
+  </si>
+  <si>
+    <t>R$  267,50</t>
+  </si>
+  <si>
+    <t>650/1</t>
+  </si>
+  <si>
+    <t>R$  305,48</t>
+  </si>
+  <si>
+    <t>estoque</t>
+  </si>
+  <si>
+    <t>681/1</t>
+  </si>
+  <si>
+    <t>R$  147,90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor	Fornecedor	Descrição
+29,9	Mercado livre	ganchos cliente angela
+118	Mercado Livre	Placas sinalizadoras
+</t>
+  </si>
+  <si>
+    <t>635/1</t>
+  </si>
+  <si>
+    <t>73/1</t>
+  </si>
+  <si>
+    <t>17/1</t>
+  </si>
+  <si>
+    <t>R$  58,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reembolso tapete cozinha MP
+</t>
   </si>
   <si>
     <t>678/1</t>
@@ -844,136 +980,12 @@
   </si>
   <si>
     <t>R$  221,20</t>
-  </si>
-  <si>
-    <t>05/06/26</t>
   </si>
   <si>
     <t xml:space="preserve">fitas de Led e conectores para cliente montagem do Eraldo
 </t>
   </si>
   <si>
-    <t>73/4</t>
-  </si>
-  <si>
-    <t>677/1</t>
-  </si>
-  <si>
-    <t>Leo Madeiras</t>
-  </si>
-  <si>
-    <t>R$  113,98</t>
-  </si>
-  <si>
-    <t>14/05/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tupia laminadora estoque
-</t>
-  </si>
-  <si>
-    <t>680/1</t>
-  </si>
-  <si>
-    <t>Magazine Stroebel</t>
-  </si>
-  <si>
-    <t>R$  159,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresa para tupia
-</t>
-  </si>
-  <si>
-    <t>674/1</t>
-  </si>
-  <si>
-    <t>R$  171,60</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>16/05/26</t>
-  </si>
-  <si>
-    <t>73/3</t>
-  </si>
-  <si>
-    <t>665/1</t>
-  </si>
-  <si>
-    <t>R$  255,24</t>
-  </si>
-  <si>
-    <t>09/06/26</t>
-  </si>
-  <si>
-    <t>679/1</t>
-  </si>
-  <si>
-    <t>Wat Fix</t>
-  </si>
-  <si>
-    <t>R$  5,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arruelas cliente angela
-</t>
-  </si>
-  <si>
-    <t>73/2</t>
-  </si>
-  <si>
-    <t>9/5</t>
-  </si>
-  <si>
-    <t>Mercado livre</t>
-  </si>
-  <si>
-    <t>R$  91,85</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>Grapa</t>
-  </si>
-  <si>
-    <t>17/1</t>
-  </si>
-  <si>
-    <t>R$  58,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reembolso tapete cozinha MP
-</t>
-  </si>
-  <si>
-    <t>73/6</t>
-  </si>
-  <si>
-    <t>01/08/26</t>
-  </si>
-  <si>
-    <t>Suportes dos banheiros cliente Abrafoton</t>
-  </si>
-  <si>
-    <t>650/1</t>
-  </si>
-  <si>
-    <t>R$  305,48</t>
-  </si>
-  <si>
-    <t>estoque</t>
-  </si>
-  <si>
-    <t>666/1</t>
-  </si>
-  <si>
-    <t>R$  267,50</t>
-  </si>
-  <si>
     <t>682/1</t>
   </si>
   <si>
@@ -981,22 +993,6 @@
   </si>
   <si>
     <t>19/06/26</t>
-  </si>
-  <si>
-    <t>73/1</t>
-  </si>
-  <si>
-    <t>635/1</t>
-  </si>
-  <si>
-    <t>671/1</t>
-  </si>
-  <si>
-    <t>R$  57,94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kit 4 luminárias de emergencia
-</t>
   </si>
   <si>
     <t>750/1</t>
@@ -1015,18 +1011,22 @@
 </t>
   </si>
   <si>
-    <t>681/1</t>
-  </si>
-  <si>
-    <t>R$  147,90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor	Fornecedor	Descrição
-29,9	Mercado livre	ganchos cliente angela
-118	Mercado Livre	Placas sinalizadoras
+    <t>677/1</t>
+  </si>
+  <si>
+    <t>R$  113,98</t>
+  </si>
+  <si>
+    <t>14/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tupia laminadora estoque
 </t>
   </si>
   <si>
+    <t>73/5</t>
+  </si>
+  <si>
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
@@ -1312,12 +1312,12 @@
     <t>79701SelmaMA</t>
   </si>
   <si>
+    <t>R$  539,27</t>
+  </si>
+  <si>
     <t>R$  28,23</t>
   </si>
   <si>
-    <t>R$  539,27</t>
-  </si>
-  <si>
     <t>4.03.01.02.02 Comissões vendas</t>
   </si>
   <si>
@@ -1588,6 +1588,27 @@
     <t>01/07/26</t>
   </si>
   <si>
+    <t>R$  738,38</t>
+  </si>
+  <si>
+    <t>R$  378,22</t>
+  </si>
+  <si>
+    <t>David Alves</t>
+  </si>
+  <si>
+    <t>R$  210,00</t>
+  </si>
+  <si>
+    <t>adm/0</t>
+  </si>
+  <si>
+    <t>DAVID ALVES</t>
+  </si>
+  <si>
+    <t>R$  680,27</t>
+  </si>
+  <si>
     <t>RAYSSA BARBOSA SILVA</t>
   </si>
   <si>
@@ -1603,27 +1624,6 @@
     <t>40901DOUGLASJOS</t>
   </si>
   <si>
-    <t>David Alves</t>
-  </si>
-  <si>
-    <t>R$  210,00</t>
-  </si>
-  <si>
-    <t>R$  378,22</t>
-  </si>
-  <si>
-    <t>R$  738,38</t>
-  </si>
-  <si>
-    <t>adm/0</t>
-  </si>
-  <si>
-    <t>DAVID ALVES</t>
-  </si>
-  <si>
-    <t>R$  680,27</t>
-  </si>
-  <si>
     <t>R$  1.007,63</t>
   </si>
   <si>
@@ -1648,12 +1648,12 @@
     <t>DECORA INTERIORES LTDA</t>
   </si>
   <si>
+    <t>R$  75,71</t>
+  </si>
+  <si>
     <t>R$  437,64</t>
   </si>
   <si>
-    <t>R$  75,71</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1726,10 +1726,10 @@
     <t>DSR maio26/1</t>
   </si>
   <si>
+    <t>R$  1.008,15</t>
+  </si>
+  <si>
     <t>R$  480,34</t>
-  </si>
-  <si>
-    <t>R$  1.008,15</t>
   </si>
   <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
@@ -1956,21 +1956,21 @@
     <t>4.03.03.08.01 Brindes para clientes (CV)</t>
   </si>
   <si>
+    <t>BRINDE CLIENTES 3/0</t>
+  </si>
+  <si>
+    <t>Licoretto Bebidas</t>
+  </si>
+  <si>
+    <t>R$  159,96</t>
+  </si>
+  <si>
+    <t>BRINDE CLIENTES 2/0</t>
+  </si>
+  <si>
     <t>BRINDE CLIENTES/0</t>
   </si>
   <si>
-    <t>Licoretto Bebidas</t>
-  </si>
-  <si>
-    <t>R$  159,96</t>
-  </si>
-  <si>
-    <t>BRINDE CLIENTES 2/0</t>
-  </si>
-  <si>
-    <t>BRINDE CLIENTES 3/0</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -2004,6 +2004,18 @@
     <t>Google 2026</t>
   </si>
   <si>
+    <t>1/3</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>R$  3.750,00</t>
+  </si>
+  <si>
+    <t>Facebook 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -2016,18 +2028,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>1/3</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>R$  3.750,00</t>
-  </si>
-  <si>
-    <t>Facebook 2026</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -2076,15 +2076,66 @@
     <t>R$  54,24</t>
   </si>
   <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  1.285,29</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
     <t>CARINA PEREIRA</t>
   </si>
   <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
     <t>Carina - Pagamento 2026</t>
   </si>
   <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>19/05/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
     <t>Denny Lucas do Carmo Pereira</t>
   </si>
   <si>
@@ -2094,57 +2145,15 @@
     <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>19/05/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  1.285,29</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
     <t>660/1</t>
   </si>
   <si>
     <t>adiantamento</t>
   </si>
   <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
     <t>Bianca Rodrigues - Salário fixo 2026</t>
   </si>
   <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
     <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
   </si>
   <si>
@@ -2154,15 +2163,6 @@
     <t>Sabrina Braunbeck - Pagamento 2026</t>
   </si>
   <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -2403,16 +2403,16 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
-    <t>672/1</t>
-  </si>
-  <si>
-    <t>Lojas Mel</t>
-  </si>
-  <si>
-    <t>R$  19,99</t>
-  </si>
-  <si>
-    <t>Material limpeza</t>
+    <t>668/1</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>R$  177,42</t>
+  </si>
+  <si>
+    <t>Papel interfolhado, esfregão</t>
   </si>
   <si>
     <t>651/1</t>
@@ -2428,16 +2428,16 @@
 </t>
   </si>
   <si>
-    <t>668/1</t>
-  </si>
-  <si>
-    <t>Shopee</t>
-  </si>
-  <si>
-    <t>R$  177,42</t>
-  </si>
-  <si>
-    <t>Papel interfolhado, esfregão</t>
+    <t>672/1</t>
+  </si>
+  <si>
+    <t>Lojas Mel</t>
+  </si>
+  <si>
+    <t>R$  19,99</t>
+  </si>
+  <si>
+    <t>Material limpeza</t>
   </si>
   <si>
     <t>634/1</t>
@@ -2536,19 +2536,64 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>R$  599,00</t>
   </si>
   <si>
     <t>Promob 2026</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
+    <t>64/12</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>22/06/26</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
+    <t>63/12</t>
+  </si>
+  <si>
+    <t>R$  376,44</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>62/12</t>
+  </si>
+  <si>
+    <t>R$  293,21</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
+    <t>3/4</t>
+  </si>
+  <si>
+    <t>R$  1.248,82</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
   </si>
   <si>
     <t>61/1</t>
@@ -2558,51 +2603,6 @@
   </si>
   <si>
     <t>R$  95,73</t>
-  </si>
-  <si>
-    <t>64/12</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>22/06/26</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>63/12</t>
-  </si>
-  <si>
-    <t>R$  376,44</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>62/12</t>
-  </si>
-  <si>
-    <t>R$  293,21</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>3/4</t>
-  </si>
-  <si>
-    <t>R$  1.248,82</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -7177,22 +7177,22 @@
         <v>260</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
+        <v>41</v>
+      </c>
+      <c r="H84" t="s">
         <v>261</v>
       </c>
-      <c r="G84" t="s">
-        <v>41</v>
-      </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>262</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>263</v>
       </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>264</v>
-      </c>
-      <c r="K84" t="s">
-        <v>57</v>
       </c>
       <c r="L84" t="s">
         <v>34</v>
@@ -7204,13 +7204,13 @@
         <v>47</v>
       </c>
       <c r="O84" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="P84" t="s">
-        <v>34</v>
+        <v>262</v>
       </c>
       <c r="Q84" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R84" t="s">
         <v>34</v>
@@ -7289,7 +7289,7 @@
         <v>267</v>
       </c>
       <c r="F86" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G86" t="s">
         <v>41</v>
@@ -7304,10 +7304,10 @@
         <v>270</v>
       </c>
       <c r="K86" t="s">
+        <v>57</v>
+      </c>
+      <c r="L86" t="s">
         <v>271</v>
-      </c>
-      <c r="L86" t="s">
-        <v>34</v>
       </c>
       <c r="M86" t="s">
         <v>258</v>
@@ -7316,7 +7316,7 @@
         <v>47</v>
       </c>
       <c r="O86" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="P86" t="s">
         <v>269</v>
@@ -7342,7 +7342,7 @@
         <v>34</v>
       </c>
       <c r="E87" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
@@ -7351,19 +7351,19 @@
         <v>41</v>
       </c>
       <c r="H87" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I87" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J87" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="K87" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L87" t="s">
-        <v>34</v>
+        <v>276</v>
       </c>
       <c r="M87" t="s">
         <v>258</v>
@@ -7372,10 +7372,10 @@
         <v>47</v>
       </c>
       <c r="O87" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="P87" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q87" t="s">
         <v>47</v>
@@ -7398,7 +7398,7 @@
         <v>34</v>
       </c>
       <c r="E88" t="s">
-        <v>274</v>
+        <v>213</v>
       </c>
       <c r="F88" t="s">
         <v>199</v>
@@ -7407,19 +7407,19 @@
         <v>41</v>
       </c>
       <c r="H88" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I88" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J88" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="K88" t="s">
-        <v>45</v>
+        <v>247</v>
       </c>
       <c r="L88" t="s">
-        <v>278</v>
+        <v>34</v>
       </c>
       <c r="M88" t="s">
         <v>258</v>
@@ -7428,10 +7428,10 @@
         <v>47</v>
       </c>
       <c r="O88" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="P88" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q88" t="s">
         <v>47</v>
@@ -7457,25 +7457,25 @@
         <v>279</v>
       </c>
       <c r="F89" t="s">
-        <v>261</v>
+        <v>199</v>
       </c>
       <c r="G89" t="s">
         <v>41</v>
       </c>
       <c r="H89" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="I89" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="J89" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="K89" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="L89" t="s">
-        <v>34</v>
+        <v>282</v>
       </c>
       <c r="M89" t="s">
         <v>258</v>
@@ -7484,13 +7484,13 @@
         <v>47</v>
       </c>
       <c r="O89" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="P89" t="s">
-        <v>34</v>
+        <v>281</v>
       </c>
       <c r="Q89" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R89" t="s">
         <v>34</v>
@@ -7510,28 +7510,28 @@
         <v>34</v>
       </c>
       <c r="E90" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F90" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="G90" t="s">
         <v>41</v>
       </c>
       <c r="H90" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="I90" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="J90" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="K90" t="s">
-        <v>283</v>
+        <v>57</v>
       </c>
       <c r="L90" t="s">
-        <v>284</v>
+        <v>34</v>
       </c>
       <c r="M90" t="s">
         <v>258</v>
@@ -7540,13 +7540,13 @@
         <v>47</v>
       </c>
       <c r="O90" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="P90" t="s">
-        <v>282</v>
+        <v>34</v>
       </c>
       <c r="Q90" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R90" t="s">
         <v>34</v>
@@ -7566,7 +7566,7 @@
         <v>34</v>
       </c>
       <c r="E91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F91" t="s">
         <v>199</v>
@@ -7575,19 +7575,19 @@
         <v>41</v>
       </c>
       <c r="H91" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I91" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J91" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="K91" t="s">
-        <v>86</v>
+        <v>290</v>
       </c>
       <c r="L91" t="s">
-        <v>288</v>
+        <v>34</v>
       </c>
       <c r="M91" t="s">
         <v>258</v>
@@ -7599,7 +7599,7 @@
         <v>156</v>
       </c>
       <c r="P91" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q91" t="s">
         <v>47</v>
@@ -7622,28 +7622,28 @@
         <v>34</v>
       </c>
       <c r="E92" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F92" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G92" t="s">
         <v>41</v>
       </c>
       <c r="H92" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="I92" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J92" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K92" t="s">
-        <v>292</v>
+        <v>86</v>
       </c>
       <c r="L92" t="s">
-        <v>34</v>
+        <v>295</v>
       </c>
       <c r="M92" t="s">
         <v>258</v>
@@ -7655,7 +7655,7 @@
         <v>156</v>
       </c>
       <c r="P92" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q92" t="s">
         <v>47</v>
@@ -7678,22 +7678,22 @@
         <v>34</v>
       </c>
       <c r="E93" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F93" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="G93" t="s">
         <v>41</v>
       </c>
       <c r="H93" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="I93" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="J93" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="K93" t="s">
         <v>57</v>
@@ -7734,10 +7734,10 @@
         <v>34</v>
       </c>
       <c r="E94" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F94" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="G94" t="s">
         <v>41</v>
@@ -7746,13 +7746,13 @@
         <v>268</v>
       </c>
       <c r="I94" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="J94" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="K94" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L94" t="s">
         <v>34</v>
@@ -7764,13 +7764,13 @@
         <v>47</v>
       </c>
       <c r="O94" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="P94" t="s">
-        <v>295</v>
+        <v>34</v>
       </c>
       <c r="Q94" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R94" t="s">
         <v>34</v>
@@ -7790,7 +7790,7 @@
         <v>34</v>
       </c>
       <c r="E95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F95" t="s">
         <v>199</v>
@@ -7799,19 +7799,19 @@
         <v>41</v>
       </c>
       <c r="H95" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="I95" t="s">
         <v>299</v>
       </c>
       <c r="J95" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="K95" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="L95" t="s">
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="M95" t="s">
         <v>258</v>
@@ -7849,25 +7849,25 @@
         <v>301</v>
       </c>
       <c r="F96" t="s">
-        <v>261</v>
+        <v>199</v>
       </c>
       <c r="G96" t="s">
         <v>41</v>
       </c>
       <c r="H96" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="I96" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="J96" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="K96" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="L96" t="s">
-        <v>34</v>
+        <v>303</v>
       </c>
       <c r="M96" t="s">
         <v>258</v>
@@ -7876,13 +7876,13 @@
         <v>47</v>
       </c>
       <c r="O96" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>34</v>
+        <v>302</v>
       </c>
       <c r="Q96" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R96" t="s">
         <v>34</v>
@@ -7902,28 +7902,28 @@
         <v>34</v>
       </c>
       <c r="E97" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F97" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G97" t="s">
         <v>41</v>
       </c>
       <c r="H97" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="I97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J97" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="K97" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L97" t="s">
-        <v>306</v>
+        <v>34</v>
       </c>
       <c r="M97" t="s">
         <v>258</v>
@@ -7935,7 +7935,7 @@
         <v>156</v>
       </c>
       <c r="P97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q97" t="s">
         <v>47</v>
@@ -7958,28 +7958,28 @@
         <v>34</v>
       </c>
       <c r="E98" t="s">
+        <v>306</v>
+      </c>
+      <c r="F98" t="s">
+        <v>199</v>
+      </c>
+      <c r="G98" t="s">
+        <v>41</v>
+      </c>
+      <c r="H98" t="s">
+        <v>287</v>
+      </c>
+      <c r="I98" t="s">
         <v>307</v>
       </c>
-      <c r="F98" t="s">
-        <v>40</v>
-      </c>
-      <c r="G98" t="s">
-        <v>41</v>
-      </c>
-      <c r="H98" t="s">
-        <v>158</v>
-      </c>
-      <c r="I98" t="s">
+      <c r="J98" t="s">
+        <v>56</v>
+      </c>
+      <c r="K98" t="s">
+        <v>56</v>
+      </c>
+      <c r="L98" t="s">
         <v>308</v>
-      </c>
-      <c r="J98" t="s">
-        <v>90</v>
-      </c>
-      <c r="K98" t="s">
-        <v>62</v>
-      </c>
-      <c r="L98" t="s">
-        <v>309</v>
       </c>
       <c r="M98" t="s">
         <v>258</v>
@@ -7991,7 +7991,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q98" t="s">
         <v>47</v>
@@ -8014,28 +8014,28 @@
         <v>34</v>
       </c>
       <c r="E99" t="s">
+        <v>309</v>
+      </c>
+      <c r="F99" t="s">
+        <v>199</v>
+      </c>
+      <c r="G99" t="s">
+        <v>41</v>
+      </c>
+      <c r="H99" t="s">
+        <v>292</v>
+      </c>
+      <c r="I99" t="s">
         <v>310</v>
       </c>
-      <c r="F99" t="s">
-        <v>173</v>
-      </c>
-      <c r="G99" t="s">
-        <v>41</v>
-      </c>
-      <c r="H99" t="s">
-        <v>262</v>
-      </c>
-      <c r="I99" t="s">
-        <v>263</v>
-      </c>
       <c r="J99" t="s">
+        <v>275</v>
+      </c>
+      <c r="K99" t="s">
+        <v>45</v>
+      </c>
+      <c r="L99" t="s">
         <v>311</v>
-      </c>
-      <c r="K99" t="s">
-        <v>57</v>
-      </c>
-      <c r="L99" t="s">
-        <v>312</v>
       </c>
       <c r="M99" t="s">
         <v>258</v>
@@ -8044,10 +8044,10 @@
         <v>47</v>
       </c>
       <c r="O99" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>310</v>
       </c>
       <c r="Q99" t="s">
         <v>47</v>
@@ -8070,7 +8070,7 @@
         <v>34</v>
       </c>
       <c r="E100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F100" t="s">
         <v>199</v>
@@ -8079,19 +8079,19 @@
         <v>41</v>
       </c>
       <c r="H100" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="I100" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="J100" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="K100" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="L100" t="s">
-        <v>315</v>
+        <v>34</v>
       </c>
       <c r="M100" t="s">
         <v>258</v>
@@ -8103,7 +8103,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="Q100" t="s">
         <v>47</v>
@@ -8126,10 +8126,10 @@
         <v>34</v>
       </c>
       <c r="E101" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F101" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G101" t="s">
         <v>41</v>
@@ -8138,16 +8138,16 @@
         <v>268</v>
       </c>
       <c r="I101" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="J101" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="K101" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="L101" t="s">
-        <v>34</v>
+        <v>271</v>
       </c>
       <c r="M101" t="s">
         <v>258</v>
@@ -8156,10 +8156,10 @@
         <v>47</v>
       </c>
       <c r="O101" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="P101" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="Q101" t="s">
         <v>47</v>
@@ -8182,28 +8182,28 @@
         <v>34</v>
       </c>
       <c r="E102" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F102" t="s">
-        <v>199</v>
+        <v>40</v>
       </c>
       <c r="G102" t="s">
         <v>41</v>
       </c>
       <c r="H102" t="s">
-        <v>268</v>
+        <v>158</v>
       </c>
       <c r="I102" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J102" t="s">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="K102" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L102" t="s">
-        <v>34</v>
+        <v>316</v>
       </c>
       <c r="M102" t="s">
         <v>258</v>
@@ -8215,7 +8215,7 @@
         <v>156</v>
       </c>
       <c r="P102" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="Q102" t="s">
         <v>47</v>
@@ -8238,28 +8238,28 @@
         <v>34</v>
       </c>
       <c r="E103" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F103" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G103" t="s">
         <v>41</v>
       </c>
       <c r="H103" t="s">
-        <v>262</v>
+        <v>318</v>
       </c>
       <c r="I103" t="s">
-        <v>263</v>
+        <v>319</v>
       </c>
       <c r="J103" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="K103" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L103" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="M103" t="s">
         <v>258</v>
@@ -8268,10 +8268,10 @@
         <v>47</v>
       </c>
       <c r="O103" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>319</v>
       </c>
       <c r="Q103" t="s">
         <v>47</v>
@@ -8294,7 +8294,7 @@
         <v>34</v>
       </c>
       <c r="E104" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F104" t="s">
         <v>199</v>
@@ -8303,16 +8303,16 @@
         <v>41</v>
       </c>
       <c r="H104" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="I104" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="J104" t="s">
-        <v>100</v>
+        <v>323</v>
       </c>
       <c r="K104" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="L104" t="s">
         <v>34</v>
@@ -8327,7 +8327,7 @@
         <v>156</v>
       </c>
       <c r="P104" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="Q104" t="s">
         <v>47</v>
@@ -8350,7 +8350,7 @@
         <v>34</v>
       </c>
       <c r="E105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F105" t="s">
         <v>199</v>
@@ -8359,19 +8359,19 @@
         <v>41</v>
       </c>
       <c r="H105" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="I105" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J105" t="s">
-        <v>277</v>
+        <v>326</v>
       </c>
       <c r="K105" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="L105" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M105" t="s">
         <v>258</v>
@@ -8380,10 +8380,10 @@
         <v>47</v>
       </c>
       <c r="O105" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q105" t="s">
         <v>47</v>
@@ -8406,7 +8406,7 @@
         <v>34</v>
       </c>
       <c r="E106" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F106" t="s">
         <v>199</v>
@@ -8415,19 +8415,19 @@
         <v>41</v>
       </c>
       <c r="H106" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="I106" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J106" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="K106" t="s">
-        <v>57</v>
+        <v>330</v>
       </c>
       <c r="L106" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M106" t="s">
         <v>258</v>
@@ -8436,10 +8436,10 @@
         <v>47</v>
       </c>
       <c r="O106" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="P106" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q106" t="s">
         <v>47</v>
@@ -8462,28 +8462,28 @@
         <v>34</v>
       </c>
       <c r="E107" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F107" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="G107" t="s">
         <v>41</v>
       </c>
       <c r="H107" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="I107" t="s">
-        <v>331</v>
+        <v>269</v>
       </c>
       <c r="J107" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="K107" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="L107" t="s">
-        <v>332</v>
+        <v>34</v>
       </c>
       <c r="M107" t="s">
         <v>258</v>
@@ -8492,13 +8492,13 @@
         <v>47</v>
       </c>
       <c r="O107" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="P107" t="s">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="Q107" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R107" t="s">
         <v>34</v>
@@ -11374,7 +11374,7 @@
         <v>34</v>
       </c>
       <c r="E159" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="F159" t="s">
         <v>203</v>
@@ -11404,7 +11404,7 @@
         <v>47</v>
       </c>
       <c r="O159" t="s">
-        <v>239</v>
+        <v>389</v>
       </c>
       <c r="P159" t="s">
         <v>428</v>
@@ -11430,7 +11430,7 @@
         <v>34</v>
       </c>
       <c r="E160" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="F160" t="s">
         <v>203</v>
@@ -11460,7 +11460,7 @@
         <v>47</v>
       </c>
       <c r="O160" t="s">
-        <v>389</v>
+        <v>239</v>
       </c>
       <c r="P160" t="s">
         <v>429</v>
@@ -12394,7 +12394,7 @@
         <v>448</v>
       </c>
       <c r="I177" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J177" t="s">
         <v>134</v>
@@ -12415,7 +12415,7 @@
         <v>389</v>
       </c>
       <c r="P177" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q177" t="s">
         <v>47</v>
@@ -15350,7 +15350,7 @@
         <v>34</v>
       </c>
       <c r="E230" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="F230" t="s">
         <v>203</v>
@@ -15359,16 +15359,16 @@
         <v>41</v>
       </c>
       <c r="H230" t="s">
+        <v>516</v>
+      </c>
+      <c r="I230" t="s">
         <v>520</v>
       </c>
-      <c r="I230" t="s">
-        <v>521</v>
-      </c>
       <c r="J230" t="s">
-        <v>134</v>
+        <v>519</v>
       </c>
       <c r="K230" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="L230" t="s">
         <v>34</v>
@@ -15380,10 +15380,10 @@
         <v>47</v>
       </c>
       <c r="O230" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="P230" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q230" t="s">
         <v>47</v>
@@ -15406,7 +15406,7 @@
         <v>34</v>
       </c>
       <c r="E231" t="s">
-        <v>522</v>
+        <v>198</v>
       </c>
       <c r="F231" t="s">
         <v>203</v>
@@ -15415,16 +15415,16 @@
         <v>41</v>
       </c>
       <c r="H231" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="I231" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J231" t="s">
-        <v>134</v>
+        <v>519</v>
       </c>
       <c r="K231" t="s">
-        <v>247</v>
+        <v>70</v>
       </c>
       <c r="L231" t="s">
         <v>34</v>
@@ -15436,10 +15436,10 @@
         <v>47</v>
       </c>
       <c r="O231" t="s">
-        <v>524</v>
+        <v>106</v>
       </c>
       <c r="P231" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Q231" t="s">
         <v>47</v>
@@ -15471,10 +15471,10 @@
         <v>41</v>
       </c>
       <c r="H232" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="I232" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="J232" t="s">
         <v>134</v>
@@ -15495,7 +15495,7 @@
         <v>138</v>
       </c>
       <c r="P232" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="Q232" t="s">
         <v>47</v>
@@ -15518,25 +15518,25 @@
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>198</v>
+        <v>524</v>
       </c>
       <c r="F233" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
       </c>
       <c r="H233" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="I233" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J233" t="s">
-        <v>519</v>
+        <v>134</v>
       </c>
       <c r="K233" t="s">
-        <v>70</v>
+        <v>247</v>
       </c>
       <c r="L233" t="s">
         <v>34</v>
@@ -15548,10 +15548,10 @@
         <v>47</v>
       </c>
       <c r="O233" t="s">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="P233" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q233" t="s">
         <v>47</v>
@@ -15574,7 +15574,7 @@
         <v>34</v>
       </c>
       <c r="E234" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="F234" t="s">
         <v>203</v>
@@ -15583,16 +15583,16 @@
         <v>41</v>
       </c>
       <c r="H234" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="I234" t="s">
         <v>528</v>
       </c>
       <c r="J234" t="s">
-        <v>519</v>
+        <v>134</v>
       </c>
       <c r="K234" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15604,7 +15604,7 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="P234" t="s">
         <v>528</v>
@@ -15633,16 +15633,16 @@
         <v>529</v>
       </c>
       <c r="F235" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G235" t="s">
         <v>41</v>
       </c>
       <c r="H235" t="s">
+        <v>527</v>
+      </c>
+      <c r="I235" t="s">
         <v>530</v>
-      </c>
-      <c r="I235" t="s">
-        <v>531</v>
       </c>
       <c r="J235" t="s">
         <v>134</v>
@@ -15660,10 +15660,10 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>156</v>
+        <v>531</v>
       </c>
       <c r="P235" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q235" t="s">
         <v>47</v>
@@ -15910,7 +15910,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="F240" t="s">
         <v>500</v>
@@ -15925,10 +15925,10 @@
         <v>540</v>
       </c>
       <c r="J240" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="K240" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15966,7 +15966,7 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="F241" t="s">
         <v>500</v>
@@ -15975,16 +15975,16 @@
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>436</v>
+        <v>539</v>
       </c>
       <c r="I241" t="s">
-        <v>428</v>
+        <v>541</v>
       </c>
       <c r="J241" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="K241" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -16022,7 +16022,7 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="F242" t="s">
         <v>500</v>
@@ -16031,16 +16031,16 @@
         <v>41</v>
       </c>
       <c r="H242" t="s">
-        <v>539</v>
+        <v>436</v>
       </c>
       <c r="I242" t="s">
-        <v>541</v>
+        <v>429</v>
       </c>
       <c r="J242" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="K242" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -16871,7 +16871,7 @@
         <v>41</v>
       </c>
       <c r="H257" t="s">
-        <v>493</v>
+        <v>417</v>
       </c>
       <c r="I257" t="s">
         <v>566</v>
@@ -16927,7 +16927,7 @@
         <v>41</v>
       </c>
       <c r="H258" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="I258" t="s">
         <v>567</v>
@@ -17325,7 +17325,7 @@
         <v>581</v>
       </c>
       <c r="J265" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K265" t="s">
         <v>125</v>
@@ -17381,7 +17381,7 @@
         <v>584</v>
       </c>
       <c r="J266" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K266" t="s">
         <v>125</v>
@@ -17549,7 +17549,7 @@
         <v>590</v>
       </c>
       <c r="J269" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K269" t="s">
         <v>125</v>
@@ -17605,7 +17605,7 @@
         <v>593</v>
       </c>
       <c r="J270" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K270" t="s">
         <v>125</v>
@@ -17661,7 +17661,7 @@
         <v>596</v>
       </c>
       <c r="J271" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K271" t="s">
         <v>125</v>
@@ -17773,7 +17773,7 @@
         <v>600</v>
       </c>
       <c r="J273" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K273" t="s">
         <v>125</v>
@@ -17885,7 +17885,7 @@
         <v>604</v>
       </c>
       <c r="J275" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K275" t="s">
         <v>125</v>
@@ -17941,7 +17941,7 @@
         <v>606</v>
       </c>
       <c r="J276" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K276" t="s">
         <v>100</v>
@@ -17997,7 +17997,7 @@
         <v>609</v>
       </c>
       <c r="J277" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K277" t="s">
         <v>125</v>
@@ -18053,7 +18053,7 @@
         <v>613</v>
       </c>
       <c r="J278" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K278" t="s">
         <v>126</v>
@@ -18262,10 +18262,10 @@
         <v>33</v>
       </c>
       <c r="E282" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="F282" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
@@ -18292,7 +18292,7 @@
         <v>47</v>
       </c>
       <c r="O282" t="s">
-        <v>389</v>
+        <v>622</v>
       </c>
       <c r="P282" t="s">
         <v>621</v>
@@ -18374,7 +18374,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F284" t="s">
         <v>173</v>
@@ -18389,10 +18389,10 @@
         <v>621</v>
       </c>
       <c r="J284" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K284" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="L284" t="s">
         <v>34</v>
@@ -18404,7 +18404,7 @@
         <v>47</v>
       </c>
       <c r="O284" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="P284" t="s">
         <v>621</v>
@@ -18430,7 +18430,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="F285" t="s">
         <v>173</v>
@@ -18445,10 +18445,10 @@
         <v>621</v>
       </c>
       <c r="J285" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K285" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18460,7 +18460,7 @@
         <v>47</v>
       </c>
       <c r="O285" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="P285" t="s">
         <v>621</v>
@@ -18486,10 +18486,10 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="F286" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
@@ -18501,10 +18501,10 @@
         <v>621</v>
       </c>
       <c r="J286" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="K286" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -18516,7 +18516,7 @@
         <v>47</v>
       </c>
       <c r="O286" t="s">
-        <v>103</v>
+        <v>353</v>
       </c>
       <c r="P286" t="s">
         <v>621</v>
@@ -18542,7 +18542,7 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="F287" t="s">
         <v>173</v>
@@ -18572,7 +18572,7 @@
         <v>47</v>
       </c>
       <c r="O287" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="P287" t="s">
         <v>621</v>
@@ -18598,10 +18598,10 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F288" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G288" t="s">
         <v>41</v>
@@ -18613,10 +18613,10 @@
         <v>621</v>
       </c>
       <c r="J288" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K288" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18628,7 +18628,7 @@
         <v>47</v>
       </c>
       <c r="O288" t="s">
-        <v>622</v>
+        <v>106</v>
       </c>
       <c r="P288" t="s">
         <v>621</v>
@@ -18654,7 +18654,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F289" t="s">
         <v>173</v>
@@ -18669,10 +18669,10 @@
         <v>621</v>
       </c>
       <c r="J289" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="K289" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="L289" t="s">
         <v>34</v>
@@ -18684,7 +18684,7 @@
         <v>47</v>
       </c>
       <c r="O289" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="P289" t="s">
         <v>621</v>
@@ -18710,10 +18710,10 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="F290" t="s">
-        <v>261</v>
+        <v>199</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
@@ -18725,10 +18725,10 @@
         <v>621</v>
       </c>
       <c r="J290" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="K290" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L290" t="s">
         <v>34</v>
@@ -18740,13 +18740,13 @@
         <v>47</v>
       </c>
       <c r="O290" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="P290" t="s">
-        <v>34</v>
+        <v>621</v>
       </c>
       <c r="Q290" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R290" t="s">
         <v>34</v>
@@ -18766,10 +18766,10 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="F291" t="s">
-        <v>173</v>
+        <v>284</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
@@ -18781,10 +18781,10 @@
         <v>621</v>
       </c>
       <c r="J291" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="K291" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="L291" t="s">
         <v>34</v>
@@ -18796,13 +18796,13 @@
         <v>47</v>
       </c>
       <c r="O291" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="P291" t="s">
-        <v>621</v>
+        <v>34</v>
       </c>
       <c r="Q291" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R291" t="s">
         <v>34</v>
@@ -18822,10 +18822,10 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>213</v>
+        <v>499</v>
       </c>
       <c r="F292" t="s">
-        <v>173</v>
+        <v>284</v>
       </c>
       <c r="G292" t="s">
         <v>41</v>
@@ -18837,10 +18837,10 @@
         <v>621</v>
       </c>
       <c r="J292" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="K292" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="L292" t="s">
         <v>34</v>
@@ -18852,13 +18852,13 @@
         <v>47</v>
       </c>
       <c r="O292" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="P292" t="s">
-        <v>621</v>
+        <v>34</v>
       </c>
       <c r="Q292" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R292" t="s">
         <v>34</v>
@@ -18934,10 +18934,10 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>499</v>
+        <v>213</v>
       </c>
       <c r="F294" t="s">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="G294" t="s">
         <v>41</v>
@@ -18949,10 +18949,10 @@
         <v>621</v>
       </c>
       <c r="J294" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="K294" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="L294" t="s">
         <v>34</v>
@@ -18964,13 +18964,13 @@
         <v>47</v>
       </c>
       <c r="O294" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="P294" t="s">
-        <v>34</v>
+        <v>621</v>
       </c>
       <c r="Q294" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R294" t="s">
         <v>34</v>
@@ -19061,7 +19061,7 @@
         <v>630</v>
       </c>
       <c r="J296" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K296" t="s">
         <v>126</v>
@@ -19285,10 +19285,10 @@
         <v>644</v>
       </c>
       <c r="J300" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="K300" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="L300" t="s">
         <v>34</v>
@@ -19341,10 +19341,10 @@
         <v>644</v>
       </c>
       <c r="J301" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="K301" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="L301" t="s">
         <v>34</v>
@@ -19397,10 +19397,10 @@
         <v>644</v>
       </c>
       <c r="J302" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="K302" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="L302" t="s">
         <v>34</v>
@@ -19565,7 +19565,7 @@
         <v>656</v>
       </c>
       <c r="J305" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="K305" t="s">
         <v>86</v>
@@ -19606,7 +19606,7 @@
         <v>34</v>
       </c>
       <c r="E306" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F306" t="s">
         <v>173</v>
@@ -19615,16 +19615,16 @@
         <v>41</v>
       </c>
       <c r="H306" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I306" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J306" t="s">
-        <v>660</v>
+        <v>182</v>
       </c>
       <c r="K306" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="L306" t="s">
         <v>661</v>
@@ -19639,7 +19639,7 @@
         <v>156</v>
       </c>
       <c r="P306" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Q306" t="s">
         <v>47</v>
@@ -19662,7 +19662,7 @@
         <v>34</v>
       </c>
       <c r="E307" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="F307" t="s">
         <v>173</v>
@@ -19671,16 +19671,16 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
+        <v>662</v>
+      </c>
+      <c r="I307" t="s">
         <v>663</v>
       </c>
-      <c r="I307" t="s">
+      <c r="J307" t="s">
         <v>664</v>
       </c>
-      <c r="J307" t="s">
-        <v>182</v>
-      </c>
       <c r="K307" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="L307" t="s">
         <v>665</v>
@@ -19695,7 +19695,7 @@
         <v>156</v>
       </c>
       <c r="P307" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="Q307" t="s">
         <v>47</v>
@@ -19901,7 +19901,7 @@
         <v>673</v>
       </c>
       <c r="J311" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K311" t="s">
         <v>86</v>
@@ -20110,7 +20110,7 @@
         <v>34</v>
       </c>
       <c r="E315" t="s">
-        <v>654</v>
+        <v>157</v>
       </c>
       <c r="F315" t="s">
         <v>173</v>
@@ -20119,19 +20119,19 @@
         <v>41</v>
       </c>
       <c r="H315" t="s">
+        <v>516</v>
+      </c>
+      <c r="I315" t="s">
+        <v>673</v>
+      </c>
+      <c r="J315" t="s">
         <v>682</v>
       </c>
-      <c r="I315" t="s">
+      <c r="K315" t="s">
+        <v>247</v>
+      </c>
+      <c r="L315" t="s">
         <v>683</v>
-      </c>
-      <c r="J315" t="s">
-        <v>660</v>
-      </c>
-      <c r="K315" t="s">
-        <v>86</v>
-      </c>
-      <c r="L315" t="s">
-        <v>684</v>
       </c>
       <c r="M315" t="s">
         <v>679</v>
@@ -20143,7 +20143,7 @@
         <v>156</v>
       </c>
       <c r="P315" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="Q315" t="s">
         <v>47</v>
@@ -20175,19 +20175,19 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
+        <v>684</v>
+      </c>
+      <c r="I316" t="s">
+        <v>673</v>
+      </c>
+      <c r="J316" t="s">
+        <v>294</v>
+      </c>
+      <c r="K316" t="s">
+        <v>247</v>
+      </c>
+      <c r="L316" t="s">
         <v>685</v>
-      </c>
-      <c r="I316" t="s">
-        <v>686</v>
-      </c>
-      <c r="J316" t="s">
-        <v>660</v>
-      </c>
-      <c r="K316" t="s">
-        <v>86</v>
-      </c>
-      <c r="L316" t="s">
-        <v>687</v>
       </c>
       <c r="M316" t="s">
         <v>679</v>
@@ -20199,7 +20199,7 @@
         <v>156</v>
       </c>
       <c r="P316" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -20222,7 +20222,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>157</v>
+        <v>658</v>
       </c>
       <c r="F317" t="s">
         <v>173</v>
@@ -20231,19 +20231,19 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
-        <v>497</v>
+        <v>417</v>
       </c>
       <c r="I317" t="s">
+        <v>686</v>
+      </c>
+      <c r="J317" t="s">
+        <v>687</v>
+      </c>
+      <c r="K317" t="s">
+        <v>86</v>
+      </c>
+      <c r="L317" t="s">
         <v>688</v>
-      </c>
-      <c r="J317" t="s">
-        <v>689</v>
-      </c>
-      <c r="K317" t="s">
-        <v>690</v>
-      </c>
-      <c r="L317" t="s">
-        <v>691</v>
       </c>
       <c r="M317" t="s">
         <v>679</v>
@@ -20255,7 +20255,7 @@
         <v>156</v>
       </c>
       <c r="P317" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -20287,19 +20287,19 @@
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="I318" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="J318" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K318" t="s">
         <v>86</v>
       </c>
       <c r="L318" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="M318" t="s">
         <v>679</v>
@@ -20311,7 +20311,7 @@
         <v>156</v>
       </c>
       <c r="P318" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="Q318" t="s">
         <v>47</v>
@@ -20334,7 +20334,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>157</v>
+        <v>654</v>
       </c>
       <c r="F319" t="s">
         <v>173</v>
@@ -20343,19 +20343,19 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
-        <v>516</v>
+        <v>692</v>
       </c>
       <c r="I319" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="J319" t="s">
+        <v>664</v>
+      </c>
+      <c r="K319" t="s">
+        <v>86</v>
+      </c>
+      <c r="L319" t="s">
         <v>694</v>
-      </c>
-      <c r="K319" t="s">
-        <v>247</v>
-      </c>
-      <c r="L319" t="s">
-        <v>695</v>
       </c>
       <c r="M319" t="s">
         <v>679</v>
@@ -20367,7 +20367,7 @@
         <v>156</v>
       </c>
       <c r="P319" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="Q319" t="s">
         <v>47</v>
@@ -20390,7 +20390,7 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="F320" t="s">
         <v>173</v>
@@ -20399,19 +20399,19 @@
         <v>41</v>
       </c>
       <c r="H320" t="s">
-        <v>417</v>
+        <v>636</v>
       </c>
       <c r="I320" t="s">
-        <v>696</v>
+        <v>673</v>
       </c>
       <c r="J320" t="s">
-        <v>697</v>
+        <v>664</v>
       </c>
       <c r="K320" t="s">
         <v>86</v>
       </c>
       <c r="L320" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="M320" t="s">
         <v>679</v>
@@ -20423,7 +20423,7 @@
         <v>156</v>
       </c>
       <c r="P320" t="s">
-        <v>696</v>
+        <v>673</v>
       </c>
       <c r="Q320" t="s">
         <v>47</v>
@@ -20446,28 +20446,28 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>699</v>
+        <v>654</v>
       </c>
       <c r="F321" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G321" t="s">
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="I321" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="J321" t="s">
-        <v>57</v>
+        <v>664</v>
       </c>
       <c r="K321" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L321" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="M321" t="s">
         <v>679</v>
@@ -20479,7 +20479,7 @@
         <v>156</v>
       </c>
       <c r="P321" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="Q321" t="s">
         <v>47</v>
@@ -20502,7 +20502,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>654</v>
+        <v>157</v>
       </c>
       <c r="F322" t="s">
         <v>173</v>
@@ -20511,19 +20511,19 @@
         <v>41</v>
       </c>
       <c r="H322" t="s">
+        <v>497</v>
+      </c>
+      <c r="I322" t="s">
+        <v>698</v>
+      </c>
+      <c r="J322" t="s">
+        <v>699</v>
+      </c>
+      <c r="K322" t="s">
+        <v>700</v>
+      </c>
+      <c r="L322" t="s">
         <v>701</v>
-      </c>
-      <c r="I322" t="s">
-        <v>673</v>
-      </c>
-      <c r="J322" t="s">
-        <v>305</v>
-      </c>
-      <c r="K322" t="s">
-        <v>247</v>
-      </c>
-      <c r="L322" t="s">
-        <v>702</v>
       </c>
       <c r="M322" t="s">
         <v>679</v>
@@ -20535,7 +20535,7 @@
         <v>156</v>
       </c>
       <c r="P322" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="Q322" t="s">
         <v>47</v>
@@ -20558,7 +20558,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>157</v>
+        <v>654</v>
       </c>
       <c r="F323" t="s">
         <v>173</v>
@@ -20567,19 +20567,19 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
-        <v>470</v>
+        <v>702</v>
       </c>
       <c r="I323" t="s">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="J323" t="s">
-        <v>689</v>
+        <v>664</v>
       </c>
       <c r="K323" t="s">
         <v>86</v>
       </c>
       <c r="L323" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M323" t="s">
         <v>679</v>
@@ -20591,7 +20591,7 @@
         <v>156</v>
       </c>
       <c r="P323" t="s">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="Q323" t="s">
         <v>47</v>
@@ -20614,28 +20614,28 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>654</v>
+        <v>705</v>
       </c>
       <c r="F324" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G324" t="s">
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>636</v>
+        <v>702</v>
       </c>
       <c r="I324" t="s">
         <v>673</v>
       </c>
       <c r="J324" t="s">
-        <v>660</v>
+        <v>57</v>
       </c>
       <c r="K324" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L324" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="M324" t="s">
         <v>679</v>
@@ -20670,7 +20670,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>654</v>
+        <v>157</v>
       </c>
       <c r="F325" t="s">
         <v>173</v>
@@ -20679,13 +20679,13 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
-        <v>705</v>
+        <v>470</v>
       </c>
       <c r="I325" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="J325" t="s">
-        <v>660</v>
+        <v>699</v>
       </c>
       <c r="K325" t="s">
         <v>86</v>
@@ -20703,7 +20703,7 @@
         <v>156</v>
       </c>
       <c r="P325" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="Q325" t="s">
         <v>47</v>
@@ -20741,7 +20741,7 @@
         <v>709</v>
       </c>
       <c r="J326" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K326" t="s">
         <v>86</v>
@@ -20847,10 +20847,10 @@
         <v>41</v>
       </c>
       <c r="H328" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I328" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J328" t="s">
         <v>176</v>
@@ -20871,7 +20871,7 @@
         <v>156</v>
       </c>
       <c r="P328" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="Q328" t="s">
         <v>47</v>
@@ -20959,10 +20959,10 @@
         <v>41</v>
       </c>
       <c r="H330" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I330" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J330" t="s">
         <v>176</v>
@@ -20983,7 +20983,7 @@
         <v>156</v>
       </c>
       <c r="P330" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="Q330" t="s">
         <v>47</v>
@@ -21177,7 +21177,7 @@
         <v>172</v>
       </c>
       <c r="F334" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="G334" t="s">
         <v>41</v>
@@ -21581,7 +21581,7 @@
         <v>747</v>
       </c>
       <c r="J341" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K341" t="s">
         <v>247</v>
@@ -21631,7 +21631,7 @@
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I342" t="s">
         <v>752</v>
@@ -21861,7 +21861,7 @@
         <v>765</v>
       </c>
       <c r="J346" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K346" t="s">
         <v>86</v>
@@ -22029,7 +22029,7 @@
         <v>777</v>
       </c>
       <c r="J349" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K349" t="s">
         <v>75</v>
@@ -22197,7 +22197,7 @@
         <v>786</v>
       </c>
       <c r="J352" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K352" t="s">
         <v>247</v>
@@ -22309,10 +22309,10 @@
         <v>793</v>
       </c>
       <c r="J354" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K354" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="L354" t="s">
         <v>794</v>
@@ -22421,10 +22421,10 @@
         <v>801</v>
       </c>
       <c r="J356" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K356" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="L356" t="s">
         <v>802</v>
@@ -22527,7 +22527,7 @@
         <v>41</v>
       </c>
       <c r="H358" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="I358" t="s">
         <v>807</v>
@@ -22701,7 +22701,7 @@
         <v>819</v>
       </c>
       <c r="J361" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K361" t="s">
         <v>86</v>
@@ -22919,19 +22919,19 @@
         <v>41</v>
       </c>
       <c r="H365" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="I365" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="J365" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="K365" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="L365" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M365" t="s">
         <v>834</v>
@@ -22943,7 +22943,7 @@
         <v>156</v>
       </c>
       <c r="P365" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="Q365" t="s">
         <v>47</v>
@@ -22975,16 +22975,16 @@
         <v>41</v>
       </c>
       <c r="H366" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="I366" t="s">
         <v>838</v>
       </c>
       <c r="J366" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="K366" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="L366" t="s">
         <v>839</v>
@@ -23037,13 +23037,13 @@
         <v>842</v>
       </c>
       <c r="J367" t="s">
-        <v>808</v>
+        <v>843</v>
       </c>
       <c r="K367" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="L367" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="M367" t="s">
         <v>834</v>
@@ -23078,7 +23078,7 @@
         <v>34</v>
       </c>
       <c r="E368" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="F368" t="s">
         <v>173</v>
@@ -23087,16 +23087,16 @@
         <v>41</v>
       </c>
       <c r="H368" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="I368" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="J368" t="s">
-        <v>846</v>
+        <v>247</v>
       </c>
       <c r="K368" t="s">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="L368" t="s">
         <v>847</v>
@@ -23111,7 +23111,7 @@
         <v>156</v>
       </c>
       <c r="P368" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="Q368" t="s">
         <v>47</v>
@@ -23205,13 +23205,13 @@
         <v>852</v>
       </c>
       <c r="J370" t="s">
-        <v>247</v>
+        <v>853</v>
       </c>
       <c r="K370" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L370" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M370" t="s">
         <v>834</v>
@@ -23246,7 +23246,7 @@
         <v>34</v>
       </c>
       <c r="E371" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F371" t="s">
         <v>173</v>
@@ -23255,19 +23255,19 @@
         <v>41</v>
       </c>
       <c r="H371" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="I371" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="J371" t="s">
-        <v>856</v>
+        <v>808</v>
       </c>
       <c r="K371" t="s">
         <v>86</v>
       </c>
       <c r="L371" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="M371" t="s">
         <v>834</v>
@@ -23279,7 +23279,7 @@
         <v>156</v>
       </c>
       <c r="P371" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="Q371" t="s">
         <v>47</v>
@@ -23597,7 +23597,7 @@
         <v>878</v>
       </c>
       <c r="J377" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K377" t="s">
         <v>86</v>
@@ -23821,7 +23821,7 @@
         <v>896</v>
       </c>
       <c r="J381" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K381" t="s">
         <v>86</v>
@@ -23933,7 +23933,7 @@
         <v>904</v>
       </c>
       <c r="J383" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="K383" t="s">
         <v>86</v>
@@ -24086,7 +24086,7 @@
         <v>33</v>
       </c>
       <c r="E386" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F386" t="s">
         <v>173</v>
@@ -24325,7 +24325,7 @@
         <v>922</v>
       </c>
       <c r="J390" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K390" t="s">
         <v>126</v>
@@ -29869,7 +29869,7 @@
         <v>1049</v>
       </c>
       <c r="J489" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="K489" t="s">
         <v>120</v>

--- a/xlsx/dre/DRE_05_2026.xlsx
+++ b/xlsx/dre/DRE_05_2026.xlsx
@@ -474,6 +474,33 @@
     <t>R$ 1.846,76</t>
   </si>
   <si>
+    <t>IRRF/2</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>R$  178,31</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>1/4</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  476,46</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
+    <t>Digisac MP 2026</t>
+  </si>
+  <si>
     <t>INSS/0</t>
   </si>
   <si>
@@ -481,33 +508,6 @@
   </si>
   <si>
     <t>R$  1.191,99</t>
-  </si>
-  <si>
-    <t>ADM</t>
-  </si>
-  <si>
-    <t>1/4</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  476,46</t>
-  </si>
-  <si>
-    <t>27/02/26</t>
-  </si>
-  <si>
-    <t>Digisac MP 2026</t>
-  </si>
-  <si>
-    <t>IRRF/2</t>
-  </si>
-  <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>R$  178,31</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -1039,6 +1039,15 @@
     <t>4.02.02.01.01 Fretes sobre compra de mercadorias da marca - provisão</t>
   </si>
   <si>
+    <t>76901R/0</t>
+  </si>
+  <si>
+    <t>RODAG TRANSPORTES LTDA*</t>
+  </si>
+  <si>
+    <t>R$  65,38</t>
+  </si>
+  <si>
     <t>82001/2</t>
   </si>
   <si>
@@ -1057,9 +1066,6 @@
     <t>82001/3</t>
   </si>
   <si>
-    <t>RODAG TRANSPORTES LTDA*</t>
-  </si>
-  <si>
     <t>R$  88,52</t>
   </si>
   <si>
@@ -1249,12 +1255,6 @@
     <t>R$  251,04</t>
   </si>
   <si>
-    <t>76901R/0</t>
-  </si>
-  <si>
-    <t>R$  65,38</t>
-  </si>
-  <si>
     <t>4.03 DESPESAS DE VENDAS</t>
   </si>
   <si>
@@ -1726,10 +1726,10 @@
     <t>DSR maio26/1</t>
   </si>
   <si>
+    <t>R$  1.008,15</t>
+  </si>
+  <si>
     <t>R$  480,34</t>
-  </si>
-  <si>
-    <t>R$  1.008,15</t>
   </si>
   <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
@@ -1956,21 +1956,21 @@
     <t>4.03.03.08.01 Brindes para clientes (CV)</t>
   </si>
   <si>
+    <t>BRINDE CLIENTES 3/0</t>
+  </si>
+  <si>
+    <t>Licoretto Bebidas</t>
+  </si>
+  <si>
+    <t>R$  159,96</t>
+  </si>
+  <si>
+    <t>BRINDE CLIENTES 2/0</t>
+  </si>
+  <si>
     <t>BRINDE CLIENTES/0</t>
   </si>
   <si>
-    <t>Licoretto Bebidas</t>
-  </si>
-  <si>
-    <t>R$  159,96</t>
-  </si>
-  <si>
-    <t>BRINDE CLIENTES 2/0</t>
-  </si>
-  <si>
-    <t>BRINDE CLIENTES 3/0</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -2004,6 +2004,18 @@
     <t>Google 2026</t>
   </si>
   <si>
+    <t>1/3</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>R$  3.750,00</t>
+  </si>
+  <si>
+    <t>Facebook 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -2016,18 +2028,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>1/3</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>R$  3.750,00</t>
-  </si>
-  <si>
-    <t>Facebook 2026</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -2430,16 +2430,16 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
-    <t>672/1</t>
-  </si>
-  <si>
-    <t>Lojas Mel</t>
-  </si>
-  <si>
-    <t>R$  19,99</t>
-  </si>
-  <si>
-    <t>Material limpeza</t>
+    <t>668/1</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>R$  177,42</t>
+  </si>
+  <si>
+    <t>Papel interfolhado, esfregão</t>
   </si>
   <si>
     <t>651/1</t>
@@ -2455,16 +2455,16 @@
 </t>
   </si>
   <si>
-    <t>668/1</t>
-  </si>
-  <si>
-    <t>Shopee</t>
-  </si>
-  <si>
-    <t>R$  177,42</t>
-  </si>
-  <si>
-    <t>Papel interfolhado, esfregão</t>
+    <t>672/1</t>
+  </si>
+  <si>
+    <t>Lojas Mel</t>
+  </si>
+  <si>
+    <t>R$  19,99</t>
+  </si>
+  <si>
+    <t>Material limpeza</t>
   </si>
   <si>
     <t>634/1</t>
@@ -2563,19 +2563,64 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>R$  599,00</t>
   </si>
   <si>
     <t>Promob 2026</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
+    <t>64/12</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>22/06/26</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
+    <t>63/12</t>
+  </si>
+  <si>
+    <t>R$  376,44</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>62/12</t>
+  </si>
+  <si>
+    <t>R$  293,21</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
+    <t>3/4</t>
+  </si>
+  <si>
+    <t>R$  1.248,82</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
   </si>
   <si>
     <t>61/1</t>
@@ -2585,51 +2630,6 @@
   </si>
   <si>
     <t>R$  95,73</t>
-  </si>
-  <si>
-    <t>64/12</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>22/06/26</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>63/12</t>
-  </si>
-  <si>
-    <t>R$  376,44</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>62/12</t>
-  </si>
-  <si>
-    <t>R$  293,21</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
-    <t>3/4</t>
-  </si>
-  <si>
-    <t>R$  1.248,82</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -8660,25 +8660,25 @@
         <v>337</v>
       </c>
       <c r="F110" t="s">
+        <v>199</v>
+      </c>
+      <c r="G110" t="s">
+        <v>41</v>
+      </c>
+      <c r="H110" t="s">
         <v>338</v>
       </c>
-      <c r="G110" t="s">
-        <v>41</v>
-      </c>
-      <c r="H110" t="s">
+      <c r="I110" t="s">
         <v>339</v>
       </c>
-      <c r="I110" t="s">
-        <v>340</v>
-      </c>
       <c r="J110" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="K110" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L110" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="M110" t="s">
         <v>336</v>
@@ -8687,13 +8687,13 @@
         <v>47</v>
       </c>
       <c r="O110" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="P110" t="s">
-        <v>34</v>
+        <v>339</v>
       </c>
       <c r="Q110" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R110" t="s">
         <v>34</v>
@@ -8713,19 +8713,19 @@
         <v>34</v>
       </c>
       <c r="E111" t="s">
+        <v>340</v>
+      </c>
+      <c r="F111" t="s">
+        <v>341</v>
+      </c>
+      <c r="G111" t="s">
+        <v>41</v>
+      </c>
+      <c r="H111" t="s">
         <v>342</v>
       </c>
-      <c r="F111" t="s">
-        <v>338</v>
-      </c>
-      <c r="G111" t="s">
-        <v>41</v>
-      </c>
-      <c r="H111" t="s">
+      <c r="I111" t="s">
         <v>343</v>
-      </c>
-      <c r="I111" t="s">
-        <v>344</v>
       </c>
       <c r="J111" t="s">
         <v>113</v>
@@ -8734,7 +8734,7 @@
         <v>113</v>
       </c>
       <c r="L111" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M111" t="s">
         <v>336</v>
@@ -8772,13 +8772,13 @@
         <v>345</v>
       </c>
       <c r="F112" t="s">
+        <v>341</v>
+      </c>
+      <c r="G112" t="s">
+        <v>41</v>
+      </c>
+      <c r="H112" t="s">
         <v>338</v>
-      </c>
-      <c r="G112" t="s">
-        <v>41</v>
-      </c>
-      <c r="H112" t="s">
-        <v>339</v>
       </c>
       <c r="I112" t="s">
         <v>346</v>
@@ -8790,7 +8790,7 @@
         <v>113</v>
       </c>
       <c r="L112" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M112" t="s">
         <v>336</v>
@@ -8828,13 +8828,13 @@
         <v>347</v>
       </c>
       <c r="F113" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G113" t="s">
         <v>41</v>
       </c>
       <c r="H113" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I113" t="s">
         <v>348</v>
@@ -8846,7 +8846,7 @@
         <v>113</v>
       </c>
       <c r="L113" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M113" t="s">
         <v>336</v>
@@ -8884,25 +8884,25 @@
         <v>349</v>
       </c>
       <c r="F114" t="s">
-        <v>203</v>
+        <v>341</v>
       </c>
       <c r="G114" t="s">
         <v>41</v>
       </c>
       <c r="H114" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I114" t="s">
         <v>350</v>
       </c>
       <c r="J114" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="K114" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="L114" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M114" t="s">
         <v>336</v>
@@ -8911,13 +8911,13 @@
         <v>47</v>
       </c>
       <c r="O114" t="s">
-        <v>351</v>
+        <v>34</v>
       </c>
       <c r="P114" t="s">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="Q114" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R114" t="s">
         <v>34</v>
@@ -8937,7 +8937,7 @@
         <v>34</v>
       </c>
       <c r="E115" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F115" t="s">
         <v>203</v>
@@ -8946,19 +8946,19 @@
         <v>41</v>
       </c>
       <c r="H115" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I115" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J115" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K115" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="L115" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M115" t="s">
         <v>336</v>
@@ -8967,10 +8967,10 @@
         <v>47</v>
       </c>
       <c r="O115" t="s">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="P115" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q115" t="s">
         <v>47</v>
@@ -9002,19 +9002,19 @@
         <v>41</v>
       </c>
       <c r="H116" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I116" t="s">
         <v>355</v>
       </c>
       <c r="J116" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="K116" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="L116" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M116" t="s">
         <v>336</v>
@@ -9023,7 +9023,7 @@
         <v>47</v>
       </c>
       <c r="O116" t="s">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="P116" t="s">
         <v>355</v>
@@ -9049,7 +9049,7 @@
         <v>34</v>
       </c>
       <c r="E117" t="s">
-        <v>221</v>
+        <v>356</v>
       </c>
       <c r="F117" t="s">
         <v>203</v>
@@ -9058,19 +9058,19 @@
         <v>41</v>
       </c>
       <c r="H117" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I117" t="s">
         <v>357</v>
       </c>
       <c r="J117" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="K117" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="L117" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M117" t="s">
         <v>336</v>
@@ -9079,7 +9079,7 @@
         <v>47</v>
       </c>
       <c r="O117" t="s">
-        <v>103</v>
+        <v>358</v>
       </c>
       <c r="P117" t="s">
         <v>357</v>
@@ -9105,7 +9105,7 @@
         <v>34</v>
       </c>
       <c r="E118" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="F118" t="s">
         <v>203</v>
@@ -9114,19 +9114,19 @@
         <v>41</v>
       </c>
       <c r="H118" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I118" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J118" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K118" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="L118" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M118" t="s">
         <v>336</v>
@@ -9135,10 +9135,10 @@
         <v>47</v>
       </c>
       <c r="O118" t="s">
+        <v>103</v>
+      </c>
+      <c r="P118" t="s">
         <v>359</v>
-      </c>
-      <c r="P118" t="s">
-        <v>358</v>
       </c>
       <c r="Q118" t="s">
         <v>47</v>
@@ -9161,7 +9161,7 @@
         <v>34</v>
       </c>
       <c r="E119" t="s">
-        <v>360</v>
+        <v>242</v>
       </c>
       <c r="F119" t="s">
         <v>203</v>
@@ -9170,10 +9170,10 @@
         <v>41</v>
       </c>
       <c r="H119" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I119" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J119" t="s">
         <v>75</v>
@@ -9182,7 +9182,7 @@
         <v>75</v>
       </c>
       <c r="L119" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M119" t="s">
         <v>336</v>
@@ -9191,10 +9191,10 @@
         <v>47</v>
       </c>
       <c r="O119" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P119" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q119" t="s">
         <v>47</v>
@@ -9217,7 +9217,7 @@
         <v>34</v>
       </c>
       <c r="E120" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="F120" t="s">
         <v>203</v>
@@ -9226,19 +9226,19 @@
         <v>41</v>
       </c>
       <c r="H120" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I120" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J120" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K120" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L120" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M120" t="s">
         <v>336</v>
@@ -9247,10 +9247,10 @@
         <v>47</v>
       </c>
       <c r="O120" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="P120" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q120" t="s">
         <v>47</v>
@@ -9273,7 +9273,7 @@
         <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>363</v>
+        <v>234</v>
       </c>
       <c r="F121" t="s">
         <v>203</v>
@@ -9282,19 +9282,19 @@
         <v>41</v>
       </c>
       <c r="H121" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I121" t="s">
         <v>364</v>
       </c>
       <c r="J121" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="K121" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="L121" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M121" t="s">
         <v>336</v>
@@ -9303,7 +9303,7 @@
         <v>47</v>
       </c>
       <c r="O121" t="s">
-        <v>206</v>
+        <v>353</v>
       </c>
       <c r="P121" t="s">
         <v>364</v>
@@ -9338,19 +9338,19 @@
         <v>41</v>
       </c>
       <c r="H122" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I122" t="s">
         <v>366</v>
       </c>
       <c r="J122" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="K122" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="L122" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M122" t="s">
         <v>336</v>
@@ -9359,7 +9359,7 @@
         <v>47</v>
       </c>
       <c r="O122" t="s">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="P122" t="s">
         <v>366</v>
@@ -9394,19 +9394,19 @@
         <v>41</v>
       </c>
       <c r="H123" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I123" t="s">
         <v>368</v>
       </c>
       <c r="J123" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K123" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L123" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M123" t="s">
         <v>336</v>
@@ -9415,7 +9415,7 @@
         <v>47</v>
       </c>
       <c r="O123" t="s">
-        <v>356</v>
+        <v>143</v>
       </c>
       <c r="P123" t="s">
         <v>368</v>
@@ -9450,19 +9450,19 @@
         <v>41</v>
       </c>
       <c r="H124" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I124" t="s">
         <v>370</v>
       </c>
       <c r="J124" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="K124" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="L124" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M124" t="s">
         <v>336</v>
@@ -9471,7 +9471,7 @@
         <v>47</v>
       </c>
       <c r="O124" t="s">
-        <v>206</v>
+        <v>358</v>
       </c>
       <c r="P124" t="s">
         <v>370</v>
@@ -9506,19 +9506,19 @@
         <v>41</v>
       </c>
       <c r="H125" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I125" t="s">
         <v>372</v>
       </c>
       <c r="J125" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="K125" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="L125" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M125" t="s">
         <v>336</v>
@@ -9527,7 +9527,7 @@
         <v>47</v>
       </c>
       <c r="O125" t="s">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="P125" t="s">
         <v>372</v>
@@ -9562,19 +9562,19 @@
         <v>41</v>
       </c>
       <c r="H126" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I126" t="s">
         <v>374</v>
       </c>
       <c r="J126" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K126" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L126" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M126" t="s">
         <v>336</v>
@@ -9583,7 +9583,7 @@
         <v>47</v>
       </c>
       <c r="O126" t="s">
-        <v>239</v>
+        <v>143</v>
       </c>
       <c r="P126" t="s">
         <v>374</v>
@@ -9618,7 +9618,7 @@
         <v>41</v>
       </c>
       <c r="H127" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I127" t="s">
         <v>376</v>
@@ -9630,7 +9630,7 @@
         <v>52</v>
       </c>
       <c r="L127" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M127" t="s">
         <v>336</v>
@@ -9674,19 +9674,19 @@
         <v>41</v>
       </c>
       <c r="H128" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I128" t="s">
         <v>378</v>
       </c>
       <c r="J128" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="K128" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="L128" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M128" t="s">
         <v>336</v>
@@ -9695,7 +9695,7 @@
         <v>47</v>
       </c>
       <c r="O128" t="s">
-        <v>103</v>
+        <v>239</v>
       </c>
       <c r="P128" t="s">
         <v>378</v>
@@ -9730,19 +9730,19 @@
         <v>41</v>
       </c>
       <c r="H129" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I129" t="s">
         <v>380</v>
       </c>
       <c r="J129" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="K129" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="L129" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M129" t="s">
         <v>336</v>
@@ -9751,7 +9751,7 @@
         <v>47</v>
       </c>
       <c r="O129" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="P129" t="s">
         <v>380</v>
@@ -9786,19 +9786,19 @@
         <v>41</v>
       </c>
       <c r="H130" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I130" t="s">
         <v>382</v>
       </c>
       <c r="J130" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K130" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L130" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M130" t="s">
         <v>336</v>
@@ -9807,7 +9807,7 @@
         <v>47</v>
       </c>
       <c r="O130" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="P130" t="s">
         <v>382</v>
@@ -9842,7 +9842,7 @@
         <v>41</v>
       </c>
       <c r="H131" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I131" t="s">
         <v>384</v>
@@ -9854,7 +9854,7 @@
         <v>70</v>
       </c>
       <c r="L131" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M131" t="s">
         <v>336</v>
@@ -9898,19 +9898,19 @@
         <v>41</v>
       </c>
       <c r="H132" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I132" t="s">
         <v>386</v>
       </c>
       <c r="J132" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K132" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L132" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M132" t="s">
         <v>336</v>
@@ -9919,7 +9919,7 @@
         <v>47</v>
       </c>
       <c r="O132" t="s">
-        <v>387</v>
+        <v>106</v>
       </c>
       <c r="P132" t="s">
         <v>386</v>
@@ -9945,7 +9945,7 @@
         <v>34</v>
       </c>
       <c r="E133" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F133" t="s">
         <v>203</v>
@@ -9954,10 +9954,10 @@
         <v>41</v>
       </c>
       <c r="H133" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I133" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J133" t="s">
         <v>66</v>
@@ -9966,7 +9966,7 @@
         <v>66</v>
       </c>
       <c r="L133" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M133" t="s">
         <v>336</v>
@@ -9975,10 +9975,10 @@
         <v>47</v>
       </c>
       <c r="O133" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="P133" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q133" t="s">
         <v>47</v>
@@ -10004,25 +10004,25 @@
         <v>390</v>
       </c>
       <c r="F134" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G134" t="s">
         <v>41</v>
       </c>
       <c r="H134" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I134" t="s">
         <v>391</v>
       </c>
       <c r="J134" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="K134" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="L134" t="s">
-        <v>34</v>
+        <v>344</v>
       </c>
       <c r="M134" t="s">
         <v>336</v>
@@ -10031,7 +10031,7 @@
         <v>47</v>
       </c>
       <c r="O134" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="P134" t="s">
         <v>391</v>
@@ -10057,7 +10057,7 @@
         <v>34</v>
       </c>
       <c r="E135" t="s">
-        <v>240</v>
+        <v>392</v>
       </c>
       <c r="F135" t="s">
         <v>199</v>
@@ -10066,16 +10066,16 @@
         <v>41</v>
       </c>
       <c r="H135" t="s">
+        <v>342</v>
+      </c>
+      <c r="I135" t="s">
         <v>393</v>
       </c>
-      <c r="I135" t="s">
-        <v>394</v>
-      </c>
       <c r="J135" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="K135" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="L135" t="s">
         <v>34</v>
@@ -10087,10 +10087,10 @@
         <v>47</v>
       </c>
       <c r="O135" t="s">
-        <v>130</v>
+        <v>394</v>
       </c>
       <c r="P135" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q135" t="s">
         <v>47</v>
@@ -10113,7 +10113,7 @@
         <v>34</v>
       </c>
       <c r="E136" t="s">
-        <v>395</v>
+        <v>240</v>
       </c>
       <c r="F136" t="s">
         <v>199</v>
@@ -10122,16 +10122,16 @@
         <v>41</v>
       </c>
       <c r="H136" t="s">
-        <v>343</v>
+        <v>395</v>
       </c>
       <c r="I136" t="s">
         <v>396</v>
       </c>
       <c r="J136" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="K136" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="L136" t="s">
         <v>34</v>
@@ -10143,7 +10143,7 @@
         <v>47</v>
       </c>
       <c r="O136" t="s">
-        <v>351</v>
+        <v>130</v>
       </c>
       <c r="P136" t="s">
         <v>396</v>
@@ -10169,7 +10169,7 @@
         <v>34</v>
       </c>
       <c r="E137" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F137" t="s">
         <v>199</v>
@@ -10178,10 +10178,10 @@
         <v>41</v>
       </c>
       <c r="H137" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I137" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J137" t="s">
         <v>66</v>
@@ -10199,10 +10199,10 @@
         <v>47</v>
       </c>
       <c r="O137" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P137" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q137" t="s">
         <v>47</v>
@@ -10225,7 +10225,7 @@
         <v>34</v>
       </c>
       <c r="E138" t="s">
-        <v>101</v>
+        <v>397</v>
       </c>
       <c r="F138" t="s">
         <v>199</v>
@@ -10234,16 +10234,16 @@
         <v>41</v>
       </c>
       <c r="H138" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I138" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J138" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="K138" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="L138" t="s">
         <v>34</v>
@@ -10255,10 +10255,10 @@
         <v>47</v>
       </c>
       <c r="O138" t="s">
-        <v>103</v>
+        <v>353</v>
       </c>
       <c r="P138" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q138" t="s">
         <v>47</v>
@@ -10281,7 +10281,7 @@
         <v>34</v>
       </c>
       <c r="E139" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="F139" t="s">
         <v>199</v>
@@ -10290,16 +10290,16 @@
         <v>41</v>
       </c>
       <c r="H139" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I139" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J139" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="K139" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="L139" t="s">
         <v>34</v>
@@ -10311,10 +10311,10 @@
         <v>47</v>
       </c>
       <c r="O139" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="P139" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q139" t="s">
         <v>47</v>
@@ -10337,7 +10337,7 @@
         <v>34</v>
       </c>
       <c r="E140" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="F140" t="s">
         <v>199</v>
@@ -10346,16 +10346,16 @@
         <v>41</v>
       </c>
       <c r="H140" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I140" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J140" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="K140" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L140" t="s">
         <v>34</v>
@@ -10367,10 +10367,10 @@
         <v>47</v>
       </c>
       <c r="O140" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="P140" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q140" t="s">
         <v>47</v>
@@ -10402,10 +10402,10 @@
         <v>41</v>
       </c>
       <c r="H141" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I141" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J141" t="s">
         <v>57</v>
@@ -10426,7 +10426,7 @@
         <v>83</v>
       </c>
       <c r="P141" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q141" t="s">
         <v>47</v>
@@ -10449,7 +10449,7 @@
         <v>34</v>
       </c>
       <c r="E142" t="s">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="F142" t="s">
         <v>199</v>
@@ -10458,16 +10458,16 @@
         <v>41</v>
       </c>
       <c r="H142" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I142" t="s">
         <v>403</v>
       </c>
       <c r="J142" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="K142" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L142" t="s">
         <v>34</v>
@@ -10479,7 +10479,7 @@
         <v>47</v>
       </c>
       <c r="O142" t="s">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="P142" t="s">
         <v>403</v>
@@ -10514,7 +10514,7 @@
         <v>41</v>
       </c>
       <c r="H143" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I143" t="s">
         <v>405</v>
@@ -10535,7 +10535,7 @@
         <v>47</v>
       </c>
       <c r="O143" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P143" t="s">
         <v>405</v>
@@ -10561,7 +10561,7 @@
         <v>34</v>
       </c>
       <c r="E144" t="s">
-        <v>101</v>
+        <v>406</v>
       </c>
       <c r="F144" t="s">
         <v>199</v>
@@ -10570,16 +10570,16 @@
         <v>41</v>
       </c>
       <c r="H144" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J144" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="K144" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="L144" t="s">
         <v>34</v>
@@ -10591,10 +10591,10 @@
         <v>47</v>
       </c>
       <c r="O144" t="s">
-        <v>103</v>
+        <v>353</v>
       </c>
       <c r="P144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q144" t="s">
         <v>47</v>
@@ -10617,7 +10617,7 @@
         <v>34</v>
       </c>
       <c r="E145" t="s">
-        <v>407</v>
+        <v>101</v>
       </c>
       <c r="F145" t="s">
         <v>199</v>
@@ -10626,7 +10626,7 @@
         <v>41</v>
       </c>
       <c r="H145" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I145" t="s">
         <v>408</v>
@@ -11095,7 +11095,7 @@
         <v>47</v>
       </c>
       <c r="O153" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P153" t="s">
         <v>421</v>
@@ -11263,7 +11263,7 @@
         <v>47</v>
       </c>
       <c r="O156" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P156" t="s">
         <v>424</v>
@@ -11319,7 +11319,7 @@
         <v>47</v>
       </c>
       <c r="O157" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P157" t="s">
         <v>425</v>
@@ -11431,7 +11431,7 @@
         <v>47</v>
       </c>
       <c r="O159" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="P159" t="s">
         <v>428</v>
@@ -12439,7 +12439,7 @@
         <v>47</v>
       </c>
       <c r="O177" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="P177" t="s">
         <v>428</v>
@@ -12607,7 +12607,7 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P180" t="s">
         <v>421</v>
@@ -13055,7 +13055,7 @@
         <v>47</v>
       </c>
       <c r="O188" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P188" t="s">
         <v>425</v>
@@ -13111,7 +13111,7 @@
         <v>47</v>
       </c>
       <c r="O189" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P189" t="s">
         <v>424</v>
@@ -13223,7 +13223,7 @@
         <v>47</v>
       </c>
       <c r="O191" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P191" t="s">
         <v>471</v>
@@ -13335,7 +13335,7 @@
         <v>47</v>
       </c>
       <c r="O193" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="P193" t="s">
         <v>473</v>
@@ -13447,7 +13447,7 @@
         <v>47</v>
       </c>
       <c r="O195" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P195" t="s">
         <v>475</v>
@@ -13727,7 +13727,7 @@
         <v>47</v>
       </c>
       <c r="O200" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P200" t="s">
         <v>480</v>
@@ -13951,7 +13951,7 @@
         <v>47</v>
       </c>
       <c r="O204" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="P204" t="s">
         <v>484</v>
@@ -14063,7 +14063,7 @@
         <v>47</v>
       </c>
       <c r="O206" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P206" t="s">
         <v>486</v>
@@ -14119,7 +14119,7 @@
         <v>47</v>
       </c>
       <c r="O207" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P207" t="s">
         <v>487</v>
@@ -14399,7 +14399,7 @@
         <v>47</v>
       </c>
       <c r="O212" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P212" t="s">
         <v>494</v>
@@ -15015,7 +15015,7 @@
         <v>47</v>
       </c>
       <c r="O223" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P223" t="s">
         <v>510</v>
@@ -15071,7 +15071,7 @@
         <v>47</v>
       </c>
       <c r="O224" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P224" t="s">
         <v>511</v>
@@ -15407,7 +15407,7 @@
         <v>47</v>
       </c>
       <c r="O230" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P230" t="s">
         <v>520</v>
@@ -15631,7 +15631,7 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P234" t="s">
         <v>528</v>
@@ -15911,7 +15911,7 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P239" t="s">
         <v>538</v>
@@ -15937,7 +15937,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F240" t="s">
         <v>500</v>
@@ -15993,7 +15993,7 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F241" t="s">
         <v>500</v>
@@ -16049,7 +16049,7 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F242" t="s">
         <v>500</v>
@@ -16609,7 +16609,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F252" t="s">
         <v>199</v>
@@ -16639,7 +16639,7 @@
         <v>47</v>
       </c>
       <c r="O252" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P252" t="s">
         <v>556</v>
@@ -16695,7 +16695,7 @@
         <v>47</v>
       </c>
       <c r="O253" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P253" t="s">
         <v>251</v>
@@ -16751,7 +16751,7 @@
         <v>47</v>
       </c>
       <c r="O254" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P254" t="s">
         <v>559</v>
@@ -16898,7 +16898,7 @@
         <v>41</v>
       </c>
       <c r="H257" t="s">
-        <v>493</v>
+        <v>417</v>
       </c>
       <c r="I257" t="s">
         <v>566</v>
@@ -16954,7 +16954,7 @@
         <v>41</v>
       </c>
       <c r="H258" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="I258" t="s">
         <v>567</v>
@@ -17729,7 +17729,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F272" t="s">
         <v>199</v>
@@ -17759,7 +17759,7 @@
         <v>47</v>
       </c>
       <c r="O272" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P272" t="s">
         <v>598</v>
@@ -18289,10 +18289,10 @@
         <v>33</v>
       </c>
       <c r="E282" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="F282" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
@@ -18319,7 +18319,7 @@
         <v>47</v>
       </c>
       <c r="O282" t="s">
-        <v>387</v>
+        <v>622</v>
       </c>
       <c r="P282" t="s">
         <v>621</v>
@@ -18345,7 +18345,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F283" t="s">
         <v>199</v>
@@ -18375,7 +18375,7 @@
         <v>47</v>
       </c>
       <c r="O283" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P283" t="s">
         <v>621</v>
@@ -18401,7 +18401,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F284" t="s">
         <v>173</v>
@@ -18416,10 +18416,10 @@
         <v>621</v>
       </c>
       <c r="J284" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K284" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="L284" t="s">
         <v>34</v>
@@ -18431,7 +18431,7 @@
         <v>47</v>
       </c>
       <c r="O284" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="P284" t="s">
         <v>621</v>
@@ -18457,7 +18457,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="F285" t="s">
         <v>173</v>
@@ -18472,10 +18472,10 @@
         <v>621</v>
       </c>
       <c r="J285" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K285" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18487,7 +18487,7 @@
         <v>47</v>
       </c>
       <c r="O285" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="P285" t="s">
         <v>621</v>
@@ -18513,10 +18513,10 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="F286" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
@@ -18528,10 +18528,10 @@
         <v>621</v>
       </c>
       <c r="J286" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="K286" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -18543,7 +18543,7 @@
         <v>47</v>
       </c>
       <c r="O286" t="s">
-        <v>103</v>
+        <v>353</v>
       </c>
       <c r="P286" t="s">
         <v>621</v>
@@ -18569,7 +18569,7 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="F287" t="s">
         <v>173</v>
@@ -18599,7 +18599,7 @@
         <v>47</v>
       </c>
       <c r="O287" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="P287" t="s">
         <v>621</v>
@@ -18625,10 +18625,10 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F288" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="G288" t="s">
         <v>41</v>
@@ -18640,10 +18640,10 @@
         <v>621</v>
       </c>
       <c r="J288" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K288" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18655,7 +18655,7 @@
         <v>47</v>
       </c>
       <c r="O288" t="s">
-        <v>622</v>
+        <v>106</v>
       </c>
       <c r="P288" t="s">
         <v>621</v>
@@ -18681,7 +18681,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F289" t="s">
         <v>173</v>
@@ -18696,10 +18696,10 @@
         <v>621</v>
       </c>
       <c r="J289" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="K289" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="L289" t="s">
         <v>34</v>
@@ -18711,7 +18711,7 @@
         <v>47</v>
       </c>
       <c r="O289" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="P289" t="s">
         <v>621</v>
@@ -18737,10 +18737,10 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="F290" t="s">
-        <v>284</v>
+        <v>199</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
@@ -18752,10 +18752,10 @@
         <v>621</v>
       </c>
       <c r="J290" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="K290" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L290" t="s">
         <v>34</v>
@@ -18767,13 +18767,13 @@
         <v>47</v>
       </c>
       <c r="O290" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="P290" t="s">
-        <v>34</v>
+        <v>621</v>
       </c>
       <c r="Q290" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R290" t="s">
         <v>34</v>
@@ -18793,10 +18793,10 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="F291" t="s">
-        <v>173</v>
+        <v>284</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
@@ -18808,10 +18808,10 @@
         <v>621</v>
       </c>
       <c r="J291" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="K291" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="L291" t="s">
         <v>34</v>
@@ -18823,13 +18823,13 @@
         <v>47</v>
       </c>
       <c r="O291" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="P291" t="s">
-        <v>621</v>
+        <v>34</v>
       </c>
       <c r="Q291" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R291" t="s">
         <v>34</v>
@@ -18849,10 +18849,10 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>213</v>
+        <v>499</v>
       </c>
       <c r="F292" t="s">
-        <v>173</v>
+        <v>284</v>
       </c>
       <c r="G292" t="s">
         <v>41</v>
@@ -18864,10 +18864,10 @@
         <v>621</v>
       </c>
       <c r="J292" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="K292" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="L292" t="s">
         <v>34</v>
@@ -18879,13 +18879,13 @@
         <v>47</v>
       </c>
       <c r="O292" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="P292" t="s">
-        <v>621</v>
+        <v>34</v>
       </c>
       <c r="Q292" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R292" t="s">
         <v>34</v>
@@ -18961,10 +18961,10 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>499</v>
+        <v>213</v>
       </c>
       <c r="F294" t="s">
-        <v>284</v>
+        <v>173</v>
       </c>
       <c r="G294" t="s">
         <v>41</v>
@@ -18976,10 +18976,10 @@
         <v>621</v>
       </c>
       <c r="J294" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="K294" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="L294" t="s">
         <v>34</v>
@@ -18991,13 +18991,13 @@
         <v>47</v>
       </c>
       <c r="O294" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="P294" t="s">
-        <v>34</v>
+        <v>621</v>
       </c>
       <c r="Q294" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R294" t="s">
         <v>34</v>
@@ -19633,7 +19633,7 @@
         <v>34</v>
       </c>
       <c r="E306" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F306" t="s">
         <v>173</v>
@@ -19642,16 +19642,16 @@
         <v>41</v>
       </c>
       <c r="H306" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I306" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J306" t="s">
-        <v>660</v>
+        <v>182</v>
       </c>
       <c r="K306" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="L306" t="s">
         <v>661</v>
@@ -19666,7 +19666,7 @@
         <v>156</v>
       </c>
       <c r="P306" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Q306" t="s">
         <v>47</v>
@@ -19689,7 +19689,7 @@
         <v>34</v>
       </c>
       <c r="E307" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="F307" t="s">
         <v>173</v>
@@ -19698,16 +19698,16 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
+        <v>662</v>
+      </c>
+      <c r="I307" t="s">
         <v>663</v>
       </c>
-      <c r="I307" t="s">
+      <c r="J307" t="s">
         <v>664</v>
       </c>
-      <c r="J307" t="s">
-        <v>182</v>
-      </c>
       <c r="K307" t="s">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="L307" t="s">
         <v>665</v>
@@ -19722,7 +19722,7 @@
         <v>156</v>
       </c>
       <c r="P307" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="Q307" t="s">
         <v>47</v>
@@ -19928,7 +19928,7 @@
         <v>673</v>
       </c>
       <c r="J311" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K311" t="s">
         <v>86</v>
@@ -20137,7 +20137,7 @@
         <v>34</v>
       </c>
       <c r="E315" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F315" t="s">
         <v>173</v>
@@ -20208,7 +20208,7 @@
         <v>686</v>
       </c>
       <c r="J316" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K316" t="s">
         <v>86</v>
@@ -20488,7 +20488,7 @@
         <v>698</v>
       </c>
       <c r="J321" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K321" t="s">
         <v>86</v>
@@ -20544,7 +20544,7 @@
         <v>673</v>
       </c>
       <c r="J322" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K322" t="s">
         <v>86</v>
@@ -20600,7 +20600,7 @@
         <v>686</v>
       </c>
       <c r="J323" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K323" t="s">
         <v>86</v>
@@ -20712,7 +20712,7 @@
         <v>708</v>
       </c>
       <c r="J325" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K325" t="s">
         <v>86</v>
@@ -20880,7 +20880,7 @@
         <v>714</v>
       </c>
       <c r="J328" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K328" t="s">
         <v>86</v>
@@ -21042,10 +21042,10 @@
         <v>41</v>
       </c>
       <c r="H331" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I331" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J331" t="s">
         <v>176</v>
@@ -21066,7 +21066,7 @@
         <v>156</v>
       </c>
       <c r="P331" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="Q331" t="s">
         <v>47</v>
@@ -21154,10 +21154,10 @@
         <v>41</v>
       </c>
       <c r="H333" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I333" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J333" t="s">
         <v>176</v>
@@ -21178,7 +21178,7 @@
         <v>156</v>
       </c>
       <c r="P333" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="Q333" t="s">
         <v>47</v>
@@ -21776,7 +21776,7 @@
         <v>756</v>
       </c>
       <c r="J344" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K344" t="s">
         <v>247</v>
@@ -21826,7 +21826,7 @@
         <v>41</v>
       </c>
       <c r="H345" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I345" t="s">
         <v>761</v>
@@ -22056,7 +22056,7 @@
         <v>774</v>
       </c>
       <c r="J349" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K349" t="s">
         <v>86</v>
@@ -22224,7 +22224,7 @@
         <v>786</v>
       </c>
       <c r="J352" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K352" t="s">
         <v>75</v>
@@ -22392,7 +22392,7 @@
         <v>795</v>
       </c>
       <c r="J355" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K355" t="s">
         <v>247</v>
@@ -22507,7 +22507,7 @@
         <v>275</v>
       </c>
       <c r="K357" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="L357" t="s">
         <v>803</v>
@@ -22619,7 +22619,7 @@
         <v>275</v>
       </c>
       <c r="K359" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="L359" t="s">
         <v>811</v>
@@ -22896,7 +22896,7 @@
         <v>828</v>
       </c>
       <c r="J364" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K364" t="s">
         <v>86</v>
@@ -23114,19 +23114,19 @@
         <v>41</v>
       </c>
       <c r="H368" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="I368" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J368" t="s">
         <v>294</v>
       </c>
       <c r="K368" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="L368" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="M368" t="s">
         <v>843</v>
@@ -23138,7 +23138,7 @@
         <v>156</v>
       </c>
       <c r="P368" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="Q368" t="s">
         <v>47</v>
@@ -23170,7 +23170,7 @@
         <v>41</v>
       </c>
       <c r="H369" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="I369" t="s">
         <v>847</v>
@@ -23179,7 +23179,7 @@
         <v>294</v>
       </c>
       <c r="K369" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="L369" t="s">
         <v>848</v>
@@ -23232,13 +23232,13 @@
         <v>851</v>
       </c>
       <c r="J370" t="s">
-        <v>817</v>
+        <v>852</v>
       </c>
       <c r="K370" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="L370" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="M370" t="s">
         <v>843</v>
@@ -23273,7 +23273,7 @@
         <v>34</v>
       </c>
       <c r="E371" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="F371" t="s">
         <v>173</v>
@@ -23282,16 +23282,16 @@
         <v>41</v>
       </c>
       <c r="H371" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="I371" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J371" t="s">
-        <v>855</v>
+        <v>247</v>
       </c>
       <c r="K371" t="s">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="L371" t="s">
         <v>856</v>
@@ -23306,7 +23306,7 @@
         <v>156</v>
       </c>
       <c r="P371" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="Q371" t="s">
         <v>47</v>
@@ -23400,13 +23400,13 @@
         <v>861</v>
       </c>
       <c r="J373" t="s">
-        <v>247</v>
+        <v>862</v>
       </c>
       <c r="K373" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L373" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M373" t="s">
         <v>843</v>
@@ -23441,7 +23441,7 @@
         <v>34</v>
       </c>
       <c r="E374" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F374" t="s">
         <v>173</v>
@@ -23450,19 +23450,19 @@
         <v>41</v>
       </c>
       <c r="H374" t="s">
-        <v>838</v>
+        <v>865</v>
       </c>
       <c r="I374" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="J374" t="s">
-        <v>865</v>
+        <v>817</v>
       </c>
       <c r="K374" t="s">
         <v>86</v>
       </c>
       <c r="L374" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="M374" t="s">
         <v>843</v>
@@ -23474,7 +23474,7 @@
         <v>156</v>
       </c>
       <c r="P374" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="Q374" t="s">
         <v>47</v>
@@ -23792,7 +23792,7 @@
         <v>887</v>
       </c>
       <c r="J380" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K380" t="s">
         <v>86</v>
@@ -24016,7 +24016,7 @@
         <v>905</v>
       </c>
       <c r="J384" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K384" t="s">
         <v>86</v>
@@ -24128,7 +24128,7 @@
         <v>913</v>
       </c>
       <c r="J386" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="K386" t="s">
         <v>86</v>
@@ -24281,7 +24281,7 @@
         <v>33</v>
       </c>
       <c r="E389" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F389" t="s">
         <v>173</v>
@@ -24844,7 +24844,7 @@
         <v>445</v>
       </c>
       <c r="F399" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G399" t="s">
         <v>41</v>
@@ -24900,7 +24900,7 @@
         <v>202</v>
       </c>
       <c r="F400" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G400" t="s">
         <v>41</v>
@@ -24983,7 +24983,7 @@
         <v>47</v>
       </c>
       <c r="O401" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="P401" t="s">
         <v>944</v>
@@ -25151,7 +25151,7 @@
         <v>47</v>
       </c>
       <c r="O404" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P404" t="s">
         <v>947</v>
@@ -25319,7 +25319,7 @@
         <v>47</v>
       </c>
       <c r="O407" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P407" t="s">
         <v>951</v>

--- a/xlsx/dre/DRE_05_2026.xlsx
+++ b/xlsx/dre/DRE_05_2026.xlsx
@@ -513,7 +513,7 @@
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 464.076,75</t>
+    <t>R$ 463.971,63</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -1765,9 +1765,93 @@
     <t>Uber</t>
   </si>
   <si>
+    <t>R$  10,24</t>
+  </si>
+  <si>
     <t>R$  23,08</t>
   </si>
   <si>
+    <t>76901U/0</t>
+  </si>
+  <si>
+    <t>R$  22,50</t>
+  </si>
+  <si>
+    <t>R$  26,94</t>
+  </si>
+  <si>
+    <t>R$  50,44</t>
+  </si>
+  <si>
+    <t>ADM/0</t>
+  </si>
+  <si>
+    <t>R$  122,15</t>
+  </si>
+  <si>
+    <t>46201UB/0</t>
+  </si>
+  <si>
+    <t>R$  27,08</t>
+  </si>
+  <si>
+    <t>46201ANGELASC</t>
+  </si>
+  <si>
+    <t>29901/0</t>
+  </si>
+  <si>
+    <t>R$  64,87</t>
+  </si>
+  <si>
+    <t>29901FL8</t>
+  </si>
+  <si>
+    <t>30301/0</t>
+  </si>
+  <si>
+    <t>R$  14,43</t>
+  </si>
+  <si>
+    <t>30301GiseleO</t>
+  </si>
+  <si>
+    <t>40701U/0</t>
+  </si>
+  <si>
+    <t>R$  14,51</t>
+  </si>
+  <si>
+    <t>40701julianMac</t>
+  </si>
+  <si>
+    <t>48101/0</t>
+  </si>
+  <si>
+    <t>R$  55,10</t>
+  </si>
+  <si>
+    <t>48101AngelaFCJ</t>
+  </si>
+  <si>
+    <t>39801/0</t>
+  </si>
+  <si>
+    <t>R$  13,97</t>
+  </si>
+  <si>
+    <t>39801CleaRH</t>
+  </si>
+  <si>
+    <t>47101u/0</t>
+  </si>
+  <si>
+    <t>R$  12,93</t>
+  </si>
+  <si>
+    <t>47101MarciaOA</t>
+  </si>
+  <si>
     <t>29201/0</t>
   </si>
   <si>
@@ -1777,88 +1861,7 @@
     <t>29201LuizAMB</t>
   </si>
   <si>
-    <t>29901/0</t>
-  </si>
-  <si>
-    <t>R$  64,87</t>
-  </si>
-  <si>
-    <t>29901FL8</t>
-  </si>
-  <si>
     <t>R$  63,76</t>
-  </si>
-  <si>
-    <t>76901U/0</t>
-  </si>
-  <si>
-    <t>R$  22,50</t>
-  </si>
-  <si>
-    <t>30301/0</t>
-  </si>
-  <si>
-    <t>R$  14,43</t>
-  </si>
-  <si>
-    <t>30301GiseleO</t>
-  </si>
-  <si>
-    <t>40701U/0</t>
-  </si>
-  <si>
-    <t>R$  14,51</t>
-  </si>
-  <si>
-    <t>40701julianMac</t>
-  </si>
-  <si>
-    <t>48101/0</t>
-  </si>
-  <si>
-    <t>R$  55,10</t>
-  </si>
-  <si>
-    <t>48101AngelaFCJ</t>
-  </si>
-  <si>
-    <t>R$  26,94</t>
-  </si>
-  <si>
-    <t>39801/0</t>
-  </si>
-  <si>
-    <t>R$  13,97</t>
-  </si>
-  <si>
-    <t>39801CleaRH</t>
-  </si>
-  <si>
-    <t>R$  50,44</t>
-  </si>
-  <si>
-    <t>ADM/0</t>
-  </si>
-  <si>
-    <t>R$  122,15</t>
-  </si>
-  <si>
-    <t>46201UB/0</t>
-  </si>
-  <si>
-    <t>R$  27,08</t>
-  </si>
-  <si>
-    <t>46201ANGELASC</t>
-  </si>
-  <si>
-    <t>47101u/0</t>
-  </si>
-  <si>
-    <t>R$  12,93</t>
-  </si>
-  <si>
-    <t>47101MarciaOA</t>
   </si>
   <si>
     <t>676/1</t>
@@ -1874,9 +1877,6 @@
 </t>
   </si>
   <si>
-    <t>R$  10,24</t>
-  </si>
-  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -2830,7 +2830,7 @@
     <t>4.07 DESPESAS FINANCEIRAS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 36.552,49</t>
+    <t>R$ 36.447,37</t>
   </si>
   <si>
     <t>4.07.01 DESPESAS FINANCEIRAS VARIÁVEIS</t>
@@ -2842,27 +2842,27 @@
     <t>4.07.01.01.01 Operações financeiras - desconto de cheques (financeiras)</t>
   </si>
   <si>
+    <t>PAGSEGURO</t>
+  </si>
+  <si>
+    <t>R$  127,47</t>
+  </si>
+  <si>
+    <t>Título referente a Valor da Taxa Financeira</t>
+  </si>
+  <si>
+    <t>R$  191,16</t>
+  </si>
+  <si>
     <t>Italíneacredi</t>
   </si>
   <si>
     <t>R$  3.395,90</t>
   </si>
   <si>
-    <t>Título referente a Valor da Taxa Financeira</t>
-  </si>
-  <si>
-    <t>PAGSEGURO</t>
-  </si>
-  <si>
     <t>R$  93,39</t>
   </si>
   <si>
-    <t>R$  194,09</t>
-  </si>
-  <si>
-    <t>R$  229,66</t>
-  </si>
-  <si>
     <t>R$  11.602,27</t>
   </si>
   <si>
@@ -3058,7 +3058,7 @@
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 36.559,19</t>
+    <t>R$ 36.454,07</t>
   </si>
   <si>
     <t>7.08.01 Despesas e receitas financeiras fixas</t>
@@ -3076,7 +3076,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ -3.167,69</t>
+    <t>R$ -3.062,57</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -3091,7 +3091,7 @@
     <t>7.50.02 TOTAL DOS CUSTOS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 380.696,19</t>
+    <t>R$ 380.591,07</t>
   </si>
   <si>
     <t>7.50.02.01 Deduções de receita</t>
@@ -3124,13 +3124,13 @@
     <t>7.60.02 TOTAL DE VENDAS - VALOR À VISTA</t>
   </si>
   <si>
-    <t>R$ 424.356,57</t>
+    <t>R$ 424.461,69</t>
   </si>
   <si>
     <t>7.60.03 TOTAL DE VENDAS - VALOR LÍQUIDO</t>
   </si>
   <si>
-    <t>R$ 417.676,60</t>
+    <t>R$ 417.781,72</t>
   </si>
   <si>
     <t>7.60.06 CUSTO DAS VENDAS - MERCADORIA</t>
@@ -3157,7 +3157,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 479.110,84</t>
+    <t>R$ 478.483,78</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>
@@ -17281,7 +17281,7 @@
         <v>33</v>
       </c>
       <c r="E264" t="s">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="F264" t="s">
         <v>199</v>
@@ -17296,10 +17296,10 @@
         <v>579</v>
       </c>
       <c r="J264" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="K264" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="L264" t="s">
         <v>34</v>
@@ -17311,7 +17311,7 @@
         <v>47</v>
       </c>
       <c r="O264" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="P264" t="s">
         <v>579</v>
@@ -17337,7 +17337,7 @@
         <v>34</v>
       </c>
       <c r="E265" t="s">
-        <v>580</v>
+        <v>81</v>
       </c>
       <c r="F265" t="s">
         <v>199</v>
@@ -17349,13 +17349,13 @@
         <v>578</v>
       </c>
       <c r="I265" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J265" t="s">
-        <v>275</v>
+        <v>57</v>
       </c>
       <c r="K265" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="L265" t="s">
         <v>34</v>
@@ -17367,10 +17367,10 @@
         <v>47</v>
       </c>
       <c r="O265" t="s">
-        <v>582</v>
+        <v>83</v>
       </c>
       <c r="P265" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q265" t="s">
         <v>47</v>
@@ -17393,7 +17393,7 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F266" t="s">
         <v>199</v>
@@ -17405,13 +17405,13 @@
         <v>578</v>
       </c>
       <c r="I266" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J266" t="s">
-        <v>275</v>
+        <v>86</v>
       </c>
       <c r="K266" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="L266" t="s">
         <v>34</v>
@@ -17423,10 +17423,10 @@
         <v>47</v>
       </c>
       <c r="O266" t="s">
-        <v>585</v>
+        <v>103</v>
       </c>
       <c r="P266" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Q266" t="s">
         <v>47</v>
@@ -17449,7 +17449,7 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>71</v>
+        <v>397</v>
       </c>
       <c r="F267" t="s">
         <v>199</v>
@@ -17461,13 +17461,13 @@
         <v>578</v>
       </c>
       <c r="I267" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="J267" t="s">
-        <v>518</v>
+        <v>66</v>
       </c>
       <c r="K267" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="L267" t="s">
         <v>34</v>
@@ -17479,10 +17479,10 @@
         <v>47</v>
       </c>
       <c r="O267" t="s">
-        <v>76</v>
+        <v>353</v>
       </c>
       <c r="P267" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="Q267" t="s">
         <v>47</v>
@@ -17505,7 +17505,7 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>587</v>
+        <v>135</v>
       </c>
       <c r="F268" t="s">
         <v>199</v>
@@ -17517,13 +17517,13 @@
         <v>578</v>
       </c>
       <c r="I268" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="J268" t="s">
-        <v>86</v>
+        <v>518</v>
       </c>
       <c r="K268" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="L268" t="s">
         <v>34</v>
@@ -17535,10 +17535,10 @@
         <v>47</v>
       </c>
       <c r="O268" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="P268" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="Q268" t="s">
         <v>47</v>
@@ -17561,7 +17561,7 @@
         <v>34</v>
       </c>
       <c r="E269" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F269" t="s">
         <v>199</v>
@@ -17573,7 +17573,7 @@
         <v>578</v>
       </c>
       <c r="I269" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="J269" t="s">
         <v>275</v>
@@ -17591,10 +17591,10 @@
         <v>47</v>
       </c>
       <c r="O269" t="s">
-        <v>591</v>
+        <v>156</v>
       </c>
       <c r="P269" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="Q269" t="s">
         <v>47</v>
@@ -17617,7 +17617,7 @@
         <v>34</v>
       </c>
       <c r="E270" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F270" t="s">
         <v>199</v>
@@ -17629,13 +17629,13 @@
         <v>578</v>
       </c>
       <c r="I270" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="J270" t="s">
         <v>275</v>
       </c>
       <c r="K270" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L270" t="s">
         <v>34</v>
@@ -17647,10 +17647,10 @@
         <v>47</v>
       </c>
       <c r="O270" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="P270" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="Q270" t="s">
         <v>47</v>
@@ -17673,7 +17673,7 @@
         <v>34</v>
       </c>
       <c r="E271" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F271" t="s">
         <v>199</v>
@@ -17685,7 +17685,7 @@
         <v>578</v>
       </c>
       <c r="I271" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="J271" t="s">
         <v>275</v>
@@ -17703,10 +17703,10 @@
         <v>47</v>
       </c>
       <c r="O271" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="P271" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="Q271" t="s">
         <v>47</v>
@@ -17729,7 +17729,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>397</v>
+        <v>593</v>
       </c>
       <c r="F272" t="s">
         <v>199</v>
@@ -17741,13 +17741,13 @@
         <v>578</v>
       </c>
       <c r="I272" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="J272" t="s">
-        <v>66</v>
+        <v>275</v>
       </c>
       <c r="K272" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="L272" t="s">
         <v>34</v>
@@ -17759,10 +17759,10 @@
         <v>47</v>
       </c>
       <c r="O272" t="s">
-        <v>353</v>
+        <v>595</v>
       </c>
       <c r="P272" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="Q272" t="s">
         <v>47</v>
@@ -17785,7 +17785,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F273" t="s">
         <v>199</v>
@@ -17797,7 +17797,7 @@
         <v>578</v>
       </c>
       <c r="I273" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="J273" t="s">
         <v>275</v>
@@ -17815,10 +17815,10 @@
         <v>47</v>
       </c>
       <c r="O273" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="P273" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -17841,7 +17841,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>135</v>
+        <v>599</v>
       </c>
       <c r="F274" t="s">
         <v>199</v>
@@ -17853,13 +17853,13 @@
         <v>578</v>
       </c>
       <c r="I274" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J274" t="s">
-        <v>518</v>
+        <v>275</v>
       </c>
       <c r="K274" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="L274" t="s">
         <v>34</v>
@@ -17871,10 +17871,10 @@
         <v>47</v>
       </c>
       <c r="O274" t="s">
-        <v>138</v>
+        <v>601</v>
       </c>
       <c r="P274" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="Q274" t="s">
         <v>47</v>
@@ -17897,7 +17897,7 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F275" t="s">
         <v>199</v>
@@ -17909,7 +17909,7 @@
         <v>578</v>
       </c>
       <c r="I275" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J275" t="s">
         <v>275</v>
@@ -17927,10 +17927,10 @@
         <v>47</v>
       </c>
       <c r="O275" t="s">
-        <v>156</v>
+        <v>604</v>
       </c>
       <c r="P275" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q275" t="s">
         <v>47</v>
@@ -17971,7 +17971,7 @@
         <v>275</v>
       </c>
       <c r="K276" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L276" t="s">
         <v>34</v>
@@ -18065,7 +18065,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>611</v>
+        <v>71</v>
       </c>
       <c r="F278" t="s">
         <v>199</v>
@@ -18074,19 +18074,19 @@
         <v>41</v>
       </c>
       <c r="H278" t="s">
-        <v>612</v>
+        <v>578</v>
       </c>
       <c r="I278" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J278" t="s">
-        <v>275</v>
+        <v>518</v>
       </c>
       <c r="K278" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="L278" t="s">
-        <v>614</v>
+        <v>34</v>
       </c>
       <c r="M278" t="s">
         <v>577</v>
@@ -18095,10 +18095,10 @@
         <v>47</v>
       </c>
       <c r="O278" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="P278" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="Q278" t="s">
         <v>47</v>
@@ -18121,7 +18121,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>249</v>
+        <v>612</v>
       </c>
       <c r="F279" t="s">
         <v>199</v>
@@ -18130,19 +18130,19 @@
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="I279" t="s">
+        <v>614</v>
+      </c>
+      <c r="J279" t="s">
+        <v>275</v>
+      </c>
+      <c r="K279" t="s">
+        <v>126</v>
+      </c>
+      <c r="L279" t="s">
         <v>615</v>
-      </c>
-      <c r="J279" t="s">
-        <v>120</v>
-      </c>
-      <c r="K279" t="s">
-        <v>120</v>
-      </c>
-      <c r="L279" t="s">
-        <v>34</v>
       </c>
       <c r="M279" t="s">
         <v>577</v>
@@ -18151,10 +18151,10 @@
         <v>47</v>
       </c>
       <c r="O279" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="P279" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="Q279" t="s">
         <v>47</v>
@@ -24729,7 +24729,7 @@
         <v>33</v>
       </c>
       <c r="E397" t="s">
-        <v>211</v>
+        <v>445</v>
       </c>
       <c r="F397" t="s">
         <v>203</v>
@@ -24744,10 +24744,10 @@
         <v>938</v>
       </c>
       <c r="J397" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="K397" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="L397" t="s">
         <v>939</v>
@@ -24759,7 +24759,7 @@
         <v>47</v>
       </c>
       <c r="O397" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="P397" t="s">
         <v>938</v>
@@ -24785,7 +24785,7 @@
         <v>34</v>
       </c>
       <c r="E398" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F398" t="s">
         <v>203</v>
@@ -24794,16 +24794,16 @@
         <v>41</v>
       </c>
       <c r="H398" t="s">
+        <v>937</v>
+      </c>
+      <c r="I398" t="s">
         <v>940</v>
       </c>
-      <c r="I398" t="s">
-        <v>941</v>
-      </c>
       <c r="J398" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K398" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="L398" t="s">
         <v>939</v>
@@ -24815,10 +24815,10 @@
         <v>47</v>
       </c>
       <c r="O398" t="s">
-        <v>490</v>
+        <v>206</v>
       </c>
       <c r="P398" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="Q398" t="s">
         <v>47</v>
@@ -24841,25 +24841,25 @@
         <v>34</v>
       </c>
       <c r="E399" t="s">
-        <v>445</v>
+        <v>211</v>
       </c>
       <c r="F399" t="s">
-        <v>341</v>
+        <v>203</v>
       </c>
       <c r="G399" t="s">
         <v>41</v>
       </c>
       <c r="H399" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="I399" t="s">
         <v>942</v>
       </c>
       <c r="J399" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="K399" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="L399" t="s">
         <v>939</v>
@@ -24871,13 +24871,13 @@
         <v>47</v>
       </c>
       <c r="O399" t="s">
-        <v>34</v>
+        <v>427</v>
       </c>
       <c r="P399" t="s">
-        <v>34</v>
+        <v>942</v>
       </c>
       <c r="Q399" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R399" t="s">
         <v>34</v>
@@ -24897,25 +24897,25 @@
         <v>34</v>
       </c>
       <c r="E400" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F400" t="s">
-        <v>341</v>
+        <v>203</v>
       </c>
       <c r="G400" t="s">
         <v>41</v>
       </c>
       <c r="H400" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="I400" t="s">
         <v>943</v>
       </c>
       <c r="J400" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K400" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="L400" t="s">
         <v>939</v>
@@ -24927,13 +24927,13 @@
         <v>47</v>
       </c>
       <c r="O400" t="s">
-        <v>34</v>
+        <v>490</v>
       </c>
       <c r="P400" t="s">
-        <v>34</v>
+        <v>943</v>
       </c>
       <c r="Q400" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R400" t="s">
         <v>34</v>
@@ -24962,7 +24962,7 @@
         <v>41</v>
       </c>
       <c r="H401" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I401" t="s">
         <v>944</v>
@@ -25018,7 +25018,7 @@
         <v>41</v>
       </c>
       <c r="H402" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I402" t="s">
         <v>945</v>
@@ -25074,7 +25074,7 @@
         <v>41</v>
       </c>
       <c r="H403" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I403" t="s">
         <v>946</v>
@@ -25130,7 +25130,7 @@
         <v>41</v>
       </c>
       <c r="H404" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I404" t="s">
         <v>947</v>
@@ -25186,7 +25186,7 @@
         <v>41</v>
       </c>
       <c r="H405" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I405" t="s">
         <v>949</v>
@@ -25242,7 +25242,7 @@
         <v>41</v>
       </c>
       <c r="H406" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="I406" t="s">
         <v>950</v>
@@ -25298,7 +25298,7 @@
         <v>41</v>
       </c>
       <c r="H407" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I407" t="s">
         <v>951</v>
@@ -25354,7 +25354,7 @@
         <v>41</v>
       </c>
       <c r="H408" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I408" t="s">
         <v>952</v>
@@ -25410,7 +25410,7 @@
         <v>41</v>
       </c>
       <c r="H409" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="I409" t="s">
         <v>953</v>
@@ -25466,7 +25466,7 @@
         <v>41</v>
       </c>
       <c r="H410" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I410" t="s">
         <v>954</v>
@@ -25522,7 +25522,7 @@
         <v>41</v>
       </c>
       <c r="H411" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I411" t="s">
         <v>955</v>
